--- a/Data/FlightPlan/FPL_25SEP26.xlsx
+++ b/Data/FlightPlan/FPL_25SEP26.xlsx
@@ -815,25 +815,118 @@
     <t>14:10</t>
   </si>
   <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
     <t>22:25</t>
   </si>
   <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
+    <t>VN-A642</t>
   </si>
   <si>
     <t>06:05</t>
@@ -842,99 +935,6 @@
     <t>13:45</t>
   </si>
   <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
     <t>VN-A643</t>
   </si>
   <si>
@@ -1238,7 +1238,7 @@
     <t>Total Record(s): 391</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 24, 2026 21:46</t>
+    <t xml:space="preserve">Generated on  Sep 24, 2026 23:24</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -7208,7 +7208,7 @@
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>781</v>
+        <v>151</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
@@ -7224,13 +7224,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>196</v>
+        <v>268</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7241,7 +7241,7 @@
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>780</v>
+        <v>648</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
@@ -7254,65 +7254,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>220</v>
+        <v>269</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>268</v>
+        <v>130</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c r="M188" s="7"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="A189" s="6"/>
-      <c r="B189" s="7"/>
-      <c r="C189" s="7"/>
+      <c t="s" r="A189" s="6">
+        <v>13</v>
+      </c>
+      <c r="B189" s="7">
+        <v>647</v>
+      </c>
+      <c t="s" r="C189" s="7">
+        <v>14</v>
+      </c>
       <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
-      <c r="F189" s="7"/>
-      <c r="G189" s="8"/>
-      <c r="H189" s="8"/>
-      <c r="I189" s="7"/>
-      <c r="J189" s="7"/>
+      <c t="s" r="E189" s="7">
+        <v>265</v>
+      </c>
+      <c r="F189" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G189" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="H189" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I189" s="7">
+        <v>97</v>
+      </c>
+      <c t="s" r="J189" s="7">
+        <v>244</v>
+      </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c r="M189" s="7"/>
     </row>
     <row r="190" ht="15" customHeight="1">
-      <c t="s" r="A190" s="6">
-        <v>13</v>
-      </c>
-      <c r="B190" s="7">
-        <v>905</v>
-      </c>
-      <c t="s" r="C190" s="7">
-        <v>14</v>
-      </c>
+      <c r="A190" s="6"/>
+      <c r="B190" s="7"/>
+      <c r="C190" s="7"/>
       <c r="D190" s="7"/>
-      <c t="s" r="E190" s="7">
-        <v>269</v>
-      </c>
-      <c r="F190" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G190" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H190" s="8">
-        <v>99</v>
-      </c>
-      <c t="s" r="I190" s="7">
-        <v>270</v>
-      </c>
-      <c t="s" r="J190" s="7">
-        <v>113</v>
-      </c>
+      <c r="E190" s="7"/>
+      <c r="F190" s="7"/>
+      <c r="G190" s="8"/>
+      <c r="H190" s="8"/>
+      <c r="I190" s="7"/>
+      <c r="J190" s="7"/>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c r="M190" s="7"/>
@@ -7322,29 +7322,29 @@
         <v>13</v>
       </c>
       <c r="B191" s="7">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H191" s="8">
         <v>99</v>
       </c>
-      <c t="s" r="H191" s="8">
-        <v>40</v>
-      </c>
       <c t="s" r="I191" s="7">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7355,29 +7355,29 @@
         <v>13</v>
       </c>
       <c r="B192" s="7">
-        <v>567</v>
+        <v>906</v>
       </c>
       <c t="s" r="C192" s="7">
         <v>14</v>
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
+        <v>99</v>
+      </c>
+      <c t="s" r="H192" s="8">
         <v>40</v>
       </c>
-      <c t="s" r="H192" s="8">
-        <v>87</v>
-      </c>
       <c t="s" r="I192" s="7">
-        <v>21</v>
+        <v>229</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>271</v>
+        <v>124</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7388,29 +7388,29 @@
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H193" s="8">
         <v>87</v>
       </c>
-      <c t="s" r="H193" s="8">
-        <v>40</v>
-      </c>
       <c t="s" r="I193" s="7">
+        <v>21</v>
+      </c>
+      <c t="s" r="J193" s="7">
         <v>272</v>
-      </c>
-      <c t="s" r="J193" s="7">
-        <v>69</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7421,29 +7421,29 @@
         <v>13</v>
       </c>
       <c r="B194" s="7">
-        <v>519</v>
+        <v>568</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
+        <v>87</v>
+      </c>
+      <c t="s" r="H194" s="8">
         <v>40</v>
       </c>
-      <c t="s" r="H194" s="8">
-        <v>155</v>
-      </c>
       <c t="s" r="I194" s="7">
-        <v>35</v>
+        <v>273</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>198</v>
+        <v>69</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7454,78 +7454,78 @@
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H195" s="8">
         <v>155</v>
       </c>
-      <c t="s" r="H195" s="8">
-        <v>40</v>
-      </c>
       <c t="s" r="I195" s="7">
-        <v>273</v>
+        <v>35</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c r="M195" s="7"/>
     </row>
     <row r="196" ht="14.25" customHeight="1">
-      <c r="A196" s="6"/>
-      <c r="B196" s="7"/>
-      <c r="C196" s="7"/>
+      <c t="s" r="A196" s="6">
+        <v>13</v>
+      </c>
+      <c r="B196" s="7">
+        <v>522</v>
+      </c>
+      <c t="s" r="C196" s="7">
+        <v>14</v>
+      </c>
       <c r="D196" s="7"/>
-      <c r="E196" s="7"/>
-      <c r="F196" s="7"/>
-      <c r="G196" s="8"/>
-      <c r="H196" s="8"/>
-      <c r="I196" s="7"/>
-      <c r="J196" s="7"/>
+      <c t="s" r="E196" s="7">
+        <v>270</v>
+      </c>
+      <c r="F196" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G196" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="H196" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I196" s="7">
+        <v>274</v>
+      </c>
+      <c t="s" r="J196" s="7">
+        <v>189</v>
+      </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c r="M196" s="7"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
-      <c t="s" r="A197" s="6">
-        <v>13</v>
-      </c>
-      <c r="B197" s="7">
-        <v>124</v>
-      </c>
-      <c t="s" r="C197" s="7">
-        <v>14</v>
-      </c>
+      <c r="A197" s="6"/>
+      <c r="B197" s="7"/>
+      <c r="C197" s="7"/>
       <c r="D197" s="7"/>
-      <c t="s" r="E197" s="7">
-        <v>274</v>
-      </c>
-      <c r="F197" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G197" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H197" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I197" s="7">
-        <v>275</v>
-      </c>
-      <c t="s" r="J197" s="7">
-        <v>235</v>
-      </c>
+      <c r="E197" s="7"/>
+      <c r="F197" s="7"/>
+      <c r="G197" s="8"/>
+      <c r="H197" s="8"/>
+      <c r="I197" s="7"/>
+      <c r="J197" s="7"/>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c r="M197" s="7"/>
@@ -7535,29 +7535,29 @@
         <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>129</v>
+        <v>1362</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7568,29 +7568,29 @@
         <v>13</v>
       </c>
       <c r="B199" s="7">
-        <v>210</v>
+        <v>1363</v>
       </c>
       <c t="s" r="C199" s="7">
         <v>14</v>
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>241</v>
+        <v>111</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7601,29 +7601,29 @@
         <v>13</v>
       </c>
       <c r="B200" s="7">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c t="s" r="C200" s="7">
         <v>14</v>
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>276</v>
+        <v>64</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7634,45 +7634,63 @@
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>150</v>
+        <v>324</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>272</v>
+        <v>122</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c r="M201" s="7"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c r="A202" s="6"/>
-      <c r="B202" s="7"/>
-      <c r="C202" s="7"/>
+      <c t="s" r="A202" s="6">
+        <v>13</v>
+      </c>
+      <c r="B202" s="7">
+        <v>807</v>
+      </c>
+      <c t="s" r="C202" s="7">
+        <v>14</v>
+      </c>
       <c r="D202" s="7"/>
-      <c r="E202" s="7"/>
-      <c r="F202" s="7"/>
-      <c r="G202" s="8"/>
-      <c r="H202" s="8"/>
-      <c r="I202" s="7"/>
-      <c r="J202" s="7"/>
+      <c t="s" r="E202" s="7">
+        <v>275</v>
+      </c>
+      <c r="F202" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G202" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H202" s="8">
+        <v>276</v>
+      </c>
+      <c t="s" r="I202" s="7">
+        <v>241</v>
+      </c>
+      <c t="s" r="J202" s="7">
+        <v>277</v>
+      </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c r="M202" s="7"/>
@@ -7682,29 +7700,29 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>123</v>
+        <v>800</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>245</v>
+        <v>278</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>278</v>
+        <v>150</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7715,14 +7733,14 @@
         <v>13</v>
       </c>
       <c r="B204" s="7">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c t="s" r="C204" s="7">
         <v>14</v>
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7737,41 +7755,23 @@
         <v>279</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c r="M204" s="7"/>
     </row>
     <row r="205" ht="15" customHeight="1">
-      <c t="s" r="A205" s="6">
-        <v>13</v>
-      </c>
-      <c r="B205" s="7">
-        <v>1491</v>
-      </c>
-      <c t="s" r="C205" s="7">
-        <v>14</v>
-      </c>
+      <c r="A205" s="6"/>
+      <c r="B205" s="7"/>
+      <c r="C205" s="7"/>
       <c r="D205" s="7"/>
-      <c t="s" r="E205" s="7">
-        <v>277</v>
-      </c>
-      <c r="F205" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G205" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H205" s="8">
-        <v>168</v>
-      </c>
-      <c t="s" r="I205" s="7">
-        <v>266</v>
-      </c>
-      <c t="s" r="J205" s="7">
-        <v>52</v>
-      </c>
+      <c r="E205" s="7"/>
+      <c r="F205" s="7"/>
+      <c r="G205" s="8"/>
+      <c r="H205" s="8"/>
+      <c r="I205" s="7"/>
+      <c r="J205" s="7"/>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c r="M205" s="7"/>
@@ -7781,29 +7781,29 @@
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>1492</v>
+        <v>123</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>168</v>
+        <v>40</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7814,29 +7814,29 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>405</v>
+        <v>130</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H207" s="8">
         <v>40</v>
       </c>
-      <c t="s" r="H207" s="8">
-        <v>123</v>
-      </c>
       <c t="s" r="I207" s="7">
-        <v>94</v>
+        <v>282</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7847,29 +7847,29 @@
         <v>13</v>
       </c>
       <c r="B208" s="7">
-        <v>406</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>128</v>
+        <v>266</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>227</v>
+        <v>52</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7880,45 +7880,63 @@
         <v>13</v>
       </c>
       <c r="B209" s="7">
-        <v>169</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
+        <v>168</v>
+      </c>
+      <c t="s" r="H209" s="8">
         <v>40</v>
       </c>
-      <c t="s" r="H209" s="8">
-        <v>29</v>
-      </c>
       <c t="s" r="I209" s="7">
-        <v>281</v>
+        <v>78</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c r="M209" s="7"/>
     </row>
     <row r="210" ht="15" customHeight="1">
-      <c r="A210" s="6"/>
-      <c r="B210" s="7"/>
-      <c r="C210" s="7"/>
+      <c t="s" r="A210" s="6">
+        <v>13</v>
+      </c>
+      <c r="B210" s="7">
+        <v>405</v>
+      </c>
+      <c t="s" r="C210" s="7">
+        <v>14</v>
+      </c>
       <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
-      <c r="G210" s="8"/>
-      <c r="H210" s="8"/>
-      <c r="I210" s="7"/>
-      <c r="J210" s="7"/>
+      <c t="s" r="E210" s="7">
+        <v>280</v>
+      </c>
+      <c r="F210" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G210" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H210" s="8">
+        <v>123</v>
+      </c>
+      <c t="s" r="I210" s="7">
+        <v>94</v>
+      </c>
+      <c t="s" r="J210" s="7">
+        <v>45</v>
+      </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c r="M210" s="7"/>
@@ -7928,29 +7946,29 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>849</v>
+        <v>406</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>284</v>
+        <v>227</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7961,26 +7979,26 @@
         <v>13</v>
       </c>
       <c r="B212" s="7">
-        <v>848</v>
+        <v>169</v>
       </c>
       <c t="s" r="C212" s="7">
         <v>14</v>
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>54</v>
+        <v>284</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>285</v>
@@ -7990,82 +8008,82 @@
       <c r="M212" s="7"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
-      <c t="s" r="A213" s="6">
-        <v>13</v>
-      </c>
-      <c r="B213" s="7">
-        <v>3900</v>
-      </c>
-      <c t="s" r="C213" s="7">
-        <v>14</v>
-      </c>
+      <c r="A213" s="6"/>
+      <c r="B213" s="7"/>
+      <c r="C213" s="7"/>
       <c r="D213" s="7"/>
-      <c t="s" r="E213" s="7">
-        <v>283</v>
-      </c>
-      <c r="F213" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G213" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H213" s="8">
-        <v>286</v>
-      </c>
-      <c t="s" r="I213" s="7">
-        <v>287</v>
-      </c>
-      <c t="s" r="J213" s="7">
-        <v>104</v>
-      </c>
+      <c r="E213" s="7"/>
+      <c r="F213" s="7"/>
+      <c r="G213" s="8"/>
+      <c r="H213" s="8"/>
+      <c r="I213" s="7"/>
+      <c r="J213" s="7"/>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c r="M213" s="7"/>
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c t="s" r="A214" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>3901</v>
+        <v>849</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>286</v>
+        <v>29</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>234</v>
+        <v>162</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c r="M214" s="7"/>
     </row>
     <row r="215" ht="15" customHeight="1">
-      <c r="A215" s="6"/>
-      <c r="B215" s="7"/>
-      <c r="C215" s="7"/>
+      <c t="s" r="A215" s="6">
+        <v>13</v>
+      </c>
+      <c r="B215" s="7">
+        <v>848</v>
+      </c>
+      <c t="s" r="C215" s="7">
+        <v>14</v>
+      </c>
       <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
-      <c r="F215" s="7"/>
-      <c r="G215" s="8"/>
-      <c r="H215" s="8"/>
-      <c r="I215" s="7"/>
-      <c r="J215" s="7"/>
+      <c t="s" r="E215" s="7">
+        <v>286</v>
+      </c>
+      <c r="F215" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G215" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H215" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I215" s="7">
+        <v>54</v>
+      </c>
+      <c t="s" r="J215" s="7">
+        <v>268</v>
+      </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c r="M215" s="7"/>
@@ -8075,29 +8093,29 @@
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>449</v>
+        <v>3900</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>70</v>
+        <v>288</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>62</v>
+        <v>269</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>290</v>
+        <v>104</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8105,66 +8123,48 @@
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c t="s" r="A217" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B217" s="7">
-        <v>450</v>
+        <v>3901</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
+        <v>286</v>
+      </c>
+      <c r="F217" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G217" s="8">
+        <v>288</v>
+      </c>
+      <c t="s" r="H217" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I217" s="7">
+        <v>234</v>
+      </c>
+      <c t="s" r="J217" s="7">
         <v>289</v>
-      </c>
-      <c r="F217" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G217" s="8">
-        <v>70</v>
-      </c>
-      <c t="s" r="H217" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I217" s="7">
-        <v>291</v>
-      </c>
-      <c t="s" r="J217" s="7">
-        <v>202</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c r="M217" s="7"/>
     </row>
     <row r="218" ht="14.25" customHeight="1">
-      <c t="s" r="A218" s="6">
-        <v>13</v>
-      </c>
-      <c r="B218" s="7">
-        <v>515</v>
-      </c>
-      <c t="s" r="C218" s="7">
-        <v>14</v>
-      </c>
+      <c r="A218" s="6"/>
+      <c r="B218" s="7"/>
+      <c r="C218" s="7"/>
       <c r="D218" s="7"/>
-      <c t="s" r="E218" s="7">
-        <v>289</v>
-      </c>
-      <c r="F218" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G218" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H218" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="I218" s="7">
-        <v>91</v>
-      </c>
-      <c t="s" r="J218" s="7">
-        <v>78</v>
-      </c>
+      <c r="E218" s="7"/>
+      <c r="F218" s="7"/>
+      <c r="G218" s="8"/>
+      <c r="H218" s="8"/>
+      <c r="I218" s="7"/>
+      <c r="J218" s="7"/>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c r="M218" s="7"/>
@@ -8174,29 +8174,29 @@
         <v>13</v>
       </c>
       <c r="B219" s="7">
-        <v>508</v>
+        <v>449</v>
       </c>
       <c t="s" r="C219" s="7">
         <v>14</v>
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>224</v>
+        <v>291</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8207,45 +8207,63 @@
         <v>13</v>
       </c>
       <c r="B220" s="7">
-        <v>773</v>
+        <v>450</v>
       </c>
       <c t="s" r="C220" s="7">
         <v>14</v>
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
+        <v>70</v>
+      </c>
+      <c t="s" r="H220" s="8">
         <v>40</v>
-      </c>
-      <c t="s" r="H220" s="8">
-        <v>17</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>292</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c r="M220" s="7"/>
     </row>
     <row r="221" ht="14.25" customHeight="1">
-      <c r="A221" s="6"/>
-      <c r="B221" s="7"/>
-      <c r="C221" s="7"/>
+      <c t="s" r="A221" s="6">
+        <v>13</v>
+      </c>
+      <c r="B221" s="7">
+        <v>515</v>
+      </c>
+      <c t="s" r="C221" s="7">
+        <v>14</v>
+      </c>
       <c r="D221" s="7"/>
-      <c r="E221" s="7"/>
-      <c r="F221" s="7"/>
-      <c r="G221" s="8"/>
-      <c r="H221" s="8"/>
-      <c r="I221" s="7"/>
-      <c r="J221" s="7"/>
+      <c t="s" r="E221" s="7">
+        <v>290</v>
+      </c>
+      <c r="F221" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G221" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H221" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="I221" s="7">
+        <v>91</v>
+      </c>
+      <c t="s" r="J221" s="7">
+        <v>78</v>
+      </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c r="M221" s="7"/>
@@ -8255,29 +8273,29 @@
         <v>13</v>
       </c>
       <c r="B222" s="7">
-        <v>1242</v>
+        <v>508</v>
       </c>
       <c t="s" r="C222" s="7">
         <v>14</v>
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>88</v>
+        <v>224</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8288,29 +8306,29 @@
         <v>13</v>
       </c>
       <c r="B223" s="7">
-        <v>1241</v>
+        <v>773</v>
       </c>
       <c t="s" r="C223" s="7">
         <v>14</v>
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
+        <v>290</v>
+      </c>
+      <c r="F223" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G223" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H223" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I223" s="7">
         <v>293</v>
       </c>
-      <c r="F223" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G223" s="8">
-        <v>92</v>
-      </c>
-      <c t="s" r="H223" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I223" s="7">
-        <v>64</v>
-      </c>
       <c t="s" r="J223" s="7">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8321,20 +8339,20 @@
         <v>13</v>
       </c>
       <c r="B224" s="7">
-        <v>134</v>
+        <v>776</v>
       </c>
       <c t="s" r="C224" s="7">
         <v>14</v>
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>40</v>
@@ -8343,41 +8361,23 @@
         <v>294</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>54</v>
+        <v>295</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c r="M224" s="7"/>
     </row>
     <row r="225" ht="15" customHeight="1">
-      <c t="s" r="A225" s="6">
-        <v>13</v>
-      </c>
-      <c r="B225" s="7">
-        <v>145</v>
-      </c>
-      <c t="s" r="C225" s="7">
-        <v>14</v>
-      </c>
+      <c r="A225" s="6"/>
+      <c r="B225" s="7"/>
+      <c r="C225" s="7"/>
       <c r="D225" s="7"/>
-      <c t="s" r="E225" s="7">
-        <v>293</v>
-      </c>
-      <c r="F225" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G225" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H225" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I225" s="7">
-        <v>124</v>
-      </c>
-      <c t="s" r="J225" s="7">
-        <v>285</v>
-      </c>
+      <c r="E225" s="7"/>
+      <c r="F225" s="7"/>
+      <c r="G225" s="8"/>
+      <c r="H225" s="8"/>
+      <c r="I225" s="7"/>
+      <c r="J225" s="7"/>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c r="M225" s="7"/>
@@ -8387,14 +8387,14 @@
         <v>13</v>
       </c>
       <c r="B226" s="7">
-        <v>331</v>
+        <v>1242</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8403,13 +8403,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>174</v>
+        <v>88</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8420,45 +8420,63 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>328</v>
+        <v>1241</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>188</v>
+        <v>64</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>22</v>
+        <v>266</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c r="M227" s="7"/>
     </row>
     <row r="228" ht="14.25" customHeight="1">
-      <c r="A228" s="6"/>
-      <c r="B228" s="7"/>
-      <c r="C228" s="7"/>
+      <c t="s" r="A228" s="6">
+        <v>13</v>
+      </c>
+      <c r="B228" s="7">
+        <v>134</v>
+      </c>
+      <c t="s" r="C228" s="7">
+        <v>14</v>
+      </c>
       <c r="D228" s="7"/>
-      <c r="E228" s="7"/>
-      <c r="F228" s="7"/>
-      <c r="G228" s="8"/>
-      <c r="H228" s="8"/>
-      <c r="I228" s="7"/>
-      <c r="J228" s="7"/>
+      <c t="s" r="E228" s="7">
+        <v>296</v>
+      </c>
+      <c r="F228" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G228" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H228" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I228" s="7">
+        <v>297</v>
+      </c>
+      <c t="s" r="J228" s="7">
+        <v>54</v>
+      </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c r="M228" s="7"/>
@@ -8468,29 +8486,29 @@
         <v>13</v>
       </c>
       <c r="B229" s="7">
-        <v>835</v>
+        <v>145</v>
       </c>
       <c t="s" r="C229" s="7">
         <v>14</v>
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8501,29 +8519,29 @@
         <v>13</v>
       </c>
       <c r="B230" s="7">
-        <v>5512</v>
+        <v>331</v>
       </c>
       <c t="s" r="C230" s="7">
         <v>14</v>
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>297</v>
+        <v>219</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8534,78 +8552,78 @@
         <v>13</v>
       </c>
       <c r="B231" s="7">
-        <v>5513</v>
+        <v>328</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c r="M231" s="7"/>
     </row>
     <row r="232" ht="14.25" customHeight="1">
-      <c t="s" r="A232" s="6">
-        <v>13</v>
-      </c>
-      <c r="B232" s="7">
-        <v>834</v>
-      </c>
-      <c t="s" r="C232" s="7">
-        <v>14</v>
-      </c>
+      <c r="A232" s="6"/>
+      <c r="B232" s="7"/>
+      <c r="C232" s="7"/>
       <c r="D232" s="7"/>
-      <c t="s" r="E232" s="7">
-        <v>295</v>
-      </c>
-      <c r="F232" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G232" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H232" s="8">
-        <v>108</v>
-      </c>
-      <c t="s" r="I232" s="7">
-        <v>36</v>
-      </c>
-      <c t="s" r="J232" s="7">
-        <v>83</v>
-      </c>
+      <c r="E232" s="7"/>
+      <c r="F232" s="7"/>
+      <c r="G232" s="8"/>
+      <c r="H232" s="8"/>
+      <c r="I232" s="7"/>
+      <c r="J232" s="7"/>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c r="M232" s="7"/>
     </row>
     <row r="233" ht="14.25" customHeight="1">
-      <c r="A233" s="6"/>
-      <c r="B233" s="7"/>
-      <c r="C233" s="7"/>
+      <c t="s" r="A233" s="6">
+        <v>13</v>
+      </c>
+      <c r="B233" s="7">
+        <v>835</v>
+      </c>
+      <c t="s" r="C233" s="7">
+        <v>14</v>
+      </c>
       <c r="D233" s="7"/>
-      <c r="E233" s="7"/>
-      <c r="F233" s="7"/>
-      <c r="G233" s="8"/>
-      <c r="H233" s="8"/>
-      <c r="I233" s="7"/>
-      <c r="J233" s="7"/>
+      <c t="s" r="E233" s="7">
+        <v>298</v>
+      </c>
+      <c r="F233" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G233" s="8">
+        <v>108</v>
+      </c>
+      <c t="s" r="H233" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I233" s="7">
+        <v>84</v>
+      </c>
+      <c t="s" r="J233" s="7">
+        <v>299</v>
+      </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c r="M233" s="7"/>
@@ -8615,7 +8633,7 @@
         <v>13</v>
       </c>
       <c r="B234" s="7">
-        <v>730</v>
+        <v>5512</v>
       </c>
       <c t="s" r="C234" s="7">
         <v>14</v>
@@ -8631,13 +8649,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>300</v>
+        <v>159</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8648,7 +8666,7 @@
         <v>13</v>
       </c>
       <c r="B235" s="7">
-        <v>731</v>
+        <v>5513</v>
       </c>
       <c t="s" r="C235" s="7">
         <v>14</v>
@@ -8661,16 +8679,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>301</v>
+        <v>227</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8681,7 +8699,7 @@
         <v>13</v>
       </c>
       <c r="B236" s="7">
-        <v>776</v>
+        <v>834</v>
       </c>
       <c t="s" r="C236" s="7">
         <v>14</v>
@@ -8697,13 +8715,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>302</v>
+        <v>36</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8729,29 +8747,29 @@
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>1362</v>
+        <v>730</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>106</v>
+        <v>302</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>179</v>
+        <v>303</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8762,29 +8780,29 @@
         <v>13</v>
       </c>
       <c r="B239" s="7">
-        <v>1363</v>
+        <v>731</v>
       </c>
       <c t="s" r="C239" s="7">
         <v>14</v>
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>110</v>
+        <v>287</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8795,63 +8813,45 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>337</v>
+        <v>780</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
+        <v>301</v>
+      </c>
+      <c r="F240" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G240" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H240" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I240" s="7">
+        <v>220</v>
+      </c>
+      <c t="s" r="J240" s="7">
         <v>304</v>
-      </c>
-      <c r="F240" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G240" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H240" s="8">
-        <v>70</v>
-      </c>
-      <c t="s" r="I240" s="7">
-        <v>64</v>
-      </c>
-      <c t="s" r="J240" s="7">
-        <v>156</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c r="M240" s="7"/>
     </row>
     <row r="241" ht="14.25" customHeight="1">
-      <c t="s" r="A241" s="6">
-        <v>13</v>
-      </c>
-      <c r="B241" s="7">
-        <v>324</v>
-      </c>
-      <c t="s" r="C241" s="7">
-        <v>14</v>
-      </c>
+      <c r="A241" s="6"/>
+      <c r="B241" s="7"/>
+      <c r="C241" s="7"/>
       <c r="D241" s="7"/>
-      <c t="s" r="E241" s="7">
-        <v>304</v>
-      </c>
-      <c r="F241" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G241" s="8">
-        <v>70</v>
-      </c>
-      <c t="s" r="H241" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I241" s="7">
-        <v>122</v>
-      </c>
-      <c t="s" r="J241" s="7">
-        <v>182</v>
-      </c>
+      <c r="E241" s="7"/>
+      <c r="F241" s="7"/>
+      <c r="G241" s="8"/>
+      <c r="H241" s="8"/>
+      <c r="I241" s="7"/>
+      <c r="J241" s="7"/>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c r="M241" s="7"/>
@@ -8861,14 +8861,14 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>807</v>
+        <v>124</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8877,13 +8877,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>305</v>
+        <v>40</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>241</v>
+        <v>306</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8894,29 +8894,29 @@
         <v>13</v>
       </c>
       <c r="B243" s="7">
-        <v>800</v>
+        <v>129</v>
       </c>
       <c t="s" r="C243" s="7">
         <v>14</v>
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>305</v>
+        <v>40</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>306</v>
+        <v>31</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8927,14 +8927,14 @@
         <v>13</v>
       </c>
       <c r="B244" s="7">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c t="s" r="C244" s="7">
         <v>14</v>
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8943,29 +8943,47 @@
         <v>29</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>141</v>
+        <v>241</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c r="M244" s="7"/>
     </row>
     <row r="245" ht="15" customHeight="1">
-      <c r="A245" s="6"/>
-      <c r="B245" s="7"/>
-      <c r="C245" s="7"/>
+      <c t="s" r="A245" s="6">
+        <v>13</v>
+      </c>
+      <c r="B245" s="7">
+        <v>211</v>
+      </c>
+      <c t="s" r="C245" s="7">
+        <v>14</v>
+      </c>
       <c r="D245" s="7"/>
-      <c r="E245" s="7"/>
-      <c r="F245" s="7"/>
-      <c r="G245" s="8"/>
-      <c r="H245" s="8"/>
-      <c r="I245" s="7"/>
-      <c r="J245" s="7"/>
+      <c t="s" r="E245" s="7">
+        <v>305</v>
+      </c>
+      <c r="F245" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G245" s="8">
+        <v>53</v>
+      </c>
+      <c t="s" r="H245" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I245" s="7">
+        <v>307</v>
+      </c>
+      <c t="s" r="J245" s="7">
+        <v>125</v>
+      </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c r="M245" s="7"/>
@@ -8975,63 +8993,45 @@
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>461</v>
+        <v>150</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H246" s="8">
         <v>40</v>
       </c>
-      <c t="s" r="H246" s="8">
-        <v>309</v>
-      </c>
       <c t="s" r="I246" s="7">
-        <v>84</v>
+        <v>273</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c r="M246" s="7"/>
     </row>
     <row r="247" ht="14.25" customHeight="1">
-      <c t="s" r="A247" s="6">
-        <v>13</v>
-      </c>
-      <c r="B247" s="7">
-        <v>462</v>
-      </c>
-      <c t="s" r="C247" s="7">
-        <v>14</v>
-      </c>
+      <c r="A247" s="6"/>
+      <c r="B247" s="7"/>
+      <c r="C247" s="7"/>
       <c r="D247" s="7"/>
-      <c t="s" r="E247" s="7">
-        <v>308</v>
-      </c>
-      <c r="F247" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G247" s="8">
-        <v>309</v>
-      </c>
-      <c t="s" r="H247" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I247" s="7">
-        <v>51</v>
-      </c>
-      <c t="s" r="J247" s="7">
-        <v>185</v>
-      </c>
+      <c r="E247" s="7"/>
+      <c r="F247" s="7"/>
+      <c r="G247" s="8"/>
+      <c r="H247" s="8"/>
+      <c r="I247" s="7"/>
+      <c r="J247" s="7"/>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c r="M247" s="7"/>
@@ -9041,7 +9041,7 @@
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>787</v>
+        <v>461</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
@@ -9057,13 +9057,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>223</v>
+        <v>84</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9074,7 +9074,7 @@
         <v>13</v>
       </c>
       <c r="B249" s="7">
-        <v>774</v>
+        <v>462</v>
       </c>
       <c t="s" r="C249" s="7">
         <v>14</v>
@@ -9087,16 +9087,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>224</v>
+        <v>51</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9107,7 +9107,7 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>517</v>
+        <v>787</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
@@ -9123,13 +9123,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>151</v>
+        <v>223</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>243</v>
+        <v>186</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9140,7 +9140,7 @@
         <v>13</v>
       </c>
       <c r="B251" s="7">
-        <v>520</v>
+        <v>774</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
@@ -9153,16 +9153,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>116</v>
+        <v>224</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9173,7 +9173,7 @@
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>7526</v>
+        <v>517</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
@@ -9189,13 +9189,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>257</v>
+        <v>155</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>310</v>
+        <v>151</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9203,10 +9203,10 @@
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c t="s" r="A253" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B253" s="7">
-        <v>7527</v>
+        <v>520</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
@@ -9219,98 +9219,98 @@
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>257</v>
+        <v>155</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>311</v>
+        <v>116</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>312</v>
+        <v>141</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c r="M253" s="7"/>
     </row>
     <row r="254" ht="14.25" customHeight="1">
-      <c r="A254" s="6"/>
-      <c r="B254" s="7"/>
-      <c r="C254" s="7"/>
+      <c t="s" r="A254" s="6">
+        <v>13</v>
+      </c>
+      <c r="B254" s="7">
+        <v>7526</v>
+      </c>
+      <c t="s" r="C254" s="7">
+        <v>14</v>
+      </c>
       <c r="D254" s="7"/>
-      <c r="E254" s="7"/>
-      <c r="F254" s="7"/>
-      <c r="G254" s="8"/>
-      <c r="H254" s="8"/>
-      <c r="I254" s="7"/>
-      <c r="J254" s="7"/>
+      <c t="s" r="E254" s="7">
+        <v>308</v>
+      </c>
+      <c r="F254" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G254" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H254" s="8">
+        <v>257</v>
+      </c>
+      <c t="s" r="I254" s="7">
+        <v>310</v>
+      </c>
+      <c t="s" r="J254" s="7">
+        <v>132</v>
+      </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c r="M254" s="7"/>
     </row>
     <row r="255" ht="15" customHeight="1">
       <c t="s" r="A255" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B255" s="7">
-        <v>959</v>
+        <v>7527</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>314</v>
+        <v>257</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>181</v>
+        <v>311</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c r="M255" s="7"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c t="s" r="A256" s="6">
-        <v>13</v>
-      </c>
-      <c r="B256" s="7">
-        <v>407</v>
-      </c>
-      <c t="s" r="C256" s="7">
-        <v>14</v>
-      </c>
+      <c r="A256" s="6"/>
+      <c r="B256" s="7"/>
+      <c r="C256" s="7"/>
       <c r="D256" s="7"/>
-      <c t="s" r="E256" s="7">
-        <v>313</v>
-      </c>
-      <c r="F256" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G256" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H256" s="8">
-        <v>123</v>
-      </c>
-      <c t="s" r="I256" s="7">
-        <v>54</v>
-      </c>
-      <c t="s" r="J256" s="7">
-        <v>55</v>
-      </c>
+      <c r="E256" s="7"/>
+      <c r="F256" s="7"/>
+      <c r="G256" s="8"/>
+      <c r="H256" s="8"/>
+      <c r="I256" s="7"/>
+      <c r="J256" s="7"/>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c r="M256" s="7"/>
@@ -9320,7 +9320,7 @@
         <v>13</v>
       </c>
       <c r="B257" s="7">
-        <v>408</v>
+        <v>959</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
@@ -9333,16 +9333,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>123</v>
+        <v>314</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>56</v>
+        <v>181</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9353,7 +9353,7 @@
         <v>13</v>
       </c>
       <c r="B258" s="7">
-        <v>1127</v>
+        <v>407</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
@@ -9369,13 +9369,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9386,7 +9386,7 @@
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>1128</v>
+        <v>408</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
@@ -9399,16 +9399,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>315</v>
+        <v>56</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>316</v>
+        <v>57</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9416,10 +9416,10 @@
     </row>
     <row r="260" ht="15" customHeight="1">
       <c t="s" r="A260" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B260" s="7">
-        <v>958</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
@@ -9435,95 +9435,95 @@
         <v>40</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>314</v>
+        <v>29</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>317</v>
+        <v>188</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c r="M260" s="7"/>
     </row>
     <row r="261" ht="14.25" customHeight="1">
-      <c r="A261" s="6"/>
-      <c r="B261" s="7"/>
-      <c r="C261" s="7"/>
+      <c t="s" r="A261" s="6">
+        <v>13</v>
+      </c>
+      <c r="B261" s="7">
+        <v>1128</v>
+      </c>
+      <c t="s" r="C261" s="7">
+        <v>14</v>
+      </c>
       <c r="D261" s="7"/>
-      <c r="E261" s="7"/>
-      <c r="F261" s="7"/>
-      <c r="G261" s="8"/>
-      <c r="H261" s="8"/>
-      <c r="I261" s="7"/>
-      <c r="J261" s="7"/>
+      <c t="s" r="E261" s="7">
+        <v>313</v>
+      </c>
+      <c r="F261" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G261" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H261" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I261" s="7">
+        <v>315</v>
+      </c>
+      <c t="s" r="J261" s="7">
+        <v>316</v>
+      </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c r="M261" s="7"/>
     </row>
     <row r="262" ht="14.25" customHeight="1">
       <c t="s" r="A262" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B262" s="7">
-        <v>302</v>
+        <v>958</v>
       </c>
       <c t="s" r="C262" s="7">
         <v>14</v>
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>87</v>
+        <v>314</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>245</v>
+        <v>317</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>41</v>
+        <v>162</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c r="M262" s="7"/>
     </row>
     <row r="263" ht="14.25" customHeight="1">
-      <c t="s" r="A263" s="6">
-        <v>13</v>
-      </c>
-      <c r="B263" s="7">
-        <v>301</v>
-      </c>
-      <c t="s" r="C263" s="7">
-        <v>14</v>
-      </c>
+      <c r="A263" s="6"/>
+      <c r="B263" s="7"/>
+      <c r="C263" s="7"/>
       <c r="D263" s="7"/>
-      <c t="s" r="E263" s="7">
-        <v>318</v>
-      </c>
-      <c r="F263" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G263" s="8">
-        <v>87</v>
-      </c>
-      <c t="s" r="H263" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I263" s="7">
-        <v>270</v>
-      </c>
-      <c t="s" r="J263" s="7">
-        <v>88</v>
-      </c>
+      <c r="E263" s="7"/>
+      <c r="F263" s="7"/>
+      <c r="G263" s="8"/>
+      <c r="H263" s="8"/>
+      <c r="I263" s="7"/>
+      <c r="J263" s="7"/>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c r="M263" s="7"/>
@@ -9533,7 +9533,7 @@
         <v>13</v>
       </c>
       <c r="B264" s="7">
-        <v>852</v>
+        <v>350</v>
       </c>
       <c t="s" r="C264" s="7">
         <v>14</v>
@@ -9549,13 +9549,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9566,7 +9566,7 @@
         <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>853</v>
+        <v>351</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
@@ -9579,16 +9579,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9599,7 +9599,7 @@
         <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
@@ -9615,13 +9615,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>319</v>
+        <v>134</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>268</v>
+        <v>148</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>311</v>
+        <v>79</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9629,10 +9629,10 @@
     </row>
     <row r="267" ht="14.25" customHeight="1">
       <c t="s" r="A267" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B267" s="7">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c t="s" r="C267" s="7">
         <v>14</v>
@@ -9645,98 +9645,98 @@
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>319</v>
+        <v>134</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>320</v>
+        <v>114</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>321</v>
+        <v>128</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c r="M267" s="7"/>
     </row>
     <row r="268" ht="14.25" customHeight="1">
-      <c r="A268" s="6"/>
-      <c r="B268" s="7"/>
-      <c r="C268" s="7"/>
+      <c t="s" r="A268" s="6">
+        <v>13</v>
+      </c>
+      <c r="B268" s="7">
+        <v>858</v>
+      </c>
+      <c t="s" r="C268" s="7">
+        <v>14</v>
+      </c>
       <c r="D268" s="7"/>
-      <c r="E268" s="7"/>
-      <c r="F268" s="7"/>
-      <c r="G268" s="8"/>
-      <c r="H268" s="8"/>
-      <c r="I268" s="7"/>
-      <c r="J268" s="7"/>
+      <c t="s" r="E268" s="7">
+        <v>318</v>
+      </c>
+      <c r="F268" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G268" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H268" s="8">
+        <v>319</v>
+      </c>
+      <c t="s" r="I268" s="7">
+        <v>304</v>
+      </c>
+      <c t="s" r="J268" s="7">
+        <v>311</v>
+      </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c r="M268" s="7"/>
     </row>
     <row r="269" ht="14.25" customHeight="1">
       <c t="s" r="A269" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B269" s="7">
-        <v>92</v>
+        <v>859</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>253</v>
+        <v>319</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c r="M269" s="7"/>
     </row>
     <row r="270" ht="15" customHeight="1">
-      <c t="s" r="A270" s="6">
-        <v>13</v>
-      </c>
-      <c r="B270" s="7">
-        <v>282</v>
-      </c>
-      <c t="s" r="C270" s="7">
-        <v>14</v>
-      </c>
+      <c r="A270" s="6"/>
+      <c r="B270" s="7"/>
+      <c r="C270" s="7"/>
       <c r="D270" s="7"/>
-      <c t="s" r="E270" s="7">
-        <v>322</v>
-      </c>
-      <c r="F270" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G270" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H270" s="8">
-        <v>120</v>
-      </c>
-      <c t="s" r="I270" s="7">
-        <v>272</v>
-      </c>
-      <c t="s" r="J270" s="7">
-        <v>323</v>
-      </c>
+      <c r="E270" s="7"/>
+      <c r="F270" s="7"/>
+      <c r="G270" s="8"/>
+      <c r="H270" s="8"/>
+      <c r="I270" s="7"/>
+      <c r="J270" s="7"/>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c r="M270" s="7"/>
@@ -9746,7 +9746,7 @@
         <v>13</v>
       </c>
       <c r="B271" s="7">
-        <v>283</v>
+        <v>92</v>
       </c>
       <c t="s" r="C271" s="7">
         <v>14</v>
@@ -9759,16 +9759,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>120</v>
+        <v>253</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>117</v>
+        <v>302</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9779,7 +9779,7 @@
         <v>13</v>
       </c>
       <c r="B272" s="7">
-        <v>822</v>
+        <v>282</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
@@ -9795,29 +9795,47 @@
         <v>29</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>190</v>
+        <v>273</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>162</v>
+        <v>323</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c r="M272" s="7"/>
     </row>
     <row r="273" ht="14.25" customHeight="1">
-      <c r="A273" s="6"/>
-      <c r="B273" s="7"/>
-      <c r="C273" s="7"/>
+      <c t="s" r="A273" s="6">
+        <v>13</v>
+      </c>
+      <c r="B273" s="7">
+        <v>283</v>
+      </c>
+      <c t="s" r="C273" s="7">
+        <v>14</v>
+      </c>
       <c r="D273" s="7"/>
-      <c r="E273" s="7"/>
-      <c r="F273" s="7"/>
-      <c r="G273" s="8"/>
-      <c r="H273" s="8"/>
-      <c r="I273" s="7"/>
-      <c r="J273" s="7"/>
+      <c t="s" r="E273" s="7">
+        <v>322</v>
+      </c>
+      <c r="F273" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G273" s="8">
+        <v>120</v>
+      </c>
+      <c t="s" r="H273" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I273" s="7">
+        <v>117</v>
+      </c>
+      <c t="s" r="J273" s="7">
+        <v>72</v>
+      </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c r="M273" s="7"/>
@@ -9827,63 +9845,45 @@
         <v>13</v>
       </c>
       <c r="B274" s="7">
-        <v>701</v>
+        <v>822</v>
       </c>
       <c t="s" r="C274" s="7">
         <v>14</v>
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>309</v>
+        <v>46</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>145</v>
+        <v>190</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c r="M274" s="7"/>
     </row>
     <row r="275" ht="15" customHeight="1">
-      <c t="s" r="A275" s="6">
-        <v>13</v>
-      </c>
-      <c r="B275" s="7">
-        <v>702</v>
-      </c>
-      <c t="s" r="C275" s="7">
-        <v>14</v>
-      </c>
+      <c r="A275" s="6"/>
+      <c r="B275" s="7"/>
+      <c r="C275" s="7"/>
       <c r="D275" s="7"/>
-      <c t="s" r="E275" s="7">
-        <v>324</v>
-      </c>
-      <c r="F275" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G275" s="8">
-        <v>309</v>
-      </c>
-      <c t="s" r="H275" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="I275" s="7">
-        <v>325</v>
-      </c>
-      <c t="s" r="J275" s="7">
-        <v>241</v>
-      </c>
+      <c r="E275" s="7"/>
+      <c r="F275" s="7"/>
+      <c r="G275" s="8"/>
+      <c r="H275" s="8"/>
+      <c r="I275" s="7"/>
+      <c r="J275" s="7"/>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c r="M275" s="7"/>
@@ -9893,7 +9893,7 @@
         <v>13</v>
       </c>
       <c r="B276" s="7">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c t="s" r="C276" s="7">
         <v>14</v>
@@ -9909,13 +9909,13 @@
         <v>155</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>70</v>
+        <v>309</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>267</v>
+        <v>145</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9926,7 +9926,7 @@
         <v>13</v>
       </c>
       <c r="B277" s="7">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c t="s" r="C277" s="7">
         <v>14</v>
@@ -9939,16 +9939,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>70</v>
+        <v>309</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>155</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>103</v>
+        <v>325</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9959,7 +9959,7 @@
         <v>13</v>
       </c>
       <c r="B278" s="7">
-        <v>878</v>
+        <v>715</v>
       </c>
       <c t="s" r="C278" s="7">
         <v>14</v>
@@ -9975,29 +9975,47 @@
         <v>155</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>326</v>
+        <v>267</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c r="M278" s="7"/>
     </row>
     <row r="279" ht="14.25" customHeight="1">
-      <c r="A279" s="6"/>
-      <c r="B279" s="7"/>
-      <c r="C279" s="7"/>
+      <c t="s" r="A279" s="6">
+        <v>13</v>
+      </c>
+      <c r="B279" s="7">
+        <v>714</v>
+      </c>
+      <c t="s" r="C279" s="7">
+        <v>14</v>
+      </c>
       <c r="D279" s="7"/>
-      <c r="E279" s="7"/>
-      <c r="F279" s="7"/>
-      <c r="G279" s="8"/>
-      <c r="H279" s="8"/>
-      <c r="I279" s="7"/>
-      <c r="J279" s="7"/>
+      <c t="s" r="E279" s="7">
+        <v>324</v>
+      </c>
+      <c r="F279" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G279" s="8">
+        <v>70</v>
+      </c>
+      <c t="s" r="H279" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="I279" s="7">
+        <v>103</v>
+      </c>
+      <c t="s" r="J279" s="7">
+        <v>196</v>
+      </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c r="M279" s="7"/>
@@ -10007,63 +10025,45 @@
         <v>13</v>
       </c>
       <c r="B280" s="7">
-        <v>350</v>
+        <v>878</v>
       </c>
       <c t="s" r="C280" s="7">
         <v>14</v>
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>62</v>
+        <v>326</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c r="M280" s="7"/>
     </row>
     <row r="281" ht="14.25" customHeight="1">
-      <c t="s" r="A281" s="6">
-        <v>13</v>
-      </c>
-      <c r="B281" s="7">
-        <v>351</v>
-      </c>
-      <c t="s" r="C281" s="7">
-        <v>14</v>
-      </c>
+      <c r="A281" s="6"/>
+      <c r="B281" s="7"/>
+      <c r="C281" s="7"/>
       <c r="D281" s="7"/>
-      <c t="s" r="E281" s="7">
-        <v>327</v>
-      </c>
-      <c r="F281" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G281" s="8">
-        <v>168</v>
-      </c>
-      <c t="s" r="H281" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I281" s="7">
-        <v>48</v>
-      </c>
-      <c t="s" r="J281" s="7">
-        <v>121</v>
-      </c>
+      <c r="E281" s="7"/>
+      <c r="F281" s="7"/>
+      <c r="G281" s="8"/>
+      <c r="H281" s="8"/>
+      <c r="I281" s="7"/>
+      <c r="J281" s="7"/>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c r="M281" s="7"/>
@@ -10073,7 +10073,7 @@
         <v>13</v>
       </c>
       <c r="B282" s="7">
-        <v>1813</v>
+        <v>302</v>
       </c>
       <c t="s" r="C282" s="7">
         <v>14</v>
@@ -10089,13 +10089,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>43</v>
+        <v>245</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10106,7 +10106,7 @@
         <v>13</v>
       </c>
       <c r="B283" s="7">
-        <v>1814</v>
+        <v>301</v>
       </c>
       <c t="s" r="C283" s="7">
         <v>14</v>
@@ -10119,16 +10119,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>79</v>
+        <v>271</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10139,7 +10139,7 @@
         <v>13</v>
       </c>
       <c r="B284" s="7">
-        <v>1831</v>
+        <v>1813</v>
       </c>
       <c t="s" r="C284" s="7">
         <v>14</v>
@@ -10155,13 +10155,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>252</v>
+        <v>99</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10172,7 +10172,7 @@
         <v>13</v>
       </c>
       <c r="B285" s="7">
-        <v>1832</v>
+        <v>1814</v>
       </c>
       <c t="s" r="C285" s="7">
         <v>14</v>
@@ -10185,32 +10185,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>252</v>
+        <v>99</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>328</v>
+        <v>149</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c r="M285" s="7"/>
     </row>
     <row r="286" ht="14.25" customHeight="1">
-      <c r="A286" s="6"/>
-      <c r="B286" s="7"/>
-      <c r="C286" s="7"/>
+      <c t="s" r="A286" s="6">
+        <v>13</v>
+      </c>
+      <c r="B286" s="7">
+        <v>1831</v>
+      </c>
+      <c t="s" r="C286" s="7">
+        <v>14</v>
+      </c>
       <c r="D286" s="7"/>
-      <c r="E286" s="7"/>
-      <c r="F286" s="7"/>
-      <c r="G286" s="8"/>
-      <c r="H286" s="8"/>
-      <c r="I286" s="7"/>
-      <c r="J286" s="7"/>
+      <c t="s" r="E286" s="7">
+        <v>327</v>
+      </c>
+      <c r="F286" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G286" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H286" s="8">
+        <v>252</v>
+      </c>
+      <c t="s" r="I286" s="7">
+        <v>44</v>
+      </c>
+      <c t="s" r="J286" s="7">
+        <v>248</v>
+      </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c r="M286" s="7"/>
@@ -10220,63 +10238,45 @@
         <v>13</v>
       </c>
       <c r="B287" s="7">
-        <v>977</v>
+        <v>1832</v>
       </c>
       <c t="s" r="C287" s="7">
         <v>14</v>
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F287" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>108</v>
+        <v>252</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>166</v>
+        <v>59</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>180</v>
+        <v>328</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c r="M287" s="7"/>
     </row>
     <row r="288" ht="14.25" customHeight="1">
-      <c t="s" r="A288" s="6">
-        <v>13</v>
-      </c>
-      <c r="B288" s="7">
-        <v>334</v>
-      </c>
-      <c t="s" r="C288" s="7">
-        <v>14</v>
-      </c>
+      <c r="A288" s="6"/>
+      <c r="B288" s="7"/>
+      <c r="C288" s="7"/>
       <c r="D288" s="7"/>
-      <c t="s" r="E288" s="7">
-        <v>329</v>
-      </c>
-      <c r="F288" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G288" s="8">
-        <v>70</v>
-      </c>
-      <c t="s" r="H288" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I288" s="7">
-        <v>27</v>
-      </c>
-      <c t="s" r="J288" s="7">
-        <v>76</v>
-      </c>
+      <c r="E288" s="7"/>
+      <c r="F288" s="7"/>
+      <c r="G288" s="8"/>
+      <c r="H288" s="8"/>
+      <c r="I288" s="7"/>
+      <c r="J288" s="7"/>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c r="M288" s="7"/>
@@ -10286,7 +10286,7 @@
         <v>13</v>
       </c>
       <c r="B289" s="7">
-        <v>374</v>
+        <v>977</v>
       </c>
       <c t="s" r="C289" s="7">
         <v>14</v>
@@ -10299,16 +10299,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>284</v>
+        <v>166</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10319,7 +10319,7 @@
         <v>13</v>
       </c>
       <c r="B290" s="7">
-        <v>375</v>
+        <v>334</v>
       </c>
       <c t="s" r="C290" s="7">
         <v>14</v>
@@ -10332,16 +10332,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>301</v>
+        <v>27</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10352,7 +10352,7 @@
         <v>13</v>
       </c>
       <c r="B291" s="7">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c t="s" r="C291" s="7">
         <v>14</v>
@@ -10368,13 +10368,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10385,7 +10385,7 @@
         <v>13</v>
       </c>
       <c r="B292" s="7">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c t="s" r="C292" s="7">
         <v>14</v>
@@ -10398,32 +10398,50 @@
         <v>320</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>196</v>
+        <v>277</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c r="M292" s="7"/>
     </row>
     <row r="293" ht="14.25" customHeight="1">
-      <c r="A293" s="6"/>
-      <c r="B293" s="7"/>
-      <c r="C293" s="7"/>
+      <c t="s" r="A293" s="6">
+        <v>13</v>
+      </c>
+      <c r="B293" s="7">
+        <v>384</v>
+      </c>
+      <c t="s" r="C293" s="7">
+        <v>14</v>
+      </c>
       <c r="D293" s="7"/>
-      <c r="E293" s="7"/>
-      <c r="F293" s="7"/>
-      <c r="G293" s="8"/>
-      <c r="H293" s="8"/>
-      <c r="I293" s="7"/>
-      <c r="J293" s="7"/>
+      <c t="s" r="E293" s="7">
+        <v>329</v>
+      </c>
+      <c r="F293" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G293" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H293" s="8">
+        <v>82</v>
+      </c>
+      <c t="s" r="I293" s="7">
+        <v>115</v>
+      </c>
+      <c t="s" r="J293" s="7">
+        <v>151</v>
+      </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c r="M293" s="7"/>
@@ -10433,63 +10451,45 @@
         <v>13</v>
       </c>
       <c r="B294" s="7">
-        <v>901</v>
+        <v>385</v>
       </c>
       <c t="s" r="C294" s="7">
         <v>14</v>
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F294" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>305</v>
+        <v>29</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>52</v>
+        <v>188</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c r="M294" s="7"/>
     </row>
     <row r="295" ht="15" customHeight="1">
-      <c t="s" r="A295" s="6">
-        <v>13</v>
-      </c>
-      <c r="B295" s="7">
-        <v>902</v>
-      </c>
-      <c t="s" r="C295" s="7">
-        <v>14</v>
-      </c>
+      <c r="A295" s="6"/>
+      <c r="B295" s="7"/>
+      <c r="C295" s="7"/>
       <c r="D295" s="7"/>
-      <c t="s" r="E295" s="7">
-        <v>331</v>
-      </c>
-      <c r="F295" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G295" s="8">
-        <v>305</v>
-      </c>
-      <c t="s" r="H295" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I295" s="7">
-        <v>54</v>
-      </c>
-      <c t="s" r="J295" s="7">
-        <v>55</v>
-      </c>
+      <c r="E295" s="7"/>
+      <c r="F295" s="7"/>
+      <c r="G295" s="8"/>
+      <c r="H295" s="8"/>
+      <c r="I295" s="7"/>
+      <c r="J295" s="7"/>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c r="M295" s="7"/>
@@ -10499,7 +10499,7 @@
         <v>13</v>
       </c>
       <c r="B296" s="7">
-        <v>151</v>
+        <v>463</v>
       </c>
       <c t="s" r="C296" s="7">
         <v>14</v>
@@ -10515,13 +10515,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>29</v>
+        <v>309</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>285</v>
+        <v>156</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>140</v>
+        <v>229</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10532,7 +10532,7 @@
         <v>13</v>
       </c>
       <c r="B297" s="7">
-        <v>648</v>
+        <v>464</v>
       </c>
       <c t="s" r="C297" s="7">
         <v>14</v>
@@ -10545,16 +10545,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>29</v>
+        <v>309</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>287</v>
+        <v>52</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>130</v>
+        <v>283</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10565,7 +10565,7 @@
         <v>13</v>
       </c>
       <c r="B298" s="7">
-        <v>647</v>
+        <v>439</v>
       </c>
       <c t="s" r="C298" s="7">
         <v>14</v>
@@ -10578,32 +10578,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>244</v>
+        <v>150</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c r="M298" s="7"/>
     </row>
     <row r="299" ht="14.25" customHeight="1">
-      <c r="A299" s="6"/>
-      <c r="B299" s="7"/>
-      <c r="C299" s="7"/>
+      <c t="s" r="A299" s="6">
+        <v>13</v>
+      </c>
+      <c r="B299" s="7">
+        <v>438</v>
+      </c>
+      <c t="s" r="C299" s="7">
+        <v>14</v>
+      </c>
       <c r="D299" s="7"/>
-      <c r="E299" s="7"/>
-      <c r="F299" s="7"/>
-      <c r="G299" s="8"/>
-      <c r="H299" s="8"/>
-      <c r="I299" s="7"/>
-      <c r="J299" s="7"/>
+      <c t="s" r="E299" s="7">
+        <v>331</v>
+      </c>
+      <c r="F299" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G299" s="8">
+        <v>82</v>
+      </c>
+      <c t="s" r="H299" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I299" s="7">
+        <v>151</v>
+      </c>
+      <c t="s" r="J299" s="7">
+        <v>35</v>
+      </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c r="M299" s="7"/>
@@ -10613,63 +10631,45 @@
         <v>13</v>
       </c>
       <c r="B300" s="7">
-        <v>823</v>
+        <v>161</v>
       </c>
       <c t="s" r="C300" s="7">
         <v>14</v>
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>284</v>
+        <v>73</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c r="M300" s="7"/>
     </row>
     <row r="301" ht="14.25" customHeight="1">
-      <c t="s" r="A301" s="6">
-        <v>13</v>
-      </c>
-      <c r="B301" s="7">
-        <v>278</v>
-      </c>
-      <c t="s" r="C301" s="7">
-        <v>14</v>
-      </c>
+      <c r="A301" s="6"/>
+      <c r="B301" s="7"/>
+      <c r="C301" s="7"/>
       <c r="D301" s="7"/>
-      <c t="s" r="E301" s="7">
-        <v>332</v>
-      </c>
-      <c r="F301" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G301" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H301" s="8">
-        <v>120</v>
-      </c>
-      <c t="s" r="I301" s="7">
-        <v>333</v>
-      </c>
-      <c t="s" r="J301" s="7">
-        <v>21</v>
-      </c>
+      <c r="E301" s="7"/>
+      <c r="F301" s="7"/>
+      <c r="G301" s="8"/>
+      <c r="H301" s="8"/>
+      <c r="I301" s="7"/>
+      <c r="J301" s="7"/>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c r="M301" s="7"/>
@@ -10679,7 +10679,7 @@
         <v>13</v>
       </c>
       <c r="B302" s="7">
-        <v>279</v>
+        <v>823</v>
       </c>
       <c t="s" r="C302" s="7">
         <v>14</v>
@@ -10692,16 +10692,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>248</v>
+        <v>287</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10712,7 +10712,7 @@
         <v>13</v>
       </c>
       <c r="B303" s="7">
-        <v>644</v>
+        <v>278</v>
       </c>
       <c t="s" r="C303" s="7">
         <v>14</v>
@@ -10728,13 +10728,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>287</v>
+        <v>333</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10745,7 +10745,7 @@
         <v>13</v>
       </c>
       <c r="B304" s="7">
-        <v>645</v>
+        <v>279</v>
       </c>
       <c t="s" r="C304" s="7">
         <v>14</v>
@@ -10758,32 +10758,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>334</v>
+        <v>44</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>335</v>
+        <v>248</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c r="M304" s="7"/>
     </row>
     <row r="305" ht="15" customHeight="1">
-      <c r="A305" s="6"/>
-      <c r="B305" s="7"/>
-      <c r="C305" s="7"/>
+      <c t="s" r="A305" s="6">
+        <v>13</v>
+      </c>
+      <c r="B305" s="7">
+        <v>644</v>
+      </c>
+      <c t="s" r="C305" s="7">
+        <v>14</v>
+      </c>
       <c r="D305" s="7"/>
-      <c r="E305" s="7"/>
-      <c r="F305" s="7"/>
-      <c r="G305" s="8"/>
-      <c r="H305" s="8"/>
-      <c r="I305" s="7"/>
-      <c r="J305" s="7"/>
+      <c t="s" r="E305" s="7">
+        <v>332</v>
+      </c>
+      <c r="F305" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G305" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H305" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="I305" s="7">
+        <v>269</v>
+      </c>
+      <c t="s" r="J305" s="7">
+        <v>193</v>
+      </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c r="M305" s="7"/>
@@ -10793,63 +10811,45 @@
         <v>13</v>
       </c>
       <c r="B306" s="7">
-        <v>321</v>
+        <v>645</v>
       </c>
       <c t="s" r="C306" s="7">
         <v>14</v>
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F306" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>88</v>
+        <v>334</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c r="M306" s="7"/>
     </row>
     <row r="307" ht="14.25" customHeight="1">
-      <c t="s" r="A307" s="6">
-        <v>13</v>
-      </c>
-      <c r="B307" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="C307" s="7">
-        <v>14</v>
-      </c>
+      <c r="A307" s="6"/>
+      <c r="B307" s="7"/>
+      <c r="C307" s="7"/>
       <c r="D307" s="7"/>
-      <c t="s" r="E307" s="7">
-        <v>336</v>
-      </c>
-      <c r="F307" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G307" s="8">
-        <v>70</v>
-      </c>
-      <c t="s" r="H307" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I307" s="7">
-        <v>136</v>
-      </c>
-      <c t="s" r="J307" s="7">
-        <v>113</v>
-      </c>
+      <c r="E307" s="7"/>
+      <c r="F307" s="7"/>
+      <c r="G307" s="8"/>
+      <c r="H307" s="8"/>
+      <c r="I307" s="7"/>
+      <c r="J307" s="7"/>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c r="M307" s="7"/>
@@ -10859,7 +10859,7 @@
         <v>13</v>
       </c>
       <c r="B308" s="7">
-        <v>136</v>
+        <v>321</v>
       </c>
       <c t="s" r="C308" s="7">
         <v>14</v>
@@ -10875,13 +10875,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>267</v>
+        <v>337</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10892,7 +10892,7 @@
         <v>13</v>
       </c>
       <c r="B309" s="7">
-        <v>147</v>
+        <v>330</v>
       </c>
       <c t="s" r="C309" s="7">
         <v>14</v>
@@ -10905,16 +10905,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>292</v>
+        <v>136</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>238</v>
+        <v>113</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10925,7 +10925,7 @@
         <v>13</v>
       </c>
       <c r="B310" s="7">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c t="s" r="C310" s="7">
         <v>14</v>
@@ -10944,26 +10944,44 @@
         <v>40</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>338</v>
+        <v>209</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>176</v>
+        <v>267</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c r="M310" s="7"/>
     </row>
     <row r="311" ht="14.25" customHeight="1">
-      <c r="A311" s="6"/>
-      <c r="B311" s="7"/>
-      <c r="C311" s="7"/>
+      <c t="s" r="A311" s="6">
+        <v>13</v>
+      </c>
+      <c r="B311" s="7">
+        <v>147</v>
+      </c>
+      <c t="s" r="C311" s="7">
+        <v>14</v>
+      </c>
       <c r="D311" s="7"/>
-      <c r="E311" s="7"/>
-      <c r="F311" s="7"/>
-      <c r="G311" s="8"/>
-      <c r="H311" s="8"/>
-      <c r="I311" s="7"/>
-      <c r="J311" s="7"/>
+      <c t="s" r="E311" s="7">
+        <v>336</v>
+      </c>
+      <c r="F311" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G311" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H311" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I311" s="7">
+        <v>293</v>
+      </c>
+      <c t="s" r="J311" s="7">
+        <v>238</v>
+      </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c r="M311" s="7"/>
@@ -10973,63 +10991,45 @@
         <v>13</v>
       </c>
       <c r="B312" s="7">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c t="s" r="C312" s="7">
         <v>14</v>
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F312" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
         <v>29</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>38</v>
+        <v>338</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c r="M312" s="7"/>
     </row>
     <row r="313" ht="14.25" customHeight="1">
-      <c t="s" r="A313" s="6">
-        <v>13</v>
-      </c>
-      <c r="B313" s="7">
-        <v>261</v>
-      </c>
-      <c t="s" r="C313" s="7">
-        <v>14</v>
-      </c>
+      <c r="A313" s="6"/>
+      <c r="B313" s="7"/>
+      <c r="C313" s="7"/>
       <c r="D313" s="7"/>
-      <c t="s" r="E313" s="7">
-        <v>339</v>
-      </c>
-      <c r="F313" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G313" s="8">
-        <v>226</v>
-      </c>
-      <c t="s" r="H313" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I313" s="7">
-        <v>279</v>
-      </c>
-      <c t="s" r="J313" s="7">
-        <v>89</v>
-      </c>
+      <c r="E313" s="7"/>
+      <c r="F313" s="7"/>
+      <c r="G313" s="8"/>
+      <c r="H313" s="8"/>
+      <c r="I313" s="7"/>
+      <c r="J313" s="7"/>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c r="M313" s="7"/>
@@ -11039,7 +11039,7 @@
         <v>13</v>
       </c>
       <c r="B314" s="7">
-        <v>1602</v>
+        <v>260</v>
       </c>
       <c t="s" r="C314" s="7">
         <v>14</v>
@@ -11055,29 +11055,47 @@
         <v>29</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>17</v>
+        <v>226</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>294</v>
+        <v>154</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c r="M314" s="7"/>
     </row>
     <row r="315" ht="15" customHeight="1">
-      <c r="A315" s="6"/>
-      <c r="B315" s="7"/>
-      <c r="C315" s="7"/>
+      <c t="s" r="A315" s="6">
+        <v>13</v>
+      </c>
+      <c r="B315" s="7">
+        <v>261</v>
+      </c>
+      <c t="s" r="C315" s="7">
+        <v>14</v>
+      </c>
       <c r="D315" s="7"/>
-      <c r="E315" s="7"/>
-      <c r="F315" s="7"/>
-      <c r="G315" s="8"/>
-      <c r="H315" s="8"/>
-      <c r="I315" s="7"/>
-      <c r="J315" s="7"/>
+      <c t="s" r="E315" s="7">
+        <v>339</v>
+      </c>
+      <c r="F315" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G315" s="8">
+        <v>226</v>
+      </c>
+      <c t="s" r="H315" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I315" s="7">
+        <v>282</v>
+      </c>
+      <c t="s" r="J315" s="7">
+        <v>89</v>
+      </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c r="M315" s="7"/>
@@ -11087,63 +11105,45 @@
         <v>13</v>
       </c>
       <c r="B316" s="7">
-        <v>335</v>
+        <v>1602</v>
       </c>
       <c t="s" r="C316" s="7">
         <v>14</v>
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F316" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G316" s="8">
         <v>29</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>266</v>
+        <v>76</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>65</v>
+        <v>297</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c r="M316" s="7"/>
     </row>
     <row r="317" ht="14.25" customHeight="1">
-      <c t="s" r="A317" s="6">
-        <v>13</v>
-      </c>
-      <c r="B317" s="7">
-        <v>766</v>
-      </c>
-      <c t="s" r="C317" s="7">
-        <v>14</v>
-      </c>
+      <c r="A317" s="6"/>
+      <c r="B317" s="7"/>
+      <c r="C317" s="7"/>
       <c r="D317" s="7"/>
-      <c t="s" r="E317" s="7">
-        <v>340</v>
-      </c>
-      <c r="F317" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G317" s="8">
-        <v>70</v>
-      </c>
-      <c t="s" r="H317" s="8">
-        <v>120</v>
-      </c>
-      <c t="s" r="I317" s="7">
-        <v>52</v>
-      </c>
-      <c t="s" r="J317" s="7">
-        <v>210</v>
-      </c>
+      <c r="E317" s="7"/>
+      <c r="F317" s="7"/>
+      <c r="G317" s="8"/>
+      <c r="H317" s="8"/>
+      <c r="I317" s="7"/>
+      <c r="J317" s="7"/>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c r="M317" s="7"/>
@@ -11153,7 +11153,7 @@
         <v>13</v>
       </c>
       <c r="B318" s="7">
-        <v>767</v>
+        <v>335</v>
       </c>
       <c t="s" r="C318" s="7">
         <v>14</v>
@@ -11166,16 +11166,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>70</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>151</v>
+        <v>65</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11186,7 +11186,7 @@
         <v>13</v>
       </c>
       <c r="B319" s="7">
-        <v>976</v>
+        <v>766</v>
       </c>
       <c t="s" r="C319" s="7">
         <v>14</v>
@@ -11202,29 +11202,47 @@
         <v>70</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>220</v>
+        <v>52</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>341</v>
+        <v>210</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c r="M319" s="7"/>
     </row>
     <row r="320" ht="15" customHeight="1">
-      <c r="A320" s="6"/>
-      <c r="B320" s="7"/>
-      <c r="C320" s="7"/>
+      <c t="s" r="A320" s="6">
+        <v>13</v>
+      </c>
+      <c r="B320" s="7">
+        <v>767</v>
+      </c>
+      <c t="s" r="C320" s="7">
+        <v>14</v>
+      </c>
       <c r="D320" s="7"/>
-      <c r="E320" s="7"/>
-      <c r="F320" s="7"/>
-      <c r="G320" s="8"/>
-      <c r="H320" s="8"/>
-      <c r="I320" s="7"/>
-      <c r="J320" s="7"/>
+      <c t="s" r="E320" s="7">
+        <v>340</v>
+      </c>
+      <c r="F320" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G320" s="8">
+        <v>120</v>
+      </c>
+      <c t="s" r="H320" s="8">
+        <v>70</v>
+      </c>
+      <c t="s" r="I320" s="7">
+        <v>94</v>
+      </c>
+      <c t="s" r="J320" s="7">
+        <v>151</v>
+      </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c r="M320" s="7"/>
@@ -11234,63 +11252,45 @@
         <v>13</v>
       </c>
       <c r="B321" s="7">
-        <v>813</v>
+        <v>976</v>
       </c>
       <c t="s" r="C321" s="7">
         <v>14</v>
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F321" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>89</v>
+        <v>341</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c r="M321" s="7"/>
     </row>
     <row r="322" ht="14.25" customHeight="1">
-      <c t="s" r="A322" s="6">
-        <v>13</v>
-      </c>
-      <c r="B322" s="7">
-        <v>970</v>
-      </c>
-      <c t="s" r="C322" s="7">
-        <v>14</v>
-      </c>
+      <c r="A322" s="6"/>
+      <c r="B322" s="7"/>
+      <c r="C322" s="7"/>
       <c r="D322" s="7"/>
-      <c t="s" r="E322" s="7">
-        <v>342</v>
-      </c>
-      <c r="F322" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G322" s="8">
-        <v>112</v>
-      </c>
-      <c t="s" r="H322" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="I322" s="7">
-        <v>202</v>
-      </c>
-      <c t="s" r="J322" s="7">
-        <v>223</v>
-      </c>
+      <c r="E322" s="7"/>
+      <c r="F322" s="7"/>
+      <c r="G322" s="8"/>
+      <c r="H322" s="8"/>
+      <c r="I322" s="7"/>
+      <c r="J322" s="7"/>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c r="M322" s="7"/>
@@ -11300,7 +11300,7 @@
         <v>13</v>
       </c>
       <c r="B323" s="7">
-        <v>8510</v>
+        <v>813</v>
       </c>
       <c t="s" r="C323" s="7">
         <v>14</v>
@@ -11313,16 +11313,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>79</v>
+        <v>214</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11333,7 +11333,7 @@
         <v>13</v>
       </c>
       <c r="B324" s="7">
-        <v>8511</v>
+        <v>970</v>
       </c>
       <c t="s" r="C324" s="7">
         <v>14</v>
@@ -11346,32 +11346,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>155</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c r="M324" s="7"/>
     </row>
     <row r="325" ht="15" customHeight="1">
-      <c r="A325" s="6"/>
-      <c r="B325" s="7"/>
-      <c r="C325" s="7"/>
+      <c t="s" r="A325" s="6">
+        <v>13</v>
+      </c>
+      <c r="B325" s="7">
+        <v>8510</v>
+      </c>
+      <c t="s" r="C325" s="7">
+        <v>14</v>
+      </c>
       <c r="D325" s="7"/>
-      <c r="E325" s="7"/>
-      <c r="F325" s="7"/>
-      <c r="G325" s="8"/>
-      <c r="H325" s="8"/>
-      <c r="I325" s="7"/>
-      <c r="J325" s="7"/>
+      <c t="s" r="E325" s="7">
+        <v>342</v>
+      </c>
+      <c r="F325" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G325" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="H325" s="8">
+        <v>134</v>
+      </c>
+      <c t="s" r="I325" s="7">
+        <v>79</v>
+      </c>
+      <c t="s" r="J325" s="7">
+        <v>128</v>
+      </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c r="M325" s="7"/>
@@ -11381,63 +11399,45 @@
         <v>13</v>
       </c>
       <c r="B326" s="7">
-        <v>801</v>
+        <v>8511</v>
       </c>
       <c t="s" r="C326" s="7">
         <v>14</v>
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F326" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>305</v>
+        <v>155</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>344</v>
+        <v>220</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c r="M326" s="7"/>
     </row>
     <row r="327" ht="14.25" customHeight="1">
-      <c t="s" r="A327" s="6">
-        <v>13</v>
-      </c>
-      <c r="B327" s="7">
-        <v>802</v>
-      </c>
-      <c t="s" r="C327" s="7">
-        <v>14</v>
-      </c>
+      <c r="A327" s="6"/>
+      <c r="B327" s="7"/>
+      <c r="C327" s="7"/>
       <c r="D327" s="7"/>
-      <c t="s" r="E327" s="7">
-        <v>343</v>
-      </c>
-      <c r="F327" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G327" s="8">
-        <v>305</v>
-      </c>
-      <c t="s" r="H327" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I327" s="7">
-        <v>113</v>
-      </c>
-      <c t="s" r="J327" s="7">
-        <v>52</v>
-      </c>
+      <c r="E327" s="7"/>
+      <c r="F327" s="7"/>
+      <c r="G327" s="8"/>
+      <c r="H327" s="8"/>
+      <c r="I327" s="7"/>
+      <c r="J327" s="7"/>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c r="M327" s="7"/>
@@ -11447,7 +11447,7 @@
         <v>13</v>
       </c>
       <c r="B328" s="7">
-        <v>640</v>
+        <v>801</v>
       </c>
       <c t="s" r="C328" s="7">
         <v>14</v>
@@ -11463,13 +11463,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>155</v>
+        <v>276</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>103</v>
+        <v>344</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11480,7 +11480,7 @@
         <v>13</v>
       </c>
       <c r="B329" s="7">
-        <v>639</v>
+        <v>802</v>
       </c>
       <c t="s" r="C329" s="7">
         <v>14</v>
@@ -11493,32 +11493,50 @@
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>155</v>
+        <v>276</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>345</v>
+        <v>113</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>346</v>
+        <v>52</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c r="M329" s="7"/>
     </row>
     <row r="330" ht="15" customHeight="1">
-      <c r="A330" s="6"/>
-      <c r="B330" s="7"/>
-      <c r="C330" s="7"/>
+      <c t="s" r="A330" s="6">
+        <v>13</v>
+      </c>
+      <c r="B330" s="7">
+        <v>640</v>
+      </c>
+      <c t="s" r="C330" s="7">
+        <v>14</v>
+      </c>
       <c r="D330" s="7"/>
-      <c r="E330" s="7"/>
-      <c r="F330" s="7"/>
-      <c r="G330" s="8"/>
-      <c r="H330" s="8"/>
-      <c r="I330" s="7"/>
-      <c r="J330" s="7"/>
+      <c t="s" r="E330" s="7">
+        <v>343</v>
+      </c>
+      <c r="F330" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G330" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H330" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="I330" s="7">
+        <v>283</v>
+      </c>
+      <c t="s" r="J330" s="7">
+        <v>103</v>
+      </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c r="M330" s="7"/>
@@ -11528,63 +11546,45 @@
         <v>13</v>
       </c>
       <c r="B331" s="7">
-        <v>501</v>
+        <v>639</v>
       </c>
       <c t="s" r="C331" s="7">
         <v>14</v>
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F331" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>135</v>
+        <v>346</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c r="M331" s="7"/>
     </row>
     <row r="332" ht="14.25" customHeight="1">
-      <c t="s" r="A332" s="6">
-        <v>13</v>
-      </c>
-      <c r="B332" s="7">
-        <v>514</v>
-      </c>
-      <c t="s" r="C332" s="7">
-        <v>14</v>
-      </c>
+      <c r="A332" s="6"/>
+      <c r="B332" s="7"/>
+      <c r="C332" s="7"/>
       <c r="D332" s="7"/>
-      <c t="s" r="E332" s="7">
-        <v>347</v>
-      </c>
-      <c r="F332" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G332" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="H332" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I332" s="7">
-        <v>147</v>
-      </c>
-      <c t="s" r="J332" s="7">
-        <v>88</v>
-      </c>
+      <c r="E332" s="7"/>
+      <c r="F332" s="7"/>
+      <c r="G332" s="8"/>
+      <c r="H332" s="8"/>
+      <c r="I332" s="7"/>
+      <c r="J332" s="7"/>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c r="M332" s="7"/>
@@ -11594,7 +11594,7 @@
         <v>13</v>
       </c>
       <c r="B333" s="7">
-        <v>563</v>
+        <v>501</v>
       </c>
       <c t="s" r="C333" s="7">
         <v>14</v>
@@ -11610,13 +11610,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>64</v>
+        <v>348</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>299</v>
+        <v>135</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11627,7 +11627,7 @@
         <v>13</v>
       </c>
       <c r="B334" s="7">
-        <v>564</v>
+        <v>514</v>
       </c>
       <c t="s" r="C334" s="7">
         <v>14</v>
@@ -11640,16 +11640,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>192</v>
+        <v>147</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11660,7 +11660,7 @@
         <v>13</v>
       </c>
       <c r="B335" s="7">
-        <v>948</v>
+        <v>563</v>
       </c>
       <c t="s" r="C335" s="7">
         <v>14</v>
@@ -11676,13 +11676,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>127</v>
+        <v>302</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11693,7 +11693,7 @@
         <v>13</v>
       </c>
       <c r="B336" s="7">
-        <v>949</v>
+        <v>564</v>
       </c>
       <c t="s" r="C336" s="7">
         <v>14</v>
@@ -11706,32 +11706,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>227</v>
+        <v>65</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c r="M336" s="7"/>
     </row>
     <row r="337" ht="14.25" customHeight="1">
-      <c r="A337" s="6"/>
-      <c r="B337" s="7"/>
-      <c r="C337" s="7"/>
+      <c t="s" r="A337" s="6">
+        <v>13</v>
+      </c>
+      <c r="B337" s="7">
+        <v>948</v>
+      </c>
+      <c t="s" r="C337" s="7">
+        <v>14</v>
+      </c>
       <c r="D337" s="7"/>
-      <c r="E337" s="7"/>
-      <c r="F337" s="7"/>
-      <c r="G337" s="8"/>
-      <c r="H337" s="8"/>
-      <c r="I337" s="7"/>
-      <c r="J337" s="7"/>
+      <c t="s" r="E337" s="7">
+        <v>347</v>
+      </c>
+      <c r="F337" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G337" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H337" s="8">
+        <v>134</v>
+      </c>
+      <c t="s" r="I337" s="7">
+        <v>78</v>
+      </c>
+      <c t="s" r="J337" s="7">
+        <v>127</v>
+      </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c r="M337" s="7"/>
@@ -11741,63 +11759,45 @@
         <v>13</v>
       </c>
       <c r="B338" s="7">
-        <v>382</v>
+        <v>949</v>
       </c>
       <c t="s" r="C338" s="7">
         <v>14</v>
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F338" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>296</v>
+        <v>227</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c r="M338" s="7"/>
     </row>
     <row r="339" ht="14.25" customHeight="1">
-      <c t="s" r="A339" s="6">
-        <v>13</v>
-      </c>
-      <c r="B339" s="7">
-        <v>383</v>
-      </c>
-      <c t="s" r="C339" s="7">
-        <v>14</v>
-      </c>
+      <c r="A339" s="6"/>
+      <c r="B339" s="7"/>
+      <c r="C339" s="7"/>
       <c r="D339" s="7"/>
-      <c t="s" r="E339" s="7">
-        <v>349</v>
-      </c>
-      <c r="F339" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G339" s="8">
-        <v>82</v>
-      </c>
-      <c t="s" r="H339" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I339" s="7">
-        <v>344</v>
-      </c>
-      <c t="s" r="J339" s="7">
-        <v>172</v>
-      </c>
+      <c r="E339" s="7"/>
+      <c r="F339" s="7"/>
+      <c r="G339" s="8"/>
+      <c r="H339" s="8"/>
+      <c r="I339" s="7"/>
+      <c r="J339" s="7"/>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c r="M339" s="7"/>
@@ -11807,7 +11807,7 @@
         <v>13</v>
       </c>
       <c r="B340" s="7">
-        <v>325</v>
+        <v>382</v>
       </c>
       <c t="s" r="C340" s="7">
         <v>14</v>
@@ -11823,13 +11823,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>125</v>
+        <v>299</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11840,7 +11840,7 @@
         <v>13</v>
       </c>
       <c r="B341" s="7">
-        <v>978</v>
+        <v>383</v>
       </c>
       <c t="s" r="C341" s="7">
         <v>14</v>
@@ -11853,32 +11853,50 @@
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>151</v>
+        <v>344</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c r="M341" s="7"/>
     </row>
     <row r="342" ht="14.25" customHeight="1">
-      <c r="A342" s="6"/>
-      <c r="B342" s="7"/>
-      <c r="C342" s="7"/>
+      <c t="s" r="A342" s="6">
+        <v>13</v>
+      </c>
+      <c r="B342" s="7">
+        <v>325</v>
+      </c>
+      <c t="s" r="C342" s="7">
+        <v>14</v>
+      </c>
       <c r="D342" s="7"/>
-      <c r="E342" s="7"/>
-      <c r="F342" s="7"/>
-      <c r="G342" s="8"/>
-      <c r="H342" s="8"/>
-      <c r="I342" s="7"/>
-      <c r="J342" s="7"/>
+      <c t="s" r="E342" s="7">
+        <v>349</v>
+      </c>
+      <c r="F342" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G342" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H342" s="8">
+        <v>70</v>
+      </c>
+      <c t="s" r="I342" s="7">
+        <v>139</v>
+      </c>
+      <c t="s" r="J342" s="7">
+        <v>125</v>
+      </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c r="M342" s="7"/>
@@ -11888,63 +11906,45 @@
         <v>13</v>
       </c>
       <c r="B343" s="7">
-        <v>855</v>
+        <v>978</v>
       </c>
       <c t="s" r="C343" s="7">
         <v>14</v>
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F343" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>351</v>
+        <v>108</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>296</v>
+        <v>151</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>229</v>
+        <v>132</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c r="M343" s="7"/>
     </row>
     <row r="344" ht="14.25" customHeight="1">
-      <c t="s" r="A344" s="6">
-        <v>13</v>
-      </c>
-      <c r="B344" s="7">
-        <v>854</v>
-      </c>
-      <c t="s" r="C344" s="7">
-        <v>14</v>
-      </c>
+      <c r="A344" s="6"/>
+      <c r="B344" s="7"/>
+      <c r="C344" s="7"/>
       <c r="D344" s="7"/>
-      <c t="s" r="E344" s="7">
-        <v>350</v>
-      </c>
-      <c r="F344" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G344" s="8">
-        <v>351</v>
-      </c>
-      <c t="s" r="H344" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I344" s="7">
-        <v>78</v>
-      </c>
-      <c t="s" r="J344" s="7">
-        <v>80</v>
-      </c>
+      <c r="E344" s="7"/>
+      <c r="F344" s="7"/>
+      <c r="G344" s="8"/>
+      <c r="H344" s="8"/>
+      <c r="I344" s="7"/>
+      <c r="J344" s="7"/>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c r="M344" s="7"/>
@@ -11954,7 +11954,7 @@
         <v>13</v>
       </c>
       <c r="B345" s="7">
-        <v>352</v>
+        <v>855</v>
       </c>
       <c t="s" r="C345" s="7">
         <v>14</v>
@@ -11970,13 +11970,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>168</v>
+        <v>351</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>69</v>
+        <v>229</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -11987,7 +11987,7 @@
         <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>353</v>
+        <v>854</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
@@ -12000,32 +12000,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>168</v>
+        <v>351</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>303</v>
+        <v>80</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c r="M346" s="7"/>
     </row>
     <row r="347" ht="14.25" customHeight="1">
-      <c r="A347" s="6"/>
-      <c r="B347" s="7"/>
-      <c r="C347" s="7"/>
+      <c t="s" r="A347" s="6">
+        <v>13</v>
+      </c>
+      <c r="B347" s="7">
+        <v>352</v>
+      </c>
+      <c t="s" r="C347" s="7">
+        <v>14</v>
+      </c>
       <c r="D347" s="7"/>
-      <c r="E347" s="7"/>
-      <c r="F347" s="7"/>
-      <c r="G347" s="8"/>
-      <c r="H347" s="8"/>
-      <c r="I347" s="7"/>
-      <c r="J347" s="7"/>
+      <c t="s" r="E347" s="7">
+        <v>350</v>
+      </c>
+      <c r="F347" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G347" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H347" s="8">
+        <v>168</v>
+      </c>
+      <c t="s" r="I347" s="7">
+        <v>264</v>
+      </c>
+      <c t="s" r="J347" s="7">
+        <v>69</v>
+      </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c r="M347" s="7"/>
@@ -12035,63 +12053,45 @@
         <v>13</v>
       </c>
       <c r="B348" s="7">
-        <v>621</v>
+        <v>353</v>
       </c>
       <c t="s" r="C348" s="7">
         <v>14</v>
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F348" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>135</v>
+        <v>295</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c r="M348" s="7"/>
     </row>
     <row r="349" ht="14.25" customHeight="1">
-      <c t="s" r="A349" s="6">
-        <v>13</v>
-      </c>
-      <c r="B349" s="7">
-        <v>632</v>
-      </c>
-      <c t="s" r="C349" s="7">
-        <v>14</v>
-      </c>
+      <c r="A349" s="6"/>
+      <c r="B349" s="7"/>
+      <c r="C349" s="7"/>
       <c r="D349" s="7"/>
-      <c t="s" r="E349" s="7">
-        <v>352</v>
-      </c>
-      <c r="F349" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G349" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H349" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="I349" s="7">
-        <v>147</v>
-      </c>
-      <c t="s" r="J349" s="7">
-        <v>88</v>
-      </c>
+      <c r="E349" s="7"/>
+      <c r="F349" s="7"/>
+      <c r="G349" s="8"/>
+      <c r="H349" s="8"/>
+      <c r="I349" s="7"/>
+      <c r="J349" s="7"/>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c r="M349" s="7"/>
@@ -12101,7 +12101,7 @@
         <v>13</v>
       </c>
       <c r="B350" s="7">
-        <v>720</v>
+        <v>621</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>14</v>
@@ -12117,13 +12117,13 @@
         <v>155</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12134,7 +12134,7 @@
         <v>13</v>
       </c>
       <c r="B351" s="7">
-        <v>721</v>
+        <v>632</v>
       </c>
       <c t="s" r="C351" s="7">
         <v>14</v>
@@ -12147,16 +12147,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>155</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>266</v>
+        <v>147</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12167,7 +12167,7 @@
         <v>13</v>
       </c>
       <c r="B352" s="7">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c t="s" r="C352" s="7">
         <v>14</v>
@@ -12183,13 +12183,13 @@
         <v>155</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>309</v>
+        <v>120</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>137</v>
+        <v>51</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>247</v>
+        <v>76</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12200,7 +12200,7 @@
         <v>13</v>
       </c>
       <c r="B353" s="7">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c t="s" r="C353" s="7">
         <v>14</v>
@@ -12213,32 +12213,50 @@
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>309</v>
+        <v>120</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>155</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>158</v>
+        <v>266</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>285</v>
+        <v>100</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c r="M353" s="7"/>
     </row>
     <row r="354" ht="14.25" customHeight="1">
-      <c r="A354" s="6"/>
-      <c r="B354" s="7"/>
-      <c r="C354" s="7"/>
+      <c t="s" r="A354" s="6">
+        <v>13</v>
+      </c>
+      <c r="B354" s="7">
+        <v>703</v>
+      </c>
+      <c t="s" r="C354" s="7">
+        <v>14</v>
+      </c>
       <c r="D354" s="7"/>
-      <c r="E354" s="7"/>
-      <c r="F354" s="7"/>
-      <c r="G354" s="8"/>
-      <c r="H354" s="8"/>
-      <c r="I354" s="7"/>
-      <c r="J354" s="7"/>
+      <c t="s" r="E354" s="7">
+        <v>352</v>
+      </c>
+      <c r="F354" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G354" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="H354" s="8">
+        <v>309</v>
+      </c>
+      <c t="s" r="I354" s="7">
+        <v>137</v>
+      </c>
+      <c t="s" r="J354" s="7">
+        <v>247</v>
+      </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c r="M354" s="7"/>
@@ -12248,63 +12266,45 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>125</v>
+        <v>704</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>40</v>
+        <v>309</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c r="M355" s="7"/>
     </row>
     <row r="356" ht="14.25" customHeight="1">
-      <c t="s" r="A356" s="6">
-        <v>13</v>
-      </c>
-      <c r="B356" s="7">
-        <v>128</v>
-      </c>
-      <c t="s" r="C356" s="7">
-        <v>14</v>
-      </c>
+      <c r="A356" s="6"/>
+      <c r="B356" s="7"/>
+      <c r="C356" s="7"/>
       <c r="D356" s="7"/>
-      <c t="s" r="E356" s="7">
-        <v>353</v>
-      </c>
-      <c r="F356" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G356" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H356" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I356" s="7">
-        <v>145</v>
-      </c>
-      <c t="s" r="J356" s="7">
-        <v>294</v>
-      </c>
+      <c r="E356" s="7"/>
+      <c r="F356" s="7"/>
+      <c r="G356" s="8"/>
+      <c r="H356" s="8"/>
+      <c r="I356" s="7"/>
+      <c r="J356" s="7"/>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c r="M356" s="7"/>
@@ -12314,7 +12314,7 @@
         <v>13</v>
       </c>
       <c r="B357" s="7">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c t="s" r="C357" s="7">
         <v>14</v>
@@ -12333,10 +12333,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>79</v>
+        <v>292</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12347,7 +12347,7 @@
         <v>13</v>
       </c>
       <c r="B358" s="7">
-        <v>3948</v>
+        <v>128</v>
       </c>
       <c t="s" r="C358" s="7">
         <v>14</v>
@@ -12363,13 +12363,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>354</v>
+        <v>40</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>238</v>
+        <v>145</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>37</v>
+        <v>297</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12377,10 +12377,10 @@
     </row>
     <row r="359" ht="14.25" customHeight="1">
       <c t="s" r="A359" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B359" s="7">
-        <v>3949</v>
+        <v>137</v>
       </c>
       <c t="s" r="C359" s="7">
         <v>14</v>
@@ -12393,98 +12393,98 @@
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>354</v>
+        <v>40</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>205</v>
+        <v>65</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c r="M359" s="7"/>
     </row>
     <row r="360" ht="15" customHeight="1">
-      <c r="A360" s="6"/>
-      <c r="B360" s="7"/>
-      <c r="C360" s="7"/>
+      <c t="s" r="A360" s="6">
+        <v>13</v>
+      </c>
+      <c r="B360" s="7">
+        <v>3948</v>
+      </c>
+      <c t="s" r="C360" s="7">
+        <v>14</v>
+      </c>
       <c r="D360" s="7"/>
-      <c r="E360" s="7"/>
-      <c r="F360" s="7"/>
-      <c r="G360" s="8"/>
-      <c r="H360" s="8"/>
-      <c r="I360" s="7"/>
-      <c r="J360" s="7"/>
+      <c t="s" r="E360" s="7">
+        <v>353</v>
+      </c>
+      <c r="F360" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G360" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H360" s="8">
+        <v>354</v>
+      </c>
+      <c t="s" r="I360" s="7">
+        <v>238</v>
+      </c>
+      <c t="s" r="J360" s="7">
+        <v>37</v>
+      </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c r="M360" s="7"/>
     </row>
     <row r="361" ht="14.25" customHeight="1">
       <c t="s" r="A361" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B361" s="7">
-        <v>981</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F361" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>16</v>
+        <v>354</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>154</v>
+        <v>205</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c r="M361" s="7"/>
     </row>
     <row r="362" ht="14.25" customHeight="1">
-      <c t="s" r="A362" s="6">
-        <v>13</v>
-      </c>
-      <c r="B362" s="7">
-        <v>451</v>
-      </c>
-      <c t="s" r="C362" s="7">
-        <v>14</v>
-      </c>
+      <c r="A362" s="6"/>
+      <c r="B362" s="7"/>
+      <c r="C362" s="7"/>
       <c r="D362" s="7"/>
-      <c t="s" r="E362" s="7">
-        <v>355</v>
-      </c>
-      <c r="F362" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G362" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H362" s="8">
-        <v>70</v>
-      </c>
-      <c t="s" r="I362" s="7">
-        <v>325</v>
-      </c>
-      <c t="s" r="J362" s="7">
-        <v>333</v>
-      </c>
+      <c r="E362" s="7"/>
+      <c r="F362" s="7"/>
+      <c r="G362" s="8"/>
+      <c r="H362" s="8"/>
+      <c r="I362" s="7"/>
+      <c r="J362" s="7"/>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c r="M362" s="7"/>
@@ -12494,7 +12494,7 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>454</v>
+        <v>981</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
@@ -12507,16 +12507,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>32</v>
+        <v>154</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12527,7 +12527,7 @@
         <v>13</v>
       </c>
       <c r="B364" s="7">
-        <v>495</v>
+        <v>451</v>
       </c>
       <c t="s" r="C364" s="7">
         <v>14</v>
@@ -12543,13 +12543,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>45</v>
+        <v>325</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12560,7 +12560,7 @@
         <v>13</v>
       </c>
       <c r="B365" s="7">
-        <v>496</v>
+        <v>454</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
@@ -12573,32 +12573,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>160</v>
+        <v>68</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c r="M365" s="7"/>
     </row>
     <row r="366" ht="14.25" customHeight="1">
-      <c r="A366" s="6"/>
-      <c r="B366" s="7"/>
-      <c r="C366" s="7"/>
+      <c t="s" r="A366" s="6">
+        <v>13</v>
+      </c>
+      <c r="B366" s="7">
+        <v>495</v>
+      </c>
+      <c t="s" r="C366" s="7">
+        <v>14</v>
+      </c>
       <c r="D366" s="7"/>
-      <c r="E366" s="7"/>
-      <c r="F366" s="7"/>
-      <c r="G366" s="8"/>
-      <c r="H366" s="8"/>
-      <c r="I366" s="7"/>
-      <c r="J366" s="7"/>
+      <c t="s" r="E366" s="7">
+        <v>355</v>
+      </c>
+      <c r="F366" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G366" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H366" s="8">
+        <v>168</v>
+      </c>
+      <c t="s" r="I366" s="7">
+        <v>45</v>
+      </c>
+      <c t="s" r="J366" s="7">
+        <v>356</v>
+      </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c r="M366" s="7"/>
@@ -12608,63 +12626,45 @@
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>869</v>
+        <v>496</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c r="M367" s="7"/>
     </row>
     <row r="368" ht="14.25" customHeight="1">
-      <c t="s" r="A368" s="6">
-        <v>13</v>
-      </c>
-      <c r="B368" s="7">
-        <v>842</v>
-      </c>
-      <c t="s" r="C368" s="7">
-        <v>14</v>
-      </c>
+      <c r="A368" s="6"/>
+      <c r="B368" s="7"/>
+      <c r="C368" s="7"/>
       <c r="D368" s="7"/>
-      <c t="s" r="E368" s="7">
-        <v>357</v>
-      </c>
-      <c r="F368" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G368" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H368" s="8">
-        <v>138</v>
-      </c>
-      <c t="s" r="I368" s="7">
-        <v>78</v>
-      </c>
-      <c t="s" r="J368" s="7">
-        <v>128</v>
-      </c>
+      <c r="E368" s="7"/>
+      <c r="F368" s="7"/>
+      <c r="G368" s="8"/>
+      <c r="H368" s="8"/>
+      <c r="I368" s="7"/>
+      <c r="J368" s="7"/>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c r="M368" s="7"/>
@@ -12674,7 +12674,7 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>843</v>
+        <v>869</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
@@ -12687,16 +12687,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12704,10 +12704,10 @@
     </row>
     <row r="370" ht="15" customHeight="1">
       <c t="s" r="A370" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>828</v>
+        <v>842</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
@@ -12723,95 +12723,95 @@
         <v>29</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c r="M370" s="7"/>
     </row>
     <row r="371" ht="14.25" customHeight="1">
-      <c r="A371" s="6"/>
-      <c r="B371" s="7"/>
-      <c r="C371" s="7"/>
+      <c t="s" r="A371" s="6">
+        <v>13</v>
+      </c>
+      <c r="B371" s="7">
+        <v>843</v>
+      </c>
+      <c t="s" r="C371" s="7">
+        <v>14</v>
+      </c>
       <c r="D371" s="7"/>
-      <c r="E371" s="7"/>
-      <c r="F371" s="7"/>
-      <c r="G371" s="8"/>
-      <c r="H371" s="8"/>
-      <c r="I371" s="7"/>
-      <c r="J371" s="7"/>
+      <c t="s" r="E371" s="7">
+        <v>357</v>
+      </c>
+      <c r="F371" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G371" s="8">
+        <v>138</v>
+      </c>
+      <c t="s" r="H371" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I371" s="7">
+        <v>140</v>
+      </c>
+      <c t="s" r="J371" s="7">
+        <v>193</v>
+      </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c r="M371" s="7"/>
     </row>
     <row r="372" ht="14.25" customHeight="1">
       <c t="s" r="A372" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B372" s="7">
-        <v>401</v>
+        <v>828</v>
       </c>
       <c t="s" r="C372" s="7">
         <v>14</v>
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F372" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c r="M372" s="7"/>
     </row>
     <row r="373" ht="14.25" customHeight="1">
-      <c t="s" r="A373" s="6">
-        <v>13</v>
-      </c>
-      <c r="B373" s="7">
-        <v>402</v>
-      </c>
-      <c t="s" r="C373" s="7">
-        <v>14</v>
-      </c>
+      <c r="A373" s="6"/>
+      <c r="B373" s="7"/>
+      <c r="C373" s="7"/>
       <c r="D373" s="7"/>
-      <c t="s" r="E373" s="7">
-        <v>358</v>
-      </c>
-      <c r="F373" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G373" s="8">
-        <v>123</v>
-      </c>
-      <c t="s" r="H373" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I373" s="7">
-        <v>64</v>
-      </c>
-      <c t="s" r="J373" s="7">
-        <v>172</v>
-      </c>
+      <c r="E373" s="7"/>
+      <c r="F373" s="7"/>
+      <c r="G373" s="8"/>
+      <c r="H373" s="8"/>
+      <c r="I373" s="7"/>
+      <c r="J373" s="7"/>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c r="M373" s="7"/>
@@ -12821,7 +12821,7 @@
         <v>13</v>
       </c>
       <c r="B374" s="7">
-        <v>775</v>
+        <v>401</v>
       </c>
       <c t="s" r="C374" s="7">
         <v>14</v>
@@ -12837,13 +12837,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>325</v>
+        <v>135</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12854,7 +12854,7 @@
         <v>13</v>
       </c>
       <c r="B375" s="7">
-        <v>772</v>
+        <v>402</v>
       </c>
       <c t="s" r="C375" s="7">
         <v>14</v>
@@ -12867,16 +12867,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12887,7 +12887,7 @@
         <v>13</v>
       </c>
       <c r="B376" s="7">
-        <v>7712</v>
+        <v>775</v>
       </c>
       <c t="s" r="C376" s="7">
         <v>14</v>
@@ -12903,13 +12903,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>354</v>
+        <v>17</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>129</v>
+        <v>325</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>359</v>
+        <v>19</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12917,10 +12917,10 @@
     </row>
     <row r="377" ht="14.25" customHeight="1">
       <c t="s" r="A377" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B377" s="7">
-        <v>7713</v>
+        <v>772</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
@@ -12933,98 +12933,98 @@
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>354</v>
+        <v>17</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>360</v>
+        <v>66</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>361</v>
+        <v>21</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c r="M377" s="7"/>
     </row>
     <row r="378" ht="14.25" customHeight="1">
-      <c r="A378" s="6"/>
-      <c r="B378" s="7"/>
-      <c r="C378" s="7"/>
+      <c t="s" r="A378" s="6">
+        <v>13</v>
+      </c>
+      <c r="B378" s="7">
+        <v>7712</v>
+      </c>
+      <c t="s" r="C378" s="7">
+        <v>14</v>
+      </c>
       <c r="D378" s="7"/>
-      <c r="E378" s="7"/>
-      <c r="F378" s="7"/>
-      <c r="G378" s="8"/>
-      <c r="H378" s="8"/>
-      <c r="I378" s="7"/>
-      <c r="J378" s="7"/>
+      <c t="s" r="E378" s="7">
+        <v>358</v>
+      </c>
+      <c r="F378" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G378" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H378" s="8">
+        <v>354</v>
+      </c>
+      <c t="s" r="I378" s="7">
+        <v>129</v>
+      </c>
+      <c t="s" r="J378" s="7">
+        <v>359</v>
+      </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c r="M378" s="7"/>
     </row>
     <row r="379" ht="14.25" customHeight="1">
       <c t="s" r="A379" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B379" s="7">
-        <v>431</v>
+        <v>7713</v>
       </c>
       <c t="s" r="C379" s="7">
         <v>14</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
+        <v>354</v>
+      </c>
+      <c t="s" r="H379" s="8">
         <v>40</v>
       </c>
-      <c t="s" r="H379" s="8">
-        <v>82</v>
-      </c>
       <c t="s" r="I379" s="7">
-        <v>275</v>
+        <v>360</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>278</v>
+        <v>361</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c r="M379" s="7"/>
     </row>
     <row r="380" ht="15" customHeight="1">
-      <c t="s" r="A380" s="6">
-        <v>13</v>
-      </c>
-      <c r="B380" s="7">
-        <v>430</v>
-      </c>
-      <c t="s" r="C380" s="7">
-        <v>14</v>
-      </c>
+      <c r="A380" s="6"/>
+      <c r="B380" s="7"/>
+      <c r="C380" s="7"/>
       <c r="D380" s="7"/>
-      <c t="s" r="E380" s="7">
-        <v>362</v>
-      </c>
-      <c r="F380" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G380" s="8">
-        <v>82</v>
-      </c>
-      <c t="s" r="H380" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I380" s="7">
-        <v>154</v>
-      </c>
-      <c t="s" r="J380" s="7">
-        <v>27</v>
-      </c>
+      <c r="E380" s="7"/>
+      <c r="F380" s="7"/>
+      <c r="G380" s="8"/>
+      <c r="H380" s="8"/>
+      <c r="I380" s="7"/>
+      <c r="J380" s="7"/>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c r="M380" s="7"/>
@@ -13034,7 +13034,7 @@
         <v>13</v>
       </c>
       <c r="B381" s="7">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c t="s" r="C381" s="7">
         <v>14</v>
@@ -13050,13 +13050,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>43</v>
+        <v>306</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>363</v>
+        <v>281</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13067,7 +13067,7 @@
         <v>13</v>
       </c>
       <c r="B382" s="7">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c t="s" r="C382" s="7">
         <v>14</v>
@@ -13080,16 +13080,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>297</v>
+        <v>154</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13100,7 +13100,7 @@
         <v>13</v>
       </c>
       <c r="B383" s="7">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c t="s" r="C383" s="7">
         <v>14</v>
@@ -13116,13 +13116,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>255</v>
+        <v>123</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>210</v>
+        <v>43</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>80</v>
+        <v>363</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13133,7 +13133,7 @@
         <v>13</v>
       </c>
       <c r="B384" s="7">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c t="s" r="C384" s="7">
         <v>14</v>
@@ -13146,16 +13146,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>255</v>
+        <v>123</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>307</v>
+        <v>101</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13166,7 +13166,7 @@
         <v>13</v>
       </c>
       <c r="B385" s="7">
-        <v>7238</v>
+        <v>423</v>
       </c>
       <c t="s" r="C385" s="7">
         <v>14</v>
@@ -13182,13 +13182,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>273</v>
+        <v>210</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13196,10 +13196,10 @@
     </row>
     <row r="386" ht="14.25" customHeight="1">
       <c t="s" r="A386" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B386" s="7">
-        <v>7239</v>
+        <v>424</v>
       </c>
       <c t="s" r="C386" s="7">
         <v>14</v>
@@ -13212,98 +13212,98 @@
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>365</v>
+        <v>272</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>366</v>
+        <v>279</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c r="M386" s="7"/>
     </row>
     <row r="387" ht="14.25" customHeight="1">
-      <c r="A387" s="6"/>
-      <c r="B387" s="7"/>
-      <c r="C387" s="7"/>
+      <c t="s" r="A387" s="6">
+        <v>13</v>
+      </c>
+      <c r="B387" s="7">
+        <v>7238</v>
+      </c>
+      <c t="s" r="C387" s="7">
+        <v>14</v>
+      </c>
       <c r="D387" s="7"/>
-      <c r="E387" s="7"/>
-      <c r="F387" s="7"/>
-      <c r="G387" s="8"/>
-      <c r="H387" s="8"/>
-      <c r="I387" s="7"/>
-      <c r="J387" s="7"/>
+      <c t="s" r="E387" s="7">
+        <v>362</v>
+      </c>
+      <c r="F387" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G387" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H387" s="8">
+        <v>288</v>
+      </c>
+      <c t="s" r="I387" s="7">
+        <v>274</v>
+      </c>
+      <c t="s" r="J387" s="7">
+        <v>364</v>
+      </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c r="M387" s="7"/>
     </row>
     <row r="388" ht="14.25" customHeight="1">
       <c t="s" r="A388" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B388" s="7">
-        <v>925</v>
+        <v>7239</v>
       </c>
       <c t="s" r="C388" s="7">
         <v>14</v>
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F388" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>108</v>
+        <v>288</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>85</v>
+        <v>365</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c r="M388" s="7"/>
     </row>
     <row r="389" ht="14.25" customHeight="1">
-      <c t="s" r="A389" s="6">
-        <v>13</v>
-      </c>
-      <c r="B389" s="7">
-        <v>693</v>
-      </c>
-      <c t="s" r="C389" s="7">
-        <v>14</v>
-      </c>
+      <c r="A389" s="6"/>
+      <c r="B389" s="7"/>
+      <c r="C389" s="7"/>
       <c r="D389" s="7"/>
-      <c t="s" r="E389" s="7">
-        <v>367</v>
-      </c>
-      <c r="F389" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G389" s="8">
-        <v>120</v>
-      </c>
-      <c t="s" r="H389" s="8">
-        <v>123</v>
-      </c>
-      <c t="s" r="I389" s="7">
-        <v>95</v>
-      </c>
-      <c t="s" r="J389" s="7">
-        <v>264</v>
-      </c>
+      <c r="E389" s="7"/>
+      <c r="F389" s="7"/>
+      <c r="G389" s="8"/>
+      <c r="H389" s="8"/>
+      <c r="I389" s="7"/>
+      <c r="J389" s="7"/>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c r="M389" s="7"/>
@@ -13313,7 +13313,7 @@
         <v>13</v>
       </c>
       <c r="B390" s="7">
-        <v>692</v>
+        <v>925</v>
       </c>
       <c t="s" r="C390" s="7">
         <v>14</v>
@@ -13326,16 +13326,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>120</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>248</v>
+        <v>85</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>117</v>
+        <v>337</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13346,7 +13346,7 @@
         <v>13</v>
       </c>
       <c r="B391" s="7">
-        <v>926</v>
+        <v>693</v>
       </c>
       <c t="s" r="C391" s="7">
         <v>14</v>
@@ -13362,29 +13362,47 @@
         <v>120</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>368</v>
+        <v>95</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c r="M391" s="7"/>
     </row>
     <row r="392" ht="14.25" customHeight="1">
-      <c r="A392" s="6"/>
-      <c r="B392" s="7"/>
-      <c r="C392" s="7"/>
+      <c t="s" r="A392" s="6">
+        <v>13</v>
+      </c>
+      <c r="B392" s="7">
+        <v>692</v>
+      </c>
+      <c t="s" r="C392" s="7">
+        <v>14</v>
+      </c>
       <c r="D392" s="7"/>
-      <c r="E392" s="7"/>
-      <c r="F392" s="7"/>
-      <c r="G392" s="8"/>
-      <c r="H392" s="8"/>
-      <c r="I392" s="7"/>
-      <c r="J392" s="7"/>
+      <c t="s" r="E392" s="7">
+        <v>367</v>
+      </c>
+      <c r="F392" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G392" s="8">
+        <v>123</v>
+      </c>
+      <c t="s" r="H392" s="8">
+        <v>120</v>
+      </c>
+      <c t="s" r="I392" s="7">
+        <v>248</v>
+      </c>
+      <c t="s" r="J392" s="7">
+        <v>117</v>
+      </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c r="M392" s="7"/>
@@ -13394,63 +13412,45 @@
         <v>13</v>
       </c>
       <c r="B393" s="7">
-        <v>392</v>
+        <v>926</v>
       </c>
       <c t="s" r="C393" s="7">
         <v>14</v>
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>74</v>
+        <v>368</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c r="M393" s="7"/>
     </row>
     <row r="394" ht="14.25" customHeight="1">
-      <c t="s" r="A394" s="6">
-        <v>13</v>
-      </c>
-      <c r="B394" s="7">
-        <v>393</v>
-      </c>
-      <c t="s" r="C394" s="7">
-        <v>14</v>
-      </c>
+      <c r="A394" s="6"/>
+      <c r="B394" s="7"/>
+      <c r="C394" s="7"/>
       <c r="D394" s="7"/>
-      <c t="s" r="E394" s="7">
-        <v>369</v>
-      </c>
-      <c r="F394" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G394" s="8">
-        <v>255</v>
-      </c>
-      <c t="s" r="H394" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I394" s="7">
-        <v>86</v>
-      </c>
-      <c t="s" r="J394" s="7">
-        <v>51</v>
-      </c>
+      <c r="E394" s="7"/>
+      <c r="F394" s="7"/>
+      <c r="G394" s="8"/>
+      <c r="H394" s="8"/>
+      <c r="I394" s="7"/>
+      <c r="J394" s="7"/>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c r="M394" s="7"/>
@@ -13460,7 +13460,7 @@
         <v>13</v>
       </c>
       <c r="B395" s="7">
-        <v>274</v>
+        <v>392</v>
       </c>
       <c t="s" r="C395" s="7">
         <v>14</v>
@@ -13476,13 +13476,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>120</v>
+        <v>255</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>370</v>
+        <v>74</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13493,7 +13493,7 @@
         <v>13</v>
       </c>
       <c r="B396" s="7">
-        <v>275</v>
+        <v>393</v>
       </c>
       <c t="s" r="C396" s="7">
         <v>14</v>
@@ -13506,16 +13506,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>120</v>
+        <v>255</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>229</v>
+        <v>86</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13526,7 +13526,7 @@
         <v>13</v>
       </c>
       <c r="B397" s="7">
-        <v>144</v>
+        <v>274</v>
       </c>
       <c t="s" r="C397" s="7">
         <v>14</v>
@@ -13542,13 +13542,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13559,7 +13559,7 @@
         <v>13</v>
       </c>
       <c r="B398" s="7">
-        <v>521</v>
+        <v>275</v>
       </c>
       <c t="s" r="C398" s="7">
         <v>14</v>
@@ -13572,16 +13572,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>307</v>
+        <v>229</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13592,7 +13592,7 @@
         <v>13</v>
       </c>
       <c r="B399" s="7">
-        <v>518</v>
+        <v>144</v>
       </c>
       <c t="s" r="C399" s="7">
         <v>14</v>
@@ -13605,32 +13605,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>371</v>
+        <v>238</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c r="M399" s="7"/>
     </row>
     <row r="400" ht="15" customHeight="1">
-      <c r="A400" s="6"/>
-      <c r="B400" s="7"/>
-      <c r="C400" s="7"/>
+      <c t="s" r="A400" s="6">
+        <v>13</v>
+      </c>
+      <c r="B400" s="7">
+        <v>521</v>
+      </c>
+      <c t="s" r="C400" s="7">
+        <v>14</v>
+      </c>
       <c r="D400" s="7"/>
-      <c r="E400" s="7"/>
-      <c r="F400" s="7"/>
-      <c r="G400" s="8"/>
-      <c r="H400" s="8"/>
-      <c r="I400" s="7"/>
-      <c r="J400" s="7"/>
+      <c t="s" r="E400" s="7">
+        <v>369</v>
+      </c>
+      <c r="F400" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G400" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H400" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="I400" s="7">
+        <v>279</v>
+      </c>
+      <c t="s" r="J400" s="7">
+        <v>71</v>
+      </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c r="M400" s="7"/>
@@ -13640,63 +13658,45 @@
         <v>13</v>
       </c>
       <c r="B401" s="7">
-        <v>879</v>
+        <v>518</v>
       </c>
       <c t="s" r="C401" s="7">
         <v>14</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>145</v>
+        <v>371</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c r="M401" s="7"/>
     </row>
     <row r="402" ht="14.25" customHeight="1">
-      <c t="s" r="A402" s="6">
-        <v>13</v>
-      </c>
-      <c r="B402" s="7">
-        <v>8890</v>
-      </c>
-      <c t="s" r="C402" s="7">
-        <v>14</v>
-      </c>
+      <c r="A402" s="6"/>
+      <c r="B402" s="7"/>
+      <c r="C402" s="7"/>
       <c r="D402" s="7"/>
-      <c t="s" r="E402" s="7">
-        <v>372</v>
-      </c>
-      <c r="F402" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G402" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="H402" s="8">
-        <v>373</v>
-      </c>
-      <c t="s" r="I402" s="7">
-        <v>363</v>
-      </c>
-      <c t="s" r="J402" s="7">
-        <v>247</v>
-      </c>
+      <c r="E402" s="7"/>
+      <c r="F402" s="7"/>
+      <c r="G402" s="8"/>
+      <c r="H402" s="8"/>
+      <c r="I402" s="7"/>
+      <c r="J402" s="7"/>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c r="M402" s="7"/>
@@ -13706,7 +13706,7 @@
         <v>13</v>
       </c>
       <c r="B403" s="7">
-        <v>8891</v>
+        <v>879</v>
       </c>
       <c t="s" r="C403" s="7">
         <v>14</v>
@@ -13719,16 +13719,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>373</v>
+        <v>108</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>155</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13739,7 +13739,7 @@
         <v>13</v>
       </c>
       <c r="B404" s="7">
-        <v>8892</v>
+        <v>8890</v>
       </c>
       <c t="s" r="C404" s="7">
         <v>14</v>
@@ -13758,10 +13758,10 @@
         <v>373</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>196</v>
+        <v>363</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>175</v>
+        <v>247</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13772,7 +13772,7 @@
         <v>13</v>
       </c>
       <c r="B405" s="7">
-        <v>8893</v>
+        <v>8891</v>
       </c>
       <c t="s" r="C405" s="7">
         <v>14</v>
@@ -13791,26 +13791,44 @@
         <v>155</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>334</v>
+        <v>55</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c r="M405" s="7"/>
     </row>
     <row r="406" ht="14.25" customHeight="1">
-      <c r="A406" s="6"/>
-      <c r="B406" s="7"/>
-      <c r="C406" s="7"/>
+      <c t="s" r="A406" s="6">
+        <v>13</v>
+      </c>
+      <c r="B406" s="7">
+        <v>8892</v>
+      </c>
+      <c t="s" r="C406" s="7">
+        <v>14</v>
+      </c>
       <c r="D406" s="7"/>
-      <c r="E406" s="7"/>
-      <c r="F406" s="7"/>
-      <c r="G406" s="8"/>
-      <c r="H406" s="8"/>
-      <c r="I406" s="7"/>
-      <c r="J406" s="7"/>
+      <c t="s" r="E406" s="7">
+        <v>372</v>
+      </c>
+      <c r="F406" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G406" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="H406" s="8">
+        <v>373</v>
+      </c>
+      <c t="s" r="I406" s="7">
+        <v>196</v>
+      </c>
+      <c t="s" r="J406" s="7">
+        <v>175</v>
+      </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c r="M406" s="7"/>
@@ -13820,63 +13838,45 @@
         <v>13</v>
       </c>
       <c r="B407" s="7">
-        <v>963</v>
+        <v>8893</v>
       </c>
       <c t="s" r="C407" s="7">
         <v>14</v>
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>108</v>
+        <v>373</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>375</v>
+        <v>334</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c r="M407" s="7"/>
     </row>
     <row r="408" ht="14.25" customHeight="1">
-      <c t="s" r="A408" s="6">
-        <v>13</v>
-      </c>
-      <c r="B408" s="7">
-        <v>463</v>
-      </c>
-      <c t="s" r="C408" s="7">
-        <v>14</v>
-      </c>
+      <c r="A408" s="6"/>
+      <c r="B408" s="7"/>
+      <c r="C408" s="7"/>
       <c r="D408" s="7"/>
-      <c t="s" r="E408" s="7">
-        <v>374</v>
-      </c>
-      <c r="F408" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G408" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H408" s="8">
-        <v>309</v>
-      </c>
-      <c t="s" r="I408" s="7">
-        <v>156</v>
-      </c>
-      <c t="s" r="J408" s="7">
-        <v>229</v>
-      </c>
+      <c r="E408" s="7"/>
+      <c r="F408" s="7"/>
+      <c r="G408" s="8"/>
+      <c r="H408" s="8"/>
+      <c r="I408" s="7"/>
+      <c r="J408" s="7"/>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c r="M408" s="7"/>
@@ -13886,7 +13886,7 @@
         <v>13</v>
       </c>
       <c r="B409" s="7">
-        <v>464</v>
+        <v>963</v>
       </c>
       <c t="s" r="C409" s="7">
         <v>14</v>
@@ -13899,16 +13899,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>309</v>
+        <v>108</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>52</v>
+        <v>375</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>280</v>
+        <v>181</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13919,7 +13919,7 @@
         <v>13</v>
       </c>
       <c r="B410" s="7">
-        <v>439</v>
+        <v>901</v>
       </c>
       <c t="s" r="C410" s="7">
         <v>14</v>
@@ -13935,13 +13935,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>150</v>
+        <v>52</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13952,7 +13952,7 @@
         <v>13</v>
       </c>
       <c r="B411" s="7">
-        <v>438</v>
+        <v>902</v>
       </c>
       <c t="s" r="C411" s="7">
         <v>14</v>
@@ -13965,16 +13965,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13985,7 +13985,7 @@
         <v>13</v>
       </c>
       <c r="B412" s="7">
-        <v>161</v>
+        <v>781</v>
       </c>
       <c t="s" r="C412" s="7">
         <v>14</v>
@@ -14001,13 +14001,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14511,7 +14511,7 @@
         <v>382</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>174</v>
@@ -14904,7 +14904,7 @@
         <v>351</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J442" s="7">
         <v>52</v>
@@ -15117,7 +15117,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>267</v>
@@ -15820,7 +15820,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>

--- a/Data/FlightPlan/FPL_25SEP26.xlsx
+++ b/Data/FlightPlan/FPL_25SEP26.xlsx
@@ -338,7 +338,7 @@
     <t>07:35</t>
   </si>
   <si>
-    <t>08:13</t>
+    <t>08:16</t>
   </si>
   <si>
     <t>08:30</t>
@@ -530,87 +530,96 @@
     <t>11:10</t>
   </si>
   <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
     <t>18:05</t>
   </si>
   <si>
-    <t>19:20</t>
-  </si>
-  <si>
     <t>22:15</t>
   </si>
   <si>
     <t>00:25</t>
   </si>
   <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
     <t>VN-A549</t>
   </si>
   <si>
@@ -695,9 +704,6 @@
     <t>VN-A554</t>
   </si>
   <si>
-    <t>12:30</t>
-  </si>
-  <si>
     <t>18:20</t>
   </si>
   <si>
@@ -902,42 +908,36 @@
     <t>VN-A639</t>
   </si>
   <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
   </si>
   <si>
     <t>00:50</t>
   </si>
   <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
     <t>VN-A643</t>
   </si>
   <si>
@@ -1241,7 +1241,7 @@
     <t>Total Record(s): 391</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 25, 2026 02:11</t>
+    <t xml:space="preserve">Generated on  Sep 25, 2026 02:42</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4350,7 +4350,7 @@
         <v>13</v>
       </c>
       <c r="B92" s="7">
-        <v>144</v>
+        <v>308</v>
       </c>
       <c t="s" r="C92" s="7">
         <v>14</v>
@@ -4366,13 +4366,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>173</v>
+        <v>94</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4383,7 +4383,7 @@
         <v>13</v>
       </c>
       <c r="B93" s="7">
-        <v>1127</v>
+        <v>307</v>
       </c>
       <c t="s" r="C93" s="7">
         <v>14</v>
@@ -4396,16 +4396,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>174</v>
+        <v>95</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4416,7 +4416,7 @@
         <v>13</v>
       </c>
       <c r="B94" s="7">
-        <v>1128</v>
+        <v>248</v>
       </c>
       <c t="s" r="C94" s="7">
         <v>14</v>
@@ -4432,62 +4432,62 @@
         <v>29</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c t="s" r="I94" s="7">
+        <v>174</v>
+      </c>
+      <c t="s" r="J94" s="7">
         <v>175</v>
-      </c>
-      <c t="s" r="J94" s="7">
-        <v>176</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
     </row>
     <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="6"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
+      <c t="s" r="A95" s="6">
+        <v>13</v>
+      </c>
+      <c r="B95" s="7">
+        <v>249</v>
+      </c>
+      <c t="s" r="C95" s="7">
+        <v>14</v>
+      </c>
       <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="7"/>
-      <c r="J95" s="7"/>
+      <c t="s" r="E95" s="7">
+        <v>165</v>
+      </c>
+      <c r="F95" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G95" s="8">
+        <v>92</v>
+      </c>
+      <c t="s" r="H95" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I95" s="7">
+        <v>176</v>
+      </c>
+      <c t="s" r="J95" s="7">
+        <v>141</v>
+      </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c t="s" r="A96" s="6">
-        <v>13</v>
-      </c>
-      <c r="B96" s="7">
-        <v>628</v>
-      </c>
-      <c t="s" r="C96" s="7">
-        <v>14</v>
-      </c>
+      <c r="A96" s="6"/>
+      <c r="B96" s="7"/>
+      <c r="C96" s="7"/>
       <c r="D96" s="7"/>
-      <c t="s" r="E96" s="7">
-        <v>177</v>
-      </c>
-      <c r="F96" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G96" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H96" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="I96" s="7">
-        <v>178</v>
-      </c>
-      <c t="s" r="J96" s="7">
-        <v>179</v>
-      </c>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="7"/>
+      <c r="J96" s="7"/>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c r="M96" s="7"/>
@@ -4497,7 +4497,7 @@
         <v>13</v>
       </c>
       <c r="B97" s="7">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c t="s" r="C97" s="7">
         <v>14</v>
@@ -4510,16 +4510,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H97" s="8">
         <v>155</v>
       </c>
-      <c t="s" r="H97" s="8">
-        <v>29</v>
-      </c>
       <c t="s" r="I97" s="7">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4530,7 +4530,7 @@
         <v>13</v>
       </c>
       <c r="B98" s="7">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c t="s" r="C98" s="7">
         <v>14</v>
@@ -4543,16 +4543,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4563,7 +4563,7 @@
         <v>13</v>
       </c>
       <c r="B99" s="7">
-        <v>1504</v>
+        <v>634</v>
       </c>
       <c t="s" r="C99" s="7">
         <v>14</v>
@@ -4576,16 +4576,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H99" s="8">
         <v>155</v>
       </c>
-      <c t="s" r="H99" s="8">
-        <v>40</v>
-      </c>
       <c t="s" r="I99" s="7">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4596,7 +4596,7 @@
         <v>13</v>
       </c>
       <c r="B100" s="7">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c t="s" r="C100" s="7">
         <v>14</v>
@@ -4609,65 +4609,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="H100" s="8">
         <v>40</v>
       </c>
-      <c t="s" r="H100" s="8">
-        <v>155</v>
-      </c>
       <c t="s" r="I100" s="7">
-        <v>32</v>
+        <v>182</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="6"/>
-      <c r="B101" s="7"/>
-      <c r="C101" s="7"/>
+      <c t="s" r="A101" s="6">
+        <v>13</v>
+      </c>
+      <c r="B101" s="7">
+        <v>1505</v>
+      </c>
+      <c t="s" r="C101" s="7">
+        <v>14</v>
+      </c>
       <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="8"/>
-      <c r="I101" s="7"/>
-      <c r="J101" s="7"/>
+      <c t="s" r="E101" s="7">
+        <v>177</v>
+      </c>
+      <c r="F101" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G101" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H101" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="I101" s="7">
+        <v>32</v>
+      </c>
+      <c t="s" r="J101" s="7">
+        <v>21</v>
+      </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c r="M101" s="7"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c t="s" r="A102" s="6">
-        <v>13</v>
-      </c>
-      <c r="B102" s="7">
-        <v>863</v>
-      </c>
-      <c t="s" r="C102" s="7">
-        <v>14</v>
-      </c>
+      <c r="A102" s="6"/>
+      <c r="B102" s="7"/>
+      <c r="C102" s="7"/>
       <c r="D102" s="7"/>
-      <c t="s" r="E102" s="7">
-        <v>183</v>
-      </c>
-      <c r="F102" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G102" s="8">
-        <v>106</v>
-      </c>
-      <c t="s" r="H102" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I102" s="7">
-        <v>184</v>
-      </c>
-      <c t="s" r="J102" s="7">
-        <v>185</v>
-      </c>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="7"/>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
@@ -4677,7 +4677,7 @@
         <v>13</v>
       </c>
       <c r="B103" s="7">
-        <v>1801</v>
+        <v>863</v>
       </c>
       <c t="s" r="C103" s="7">
         <v>14</v>
@@ -4690,16 +4690,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>186</v>
+        <v>29</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4710,7 +4710,7 @@
         <v>13</v>
       </c>
       <c r="B104" s="7">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c t="s" r="C104" s="7">
         <v>14</v>
@@ -4723,65 +4723,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H104" s="8">
         <v>186</v>
       </c>
-      <c t="s" r="H104" s="8">
-        <v>29</v>
-      </c>
       <c t="s" r="I104" s="7">
+        <v>187</v>
+      </c>
+      <c t="s" r="J104" s="7">
         <v>188</v>
-      </c>
-      <c t="s" r="J104" s="7">
-        <v>153</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
     </row>
     <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="6"/>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7"/>
+      <c t="s" r="A105" s="6">
+        <v>13</v>
+      </c>
+      <c r="B105" s="7">
+        <v>1802</v>
+      </c>
+      <c t="s" r="C105" s="7">
+        <v>14</v>
+      </c>
       <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="8"/>
-      <c r="H105" s="8"/>
-      <c r="I105" s="7"/>
-      <c r="J105" s="7"/>
+      <c t="s" r="E105" s="7">
+        <v>183</v>
+      </c>
+      <c r="F105" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G105" s="8">
+        <v>186</v>
+      </c>
+      <c t="s" r="H105" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I105" s="7">
+        <v>189</v>
+      </c>
+      <c t="s" r="J105" s="7">
+        <v>153</v>
+      </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c r="M105" s="7"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c t="s" r="A106" s="6">
-        <v>13</v>
-      </c>
-      <c r="B106" s="7">
-        <v>961</v>
-      </c>
-      <c t="s" r="C106" s="7">
-        <v>14</v>
-      </c>
+      <c r="A106" s="6"/>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
       <c r="D106" s="7"/>
-      <c t="s" r="E106" s="7">
-        <v>189</v>
-      </c>
-      <c r="F106" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G106" s="8">
-        <v>106</v>
-      </c>
-      <c t="s" r="H106" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I106" s="7">
-        <v>190</v>
-      </c>
-      <c t="s" r="J106" s="7">
-        <v>19</v>
-      </c>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="7"/>
+      <c r="J106" s="7"/>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c r="M106" s="7"/>
@@ -4791,29 +4791,29 @@
         <v>13</v>
       </c>
       <c r="B107" s="7">
-        <v>441</v>
+        <v>961</v>
       </c>
       <c t="s" r="C107" s="7">
         <v>14</v>
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
+        <v>106</v>
+      </c>
+      <c t="s" r="H107" s="8">
         <v>40</v>
       </c>
-      <c t="s" r="H107" s="8">
-        <v>70</v>
-      </c>
       <c t="s" r="I107" s="7">
-        <v>68</v>
+        <v>191</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>191</v>
+        <v>19</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4824,26 +4824,26 @@
         <v>13</v>
       </c>
       <c r="B108" s="7">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c t="s" r="C108" s="7">
         <v>14</v>
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H108" s="8">
         <v>70</v>
       </c>
-      <c t="s" r="H108" s="8">
-        <v>40</v>
-      </c>
       <c t="s" r="I108" s="7">
-        <v>174</v>
+        <v>68</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>192</v>
@@ -4854,81 +4854,81 @@
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c t="s" r="A109" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B109" s="7">
-        <v>958</v>
+        <v>442</v>
       </c>
       <c t="s" r="C109" s="7">
         <v>14</v>
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
+        <v>70</v>
+      </c>
+      <c t="s" r="H109" s="8">
         <v>40</v>
       </c>
-      <c t="s" r="H109" s="8">
+      <c t="s" r="I109" s="7">
+        <v>187</v>
+      </c>
+      <c t="s" r="J109" s="7">
         <v>193</v>
-      </c>
-      <c t="s" r="I109" s="7">
-        <v>194</v>
-      </c>
-      <c t="s" r="J109" s="7">
-        <v>162</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
     </row>
     <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="6"/>
-      <c r="B110" s="7"/>
-      <c r="C110" s="7"/>
+      <c t="s" r="A110" s="6">
+        <v>25</v>
+      </c>
+      <c r="B110" s="7">
+        <v>958</v>
+      </c>
+      <c t="s" r="C110" s="7">
+        <v>14</v>
+      </c>
       <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="7"/>
-      <c r="J110" s="7"/>
+      <c t="s" r="E110" s="7">
+        <v>190</v>
+      </c>
+      <c r="F110" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G110" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H110" s="8">
+        <v>194</v>
+      </c>
+      <c t="s" r="I110" s="7">
+        <v>195</v>
+      </c>
+      <c t="s" r="J110" s="7">
+        <v>162</v>
+      </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c t="s" r="A111" s="6">
-        <v>13</v>
-      </c>
-      <c r="B111" s="7">
-        <v>156</v>
-      </c>
-      <c t="s" r="C111" s="7">
-        <v>14</v>
-      </c>
+      <c r="A111" s="6"/>
+      <c r="B111" s="7"/>
+      <c r="C111" s="7"/>
       <c r="D111" s="7"/>
-      <c t="s" r="E111" s="7">
-        <v>195</v>
-      </c>
-      <c r="F111" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G111" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H111" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I111" s="7">
-        <v>167</v>
-      </c>
-      <c t="s" r="J111" s="7">
-        <v>120</v>
-      </c>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="7"/>
+      <c r="J111" s="7"/>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
@@ -4938,29 +4938,29 @@
         <v>13</v>
       </c>
       <c r="B112" s="7">
-        <v>135</v>
+        <v>350</v>
       </c>
       <c t="s" r="C112" s="7">
         <v>14</v>
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>29</v>
+        <v>168</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>147</v>
+        <v>62</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4971,29 +4971,29 @@
         <v>13</v>
       </c>
       <c r="B113" s="7">
-        <v>308</v>
+        <v>351</v>
       </c>
       <c t="s" r="C113" s="7">
         <v>14</v>
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>29</v>
+        <v>168</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5004,29 +5004,29 @@
         <v>13</v>
       </c>
       <c r="B114" s="7">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c t="s" r="C114" s="7">
         <v>14</v>
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5037,29 +5037,29 @@
         <v>13</v>
       </c>
       <c r="B115" s="7">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c t="s" r="C115" s="7">
         <v>14</v>
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5070,45 +5070,63 @@
         <v>13</v>
       </c>
       <c r="B116" s="7">
-        <v>249</v>
+        <v>144</v>
       </c>
       <c t="s" r="C116" s="7">
         <v>14</v>
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c r="M116" s="7"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="6"/>
-      <c r="B117" s="7"/>
-      <c r="C117" s="7"/>
+      <c t="s" r="A117" s="6">
+        <v>13</v>
+      </c>
+      <c r="B117" s="7">
+        <v>1127</v>
+      </c>
+      <c t="s" r="C117" s="7">
+        <v>14</v>
+      </c>
       <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="8"/>
-      <c r="H117" s="8"/>
-      <c r="I117" s="7"/>
-      <c r="J117" s="7"/>
+      <c t="s" r="E117" s="7">
+        <v>196</v>
+      </c>
+      <c r="F117" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G117" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H117" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I117" s="7">
+        <v>187</v>
+      </c>
+      <c t="s" r="J117" s="7">
+        <v>160</v>
+      </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c r="M117" s="7"/>
@@ -5118,63 +5136,45 @@
         <v>13</v>
       </c>
       <c r="B118" s="7">
-        <v>2979</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C118" s="7">
         <v>14</v>
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>201</v>
+        <v>29</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I118" s="7">
+        <v>201</v>
+      </c>
+      <c t="s" r="J118" s="7">
         <v>202</v>
-      </c>
-      <c t="s" r="J118" s="7">
-        <v>120</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c r="M118" s="7"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c t="s" r="A119" s="6">
-        <v>13</v>
-      </c>
-      <c r="B119" s="7">
-        <v>2979</v>
-      </c>
-      <c t="s" r="C119" s="7">
-        <v>14</v>
-      </c>
+      <c r="A119" s="6"/>
+      <c r="B119" s="7"/>
+      <c r="C119" s="7"/>
       <c r="D119" s="7"/>
-      <c t="s" r="E119" s="7">
-        <v>200</v>
-      </c>
-      <c r="F119" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G119" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H119" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I119" s="7">
-        <v>51</v>
-      </c>
-      <c t="s" r="J119" s="7">
-        <v>203</v>
-      </c>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
+      <c r="G119" s="8"/>
+      <c r="H119" s="8"/>
+      <c r="I119" s="7"/>
+      <c r="J119" s="7"/>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c r="M119" s="7"/>
@@ -5184,29 +5184,29 @@
         <v>13</v>
       </c>
       <c r="B120" s="7">
-        <v>7706</v>
+        <v>2979</v>
       </c>
       <c t="s" r="C120" s="7">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>17</v>
+        <v>204</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>141</v>
+        <v>205</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5214,17 +5214,17 @@
     </row>
     <row r="121" ht="14.25" customHeight="1">
       <c t="s" r="A121" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B121" s="7">
-        <v>7706</v>
+        <v>2979</v>
       </c>
       <c t="s" r="C121" s="7">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5233,46 +5233,68 @@
         <v>40</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c t="s" r="I121" s="7">
+        <v>51</v>
+      </c>
+      <c t="s" r="J121" s="7">
         <v>206</v>
       </c>
-      <c t="s" r="J121" s="7">
-        <v>27</v>
-      </c>
-      <c r="K121" s="7"/>
+      <c t="s" r="K121" s="7">
+        <v>76</v>
+      </c>
       <c r="L121" s="7"/>
-      <c r="M121" s="7"/>
+      <c t="s" r="M121" s="7">
+        <v>182</v>
+      </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="6"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="7"/>
+      <c t="s" r="A122" s="6">
+        <v>13</v>
+      </c>
+      <c r="B122" s="7">
+        <v>7706</v>
+      </c>
+      <c t="s" r="C122" s="7">
+        <v>207</v>
+      </c>
       <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="8"/>
-      <c r="H122" s="8"/>
-      <c r="I122" s="7"/>
-      <c r="J122" s="7"/>
+      <c t="s" r="E122" s="7">
+        <v>203</v>
+      </c>
+      <c r="F122" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G122" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H122" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I122" s="7">
+        <v>141</v>
+      </c>
+      <c t="s" r="J122" s="7">
+        <v>47</v>
+      </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c r="M122" s="7"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c t="s" r="A123" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B123" s="7">
-        <v>929</v>
+        <v>7706</v>
       </c>
       <c t="s" r="C123" s="7">
-        <v>14</v>
+        <v>207</v>
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5287,41 +5309,23 @@
         <v>209</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c r="M123" s="7"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c t="s" r="A124" s="6">
-        <v>13</v>
-      </c>
-      <c r="B124" s="7">
-        <v>928</v>
-      </c>
-      <c t="s" r="C124" s="7">
-        <v>14</v>
-      </c>
+      <c r="A124" s="6"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="7"/>
       <c r="D124" s="7"/>
-      <c t="s" r="E124" s="7">
-        <v>207</v>
-      </c>
-      <c r="F124" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G124" s="8">
-        <v>208</v>
-      </c>
-      <c t="s" r="H124" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I124" s="7">
-        <v>54</v>
-      </c>
-      <c t="s" r="J124" s="7">
-        <v>197</v>
-      </c>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7"/>
+      <c r="G124" s="8"/>
+      <c r="H124" s="8"/>
+      <c r="I124" s="7"/>
+      <c r="J124" s="7"/>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
@@ -5331,14 +5335,14 @@
         <v>13</v>
       </c>
       <c r="B125" s="7">
-        <v>907</v>
+        <v>929</v>
       </c>
       <c t="s" r="C125" s="7">
         <v>14</v>
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5347,13 +5351,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>71</v>
+        <v>212</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>211</v>
+        <v>52</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5361,71 +5365,89 @@
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c t="s" r="A126" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B126" s="7">
-        <v>910</v>
+        <v>928</v>
       </c>
       <c t="s" r="C126" s="7">
         <v>14</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>212</v>
+        <v>54</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c r="M126" s="7"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="6"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
+      <c t="s" r="A127" s="6">
+        <v>13</v>
+      </c>
+      <c r="B127" s="7">
+        <v>907</v>
+      </c>
+      <c t="s" r="C127" s="7">
+        <v>14</v>
+      </c>
       <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-      <c r="G127" s="8"/>
-      <c r="H127" s="8"/>
-      <c r="I127" s="7"/>
-      <c r="J127" s="7"/>
+      <c t="s" r="E127" s="7">
+        <v>210</v>
+      </c>
+      <c r="F127" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G127" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H127" s="8">
+        <v>213</v>
+      </c>
+      <c t="s" r="I127" s="7">
+        <v>71</v>
+      </c>
+      <c t="s" r="J127" s="7">
+        <v>214</v>
+      </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c r="M127" s="7"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c t="s" r="A128" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B128" s="7">
-        <v>921</v>
+        <v>910</v>
       </c>
       <c t="s" r="C128" s="7">
         <v>14</v>
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>40</v>
@@ -5441,34 +5463,16 @@
       <c r="M128" s="7"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c t="s" r="A129" s="6">
-        <v>13</v>
-      </c>
-      <c r="B129" s="7">
-        <v>946</v>
-      </c>
-      <c t="s" r="C129" s="7">
-        <v>14</v>
-      </c>
+      <c r="A129" s="6"/>
+      <c r="B129" s="7"/>
+      <c r="C129" s="7"/>
       <c r="D129" s="7"/>
-      <c t="s" r="E129" s="7">
-        <v>214</v>
-      </c>
-      <c r="F129" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G129" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H129" s="8">
-        <v>217</v>
-      </c>
-      <c t="s" r="I129" s="7">
-        <v>32</v>
-      </c>
-      <c t="s" r="J129" s="7">
-        <v>218</v>
-      </c>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7"/>
+      <c r="G129" s="8"/>
+      <c r="H129" s="8"/>
+      <c r="I129" s="7"/>
+      <c r="J129" s="7"/>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c r="M129" s="7"/>
@@ -5478,26 +5482,26 @@
         <v>13</v>
       </c>
       <c r="B130" s="7">
-        <v>947</v>
+        <v>921</v>
       </c>
       <c t="s" r="C130" s="7">
         <v>14</v>
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>217</v>
+        <v>163</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>219</v>
@@ -5507,16 +5511,34 @@
       <c r="M130" s="7"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="6"/>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
+      <c t="s" r="A131" s="6">
+        <v>13</v>
+      </c>
+      <c r="B131" s="7">
+        <v>946</v>
+      </c>
+      <c t="s" r="C131" s="7">
+        <v>14</v>
+      </c>
       <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="8"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="7"/>
-      <c r="J131" s="7"/>
+      <c t="s" r="E131" s="7">
+        <v>217</v>
+      </c>
+      <c r="F131" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G131" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H131" s="8">
+        <v>220</v>
+      </c>
+      <c t="s" r="I131" s="7">
+        <v>32</v>
+      </c>
+      <c t="s" r="J131" s="7">
+        <v>221</v>
+      </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
@@ -5526,26 +5548,26 @@
         <v>13</v>
       </c>
       <c r="B132" s="7">
-        <v>7615</v>
+        <v>947</v>
       </c>
       <c t="s" r="C132" s="7">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
+        <v>217</v>
+      </c>
+      <c r="F132" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G132" s="8">
         <v>220</v>
-      </c>
-      <c r="F132" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G132" s="8">
-        <v>221</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>222</v>
@@ -5555,34 +5577,16 @@
       <c r="M132" s="7"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c t="s" r="A133" s="6">
-        <v>13</v>
-      </c>
-      <c r="B133" s="7">
-        <v>7615</v>
-      </c>
-      <c t="s" r="C133" s="7">
-        <v>204</v>
-      </c>
+      <c r="A133" s="6"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="7"/>
       <c r="D133" s="7"/>
-      <c t="s" r="E133" s="7">
-        <v>220</v>
-      </c>
-      <c r="F133" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G133" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H133" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I133" s="7">
-        <v>93</v>
-      </c>
-      <c t="s" r="J133" s="7">
-        <v>223</v>
-      </c>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="8"/>
+      <c r="H133" s="8"/>
+      <c r="I133" s="7"/>
+      <c r="J133" s="7"/>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
@@ -5592,29 +5596,29 @@
         <v>13</v>
       </c>
       <c r="B134" s="7">
-        <v>601</v>
+        <v>7615</v>
       </c>
       <c t="s" r="C134" s="7">
-        <v>14</v>
+        <v>207</v>
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>17</v>
+        <v>224</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5625,29 +5629,29 @@
         <v>13</v>
       </c>
       <c r="B135" s="7">
-        <v>262</v>
+        <v>7615</v>
       </c>
       <c t="s" r="C135" s="7">
-        <v>14</v>
+        <v>207</v>
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>225</v>
+        <v>17</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>218</v>
+        <v>93</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5658,45 +5662,63 @@
         <v>13</v>
       </c>
       <c r="B136" s="7">
-        <v>263</v>
+        <v>601</v>
       </c>
       <c t="s" r="C136" s="7">
         <v>14</v>
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>225</v>
+        <v>17</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>226</v>
+        <v>56</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c r="M136" s="7"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="6"/>
-      <c r="B137" s="7"/>
-      <c r="C137" s="7"/>
+      <c t="s" r="A137" s="6">
+        <v>13</v>
+      </c>
+      <c r="B137" s="7">
+        <v>262</v>
+      </c>
+      <c t="s" r="C137" s="7">
+        <v>14</v>
+      </c>
       <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
-      <c r="G137" s="8"/>
-      <c r="H137" s="8"/>
-      <c r="I137" s="7"/>
-      <c r="J137" s="7"/>
+      <c t="s" r="E137" s="7">
+        <v>223</v>
+      </c>
+      <c r="F137" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G137" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H137" s="8">
+        <v>228</v>
+      </c>
+      <c t="s" r="I137" s="7">
+        <v>221</v>
+      </c>
+      <c t="s" r="J137" s="7">
+        <v>187</v>
+      </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c r="M137" s="7"/>
@@ -5706,63 +5728,45 @@
         <v>13</v>
       </c>
       <c r="B138" s="7">
-        <v>2925</v>
+        <v>263</v>
       </c>
       <c t="s" r="C138" s="7">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>40</v>
+        <v>228</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>120</v>
+        <v>229</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c r="M138" s="7"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c t="s" r="A139" s="6">
-        <v>13</v>
-      </c>
-      <c r="B139" s="7">
-        <v>629</v>
-      </c>
-      <c t="s" r="C139" s="7">
-        <v>14</v>
-      </c>
+      <c r="A139" s="6"/>
+      <c r="B139" s="7"/>
+      <c r="C139" s="7"/>
       <c r="D139" s="7"/>
-      <c t="s" r="E139" s="7">
-        <v>227</v>
-      </c>
-      <c r="F139" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G139" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="H139" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I139" s="7">
-        <v>190</v>
-      </c>
-      <c t="s" r="J139" s="7">
-        <v>228</v>
-      </c>
+      <c r="E139" s="7"/>
+      <c r="F139" s="7"/>
+      <c r="G139" s="8"/>
+      <c r="H139" s="8"/>
+      <c r="I139" s="7"/>
+      <c r="J139" s="7"/>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c r="M139" s="7"/>
@@ -5772,29 +5776,29 @@
         <v>13</v>
       </c>
       <c r="B140" s="7">
-        <v>600</v>
+        <v>2925</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>14</v>
+        <v>207</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5805,189 +5809,189 @@
         <v>13</v>
       </c>
       <c r="B141" s="7">
-        <v>5068</v>
+        <v>629</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>32</v>
+        <v>191</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>56</v>
-      </c>
-      <c t="s" r="K141" s="7">
-        <v>114</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="K141" s="7"/>
       <c r="L141" s="7"/>
-      <c t="s" r="M141" s="7">
-        <v>229</v>
-      </c>
+      <c r="M141" s="7"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
       <c t="s" r="A142" s="6">
         <v>13</v>
       </c>
       <c r="B142" s="7">
-        <v>5068</v>
+        <v>600</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>230</v>
+        <v>17</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>126</v>
+        <v>32</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>231</v>
-      </c>
-      <c t="s" r="K142" s="7">
-        <v>139</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="K142" s="7"/>
       <c r="L142" s="7"/>
-      <c t="s" r="M142" s="7">
-        <v>206</v>
-      </c>
+      <c r="M142" s="7"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c t="s" r="A143" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B143" s="7">
-        <v>5069</v>
+        <v>5068</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>230</v>
+        <v>17</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>232</v>
+        <v>32</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>233</v>
+        <v>56</v>
       </c>
       <c t="s" r="K143" s="7">
-        <v>234</v>
+        <v>114</v>
       </c>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="6"/>
-      <c r="B144" s="7"/>
-      <c r="C144" s="7"/>
+      <c t="s" r="A144" s="6">
+        <v>13</v>
+      </c>
+      <c r="B144" s="7">
+        <v>5068</v>
+      </c>
+      <c t="s" r="C144" s="7">
+        <v>207</v>
+      </c>
       <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="7"/>
-      <c r="G144" s="8"/>
-      <c r="H144" s="8"/>
-      <c r="I144" s="7"/>
-      <c r="J144" s="7"/>
-      <c r="K144" s="7"/>
+      <c t="s" r="E144" s="7">
+        <v>230</v>
+      </c>
+      <c r="F144" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G144" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H144" s="8">
+        <v>232</v>
+      </c>
+      <c t="s" r="I144" s="7">
+        <v>126</v>
+      </c>
+      <c t="s" r="J144" s="7">
+        <v>233</v>
+      </c>
+      <c t="s" r="K144" s="7">
+        <v>139</v>
+      </c>
       <c r="L144" s="7"/>
-      <c r="M144" s="7"/>
+      <c t="s" r="M144" s="7">
+        <v>209</v>
+      </c>
     </row>
     <row r="145" ht="15" customHeight="1">
       <c t="s" r="A145" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B145" s="7">
-        <v>933</v>
+        <v>5069</v>
       </c>
       <c t="s" r="C145" s="7">
-        <v>14</v>
+        <v>207</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>46</v>
+        <v>232</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>51</v>
+        <v>234</v>
       </c>
       <c t="s" r="J145" s="7">
+        <v>235</v>
+      </c>
+      <c t="s" r="K145" s="7">
+        <v>236</v>
+      </c>
+      <c r="L145" s="7"/>
+      <c t="s" r="M145" s="7">
         <v>237</v>
       </c>
-      <c r="K145" s="7"/>
-      <c r="L145" s="7"/>
-      <c r="M145" s="7"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c t="s" r="A146" s="6">
-        <v>13</v>
-      </c>
-      <c r="B146" s="7">
-        <v>525</v>
-      </c>
-      <c t="s" r="C146" s="7">
-        <v>14</v>
-      </c>
+      <c r="A146" s="6"/>
+      <c r="B146" s="7"/>
+      <c r="C146" s="7"/>
       <c r="D146" s="7"/>
-      <c t="s" r="E146" s="7">
-        <v>236</v>
-      </c>
-      <c r="F146" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G146" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H146" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="I146" s="7">
-        <v>66</v>
-      </c>
-      <c t="s" r="J146" s="7">
-        <v>113</v>
-      </c>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7"/>
+      <c r="G146" s="8"/>
+      <c r="H146" s="8"/>
+      <c r="I146" s="7"/>
+      <c r="J146" s="7"/>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c r="M146" s="7"/>
@@ -5997,29 +6001,29 @@
         <v>13</v>
       </c>
       <c r="B147" s="7">
-        <v>528</v>
+        <v>933</v>
       </c>
       <c t="s" r="C147" s="7">
         <v>14</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>33</v>
+        <v>239</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6030,14 +6034,14 @@
         <v>13</v>
       </c>
       <c r="B148" s="7">
-        <v>1157</v>
+        <v>525</v>
       </c>
       <c t="s" r="C148" s="7">
         <v>14</v>
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6046,13 +6050,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6063,45 +6067,63 @@
         <v>13</v>
       </c>
       <c r="B149" s="7">
-        <v>1156</v>
+        <v>528</v>
       </c>
       <c t="s" r="C149" s="7">
         <v>14</v>
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>238</v>
+        <v>125</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c r="M149" s="7"/>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="6"/>
-      <c r="B150" s="7"/>
-      <c r="C150" s="7"/>
+      <c t="s" r="A150" s="6">
+        <v>13</v>
+      </c>
+      <c r="B150" s="7">
+        <v>1157</v>
+      </c>
+      <c t="s" r="C150" s="7">
+        <v>14</v>
+      </c>
       <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
-      <c r="G150" s="8"/>
-      <c r="H150" s="8"/>
-      <c r="I150" s="7"/>
-      <c r="J150" s="7"/>
+      <c t="s" r="E150" s="7">
+        <v>238</v>
+      </c>
+      <c r="F150" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G150" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H150" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I150" s="7">
+        <v>200</v>
+      </c>
+      <c t="s" r="J150" s="7">
+        <v>116</v>
+      </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c r="M150" s="7"/>
@@ -6111,63 +6133,45 @@
         <v>13</v>
       </c>
       <c r="B151" s="7">
-        <v>503</v>
+        <v>1156</v>
       </c>
       <c t="s" r="C151" s="7">
         <v>14</v>
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H151" s="8">
         <v>40</v>
       </c>
-      <c t="s" r="H151" s="8">
-        <v>155</v>
-      </c>
       <c t="s" r="I151" s="7">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c t="s" r="A152" s="6">
-        <v>13</v>
-      </c>
-      <c r="B152" s="7">
-        <v>524</v>
-      </c>
-      <c t="s" r="C152" s="7">
-        <v>14</v>
-      </c>
+      <c r="A152" s="6"/>
+      <c r="B152" s="7"/>
+      <c r="C152" s="7"/>
       <c r="D152" s="7"/>
-      <c t="s" r="E152" s="7">
-        <v>239</v>
-      </c>
-      <c r="F152" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G152" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="H152" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I152" s="7">
-        <v>64</v>
-      </c>
-      <c t="s" r="J152" s="7">
-        <v>171</v>
-      </c>
+      <c r="E152" s="7"/>
+      <c r="F152" s="7"/>
+      <c r="G152" s="8"/>
+      <c r="H152" s="8"/>
+      <c r="I152" s="7"/>
+      <c r="J152" s="7"/>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c r="M152" s="7"/>
@@ -6177,14 +6181,14 @@
         <v>13</v>
       </c>
       <c r="B153" s="7">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c t="s" r="C153" s="7">
         <v>14</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6196,10 +6200,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>228</v>
+        <v>88</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6210,14 +6214,14 @@
         <v>13</v>
       </c>
       <c r="B154" s="7">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c t="s" r="C154" s="7">
         <v>14</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6229,10 +6233,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>240</v>
+        <v>64</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6243,14 +6247,14 @@
         <v>13</v>
       </c>
       <c r="B155" s="7">
-        <v>913</v>
+        <v>507</v>
       </c>
       <c t="s" r="C155" s="7">
         <v>14</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6259,13 +6263,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>241</v>
+        <v>155</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6276,20 +6280,20 @@
         <v>13</v>
       </c>
       <c r="B156" s="7">
-        <v>914</v>
+        <v>510</v>
       </c>
       <c t="s" r="C156" s="7">
         <v>14</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>241</v>
+        <v>155</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>40</v>
@@ -6298,7 +6302,7 @@
         <v>242</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>243</v>
+        <v>32</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6309,14 +6313,14 @@
         <v>13</v>
       </c>
       <c r="B157" s="7">
-        <v>962</v>
+        <v>913</v>
       </c>
       <c t="s" r="C157" s="7">
         <v>14</v>
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6325,29 +6329,47 @@
         <v>40</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>106</v>
+        <v>243</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>244</v>
+        <v>56</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c r="M157" s="7"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="6"/>
-      <c r="B158" s="7"/>
-      <c r="C158" s="7"/>
+      <c t="s" r="A158" s="6">
+        <v>13</v>
+      </c>
+      <c r="B158" s="7">
+        <v>914</v>
+      </c>
+      <c t="s" r="C158" s="7">
+        <v>14</v>
+      </c>
       <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
-      <c r="G158" s="8"/>
-      <c r="H158" s="8"/>
-      <c r="I158" s="7"/>
-      <c r="J158" s="7"/>
+      <c t="s" r="E158" s="7">
+        <v>241</v>
+      </c>
+      <c r="F158" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G158" s="8">
+        <v>243</v>
+      </c>
+      <c t="s" r="H158" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I158" s="7">
+        <v>244</v>
+      </c>
+      <c t="s" r="J158" s="7">
+        <v>245</v>
+      </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c r="M158" s="7"/>
@@ -6357,63 +6379,45 @@
         <v>13</v>
       </c>
       <c r="B159" s="7">
-        <v>886</v>
+        <v>962</v>
       </c>
       <c t="s" r="C159" s="7">
         <v>14</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
+        <v>241</v>
+      </c>
+      <c r="F159" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G159" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H159" s="8">
+        <v>106</v>
+      </c>
+      <c t="s" r="I159" s="7">
         <v>246</v>
       </c>
-      <c r="F159" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G159" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H159" s="8">
-        <v>217</v>
-      </c>
-      <c t="s" r="I159" s="7">
-        <v>146</v>
-      </c>
       <c t="s" r="J159" s="7">
-        <v>184</v>
+        <v>247</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c r="M159" s="7"/>
     </row>
     <row r="160" ht="15" customHeight="1">
-      <c t="s" r="A160" s="6">
-        <v>13</v>
-      </c>
-      <c r="B160" s="7">
-        <v>885</v>
-      </c>
-      <c t="s" r="C160" s="7">
-        <v>14</v>
-      </c>
+      <c r="A160" s="6"/>
+      <c r="B160" s="7"/>
+      <c r="C160" s="7"/>
       <c r="D160" s="7"/>
-      <c t="s" r="E160" s="7">
-        <v>246</v>
-      </c>
-      <c r="F160" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G160" s="8">
-        <v>217</v>
-      </c>
-      <c t="s" r="H160" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I160" s="7">
-        <v>182</v>
-      </c>
-      <c t="s" r="J160" s="7">
-        <v>247</v>
-      </c>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
+      <c r="G160" s="8"/>
+      <c r="H160" s="8"/>
+      <c r="I160" s="7"/>
+      <c r="J160" s="7"/>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
@@ -6423,14 +6427,14 @@
         <v>13</v>
       </c>
       <c r="B161" s="7">
-        <v>148</v>
+        <v>886</v>
       </c>
       <c t="s" r="C161" s="7">
         <v>14</v>
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6439,13 +6443,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>40</v>
+        <v>220</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6456,26 +6460,26 @@
         <v>13</v>
       </c>
       <c r="B162" s="7">
-        <v>155</v>
+        <v>885</v>
       </c>
       <c t="s" r="C162" s="7">
         <v>14</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>40</v>
+        <v>220</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>69</v>
+        <v>182</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>249</v>
@@ -6485,16 +6489,34 @@
       <c r="M162" s="7"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
-      <c r="A163" s="6"/>
-      <c r="B163" s="7"/>
-      <c r="C163" s="7"/>
+      <c t="s" r="A163" s="6">
+        <v>13</v>
+      </c>
+      <c r="B163" s="7">
+        <v>148</v>
+      </c>
+      <c t="s" r="C163" s="7">
+        <v>14</v>
+      </c>
       <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7"/>
-      <c r="G163" s="8"/>
-      <c r="H163" s="8"/>
-      <c r="I163" s="7"/>
-      <c r="J163" s="7"/>
+      <c t="s" r="E163" s="7">
+        <v>248</v>
+      </c>
+      <c r="F163" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G163" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H163" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I163" s="7">
+        <v>67</v>
+      </c>
+      <c t="s" r="J163" s="7">
+        <v>250</v>
+      </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
@@ -6504,177 +6526,159 @@
         <v>13</v>
       </c>
       <c r="B164" s="7">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c t="s" r="C164" s="7">
-        <v>250</v>
+        <v>14</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
+        <v>248</v>
+      </c>
+      <c r="F164" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G164" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H164" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I164" s="7">
+        <v>69</v>
+      </c>
+      <c t="s" r="J164" s="7">
         <v>251</v>
-      </c>
-      <c r="F164" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G164" s="8">
-        <v>252</v>
-      </c>
-      <c t="s" r="H164" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I164" s="7">
-        <v>139</v>
-      </c>
-      <c t="s" r="J164" s="7">
-        <v>116</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c r="M164" s="7"/>
     </row>
     <row r="165" ht="15" customHeight="1">
-      <c t="s" r="A165" s="6">
-        <v>13</v>
-      </c>
-      <c r="B165" s="7">
-        <v>163</v>
-      </c>
-      <c t="s" r="C165" s="7">
-        <v>14</v>
-      </c>
+      <c r="A165" s="6"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="7"/>
       <c r="D165" s="7"/>
-      <c t="s" r="E165" s="7">
-        <v>251</v>
-      </c>
-      <c r="F165" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G165" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H165" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I165" s="7">
-        <v>192</v>
-      </c>
-      <c t="s" r="J165" s="7">
-        <v>188</v>
-      </c>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="8"/>
+      <c r="H165" s="8"/>
+      <c r="I165" s="7"/>
+      <c r="J165" s="7"/>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c r="M165" s="7"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c t="s" r="A166" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B166" s="7">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c t="s" r="C166" s="7">
-        <v>14</v>
+        <v>252</v>
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>29</v>
+        <v>254</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>253</v>
+        <v>40</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c r="M166" s="7"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
-      <c r="A167" s="6"/>
-      <c r="B167" s="7"/>
-      <c r="C167" s="7"/>
+      <c t="s" r="A167" s="6">
+        <v>13</v>
+      </c>
+      <c r="B167" s="7">
+        <v>163</v>
+      </c>
+      <c t="s" r="C167" s="7">
+        <v>14</v>
+      </c>
       <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
-      <c r="G167" s="8"/>
-      <c r="H167" s="8"/>
-      <c r="I167" s="7"/>
-      <c r="J167" s="7"/>
+      <c t="s" r="E167" s="7">
+        <v>253</v>
+      </c>
+      <c r="F167" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G167" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H167" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I167" s="7">
+        <v>193</v>
+      </c>
+      <c t="s" r="J167" s="7">
+        <v>189</v>
+      </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c r="M167" s="7"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
       <c t="s" r="A168" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B168" s="7">
-        <v>633</v>
+        <v>91</v>
       </c>
       <c t="s" r="C168" s="7">
         <v>14</v>
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>29</v>
+        <v>255</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>247</v>
+        <v>102</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c r="M168" s="7"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c t="s" r="A169" s="6">
-        <v>13</v>
-      </c>
-      <c r="B169" s="7">
-        <v>394</v>
-      </c>
-      <c t="s" r="C169" s="7">
-        <v>14</v>
-      </c>
+      <c r="A169" s="6"/>
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
       <c r="D169" s="7"/>
-      <c t="s" r="E169" s="7">
-        <v>254</v>
-      </c>
-      <c r="F169" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G169" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H169" s="8">
-        <v>255</v>
-      </c>
-      <c t="s" r="I169" s="7">
-        <v>80</v>
-      </c>
-      <c t="s" r="J169" s="7">
-        <v>218</v>
-      </c>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7"/>
+      <c r="G169" s="8"/>
+      <c r="H169" s="8"/>
+      <c r="I169" s="7"/>
+      <c r="J169" s="7"/>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
@@ -6684,29 +6688,29 @@
         <v>13</v>
       </c>
       <c r="B170" s="7">
-        <v>395</v>
+        <v>633</v>
       </c>
       <c t="s" r="C170" s="7">
         <v>14</v>
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>255</v>
+        <v>155</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>256</v>
+        <v>95</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6717,14 +6721,14 @@
         <v>13</v>
       </c>
       <c r="B171" s="7">
-        <v>3908</v>
+        <v>394</v>
       </c>
       <c t="s" r="C171" s="7">
         <v>14</v>
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6736,10 +6740,10 @@
         <v>257</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>258</v>
+        <v>80</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>259</v>
+        <v>221</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6747,17 +6751,17 @@
     </row>
     <row r="172" ht="14.25" customHeight="1">
       <c t="s" r="A172" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B172" s="7">
-        <v>3909</v>
+        <v>395</v>
       </c>
       <c t="s" r="C172" s="7">
         <v>14</v>
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6769,92 +6773,92 @@
         <v>29</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c r="M172" s="7"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
-      <c r="A173" s="6"/>
-      <c r="B173" s="7"/>
-      <c r="C173" s="7"/>
+      <c t="s" r="A173" s="6">
+        <v>13</v>
+      </c>
+      <c r="B173" s="7">
+        <v>3908</v>
+      </c>
+      <c t="s" r="C173" s="7">
+        <v>14</v>
+      </c>
       <c r="D173" s="7"/>
-      <c r="E173" s="7"/>
-      <c r="F173" s="7"/>
-      <c r="G173" s="8"/>
-      <c r="H173" s="8"/>
-      <c r="I173" s="7"/>
-      <c r="J173" s="7"/>
+      <c t="s" r="E173" s="7">
+        <v>256</v>
+      </c>
+      <c r="F173" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G173" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H173" s="8">
+        <v>259</v>
+      </c>
+      <c t="s" r="I173" s="7">
+        <v>260</v>
+      </c>
+      <c t="s" r="J173" s="7">
+        <v>261</v>
+      </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c r="M173" s="7"/>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c t="s" r="A174" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B174" s="7">
-        <v>989</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C174" s="7">
         <v>14</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
+        <v>256</v>
+      </c>
+      <c r="F174" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G174" s="8">
+        <v>259</v>
+      </c>
+      <c t="s" r="H174" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I174" s="7">
         <v>262</v>
       </c>
-      <c r="F174" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G174" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H174" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="I174" s="7">
+      <c t="s" r="J174" s="7">
         <v>263</v>
-      </c>
-      <c t="s" r="J174" s="7">
-        <v>147</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c r="M174" s="7"/>
     </row>
     <row r="175" ht="15" customHeight="1">
-      <c t="s" r="A175" s="6">
-        <v>13</v>
-      </c>
-      <c r="B175" s="7">
-        <v>973</v>
-      </c>
-      <c t="s" r="C175" s="7">
-        <v>14</v>
-      </c>
+      <c r="A175" s="6"/>
+      <c r="B175" s="7"/>
+      <c r="C175" s="7"/>
       <c r="D175" s="7"/>
-      <c t="s" r="E175" s="7">
-        <v>262</v>
-      </c>
-      <c r="F175" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G175" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="H175" s="8">
-        <v>111</v>
-      </c>
-      <c t="s" r="I175" s="7">
-        <v>222</v>
-      </c>
-      <c t="s" r="J175" s="7">
-        <v>159</v>
-      </c>
+      <c r="E175" s="7"/>
+      <c r="F175" s="7"/>
+      <c r="G175" s="8"/>
+      <c r="H175" s="8"/>
+      <c r="I175" s="7"/>
+      <c r="J175" s="7"/>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c r="M175" s="7"/>
@@ -6864,29 +6868,29 @@
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>814</v>
+        <v>989</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6897,29 +6901,29 @@
         <v>13</v>
       </c>
       <c r="B177" s="7">
-        <v>1216</v>
+        <v>973</v>
       </c>
       <c t="s" r="C177" s="7">
         <v>14</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>22</v>
+        <v>225</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6930,45 +6934,63 @@
         <v>13</v>
       </c>
       <c r="B178" s="7">
-        <v>1217</v>
+        <v>814</v>
       </c>
       <c t="s" r="C178" s="7">
         <v>14</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c r="M178" s="7"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
-      <c r="A179" s="6"/>
-      <c r="B179" s="7"/>
-      <c r="C179" s="7"/>
+      <c t="s" r="A179" s="6">
+        <v>13</v>
+      </c>
+      <c r="B179" s="7">
+        <v>1216</v>
+      </c>
+      <c t="s" r="C179" s="7">
+        <v>14</v>
+      </c>
       <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
-      <c r="F179" s="7"/>
-      <c r="G179" s="8"/>
-      <c r="H179" s="8"/>
-      <c r="I179" s="7"/>
-      <c r="J179" s="7"/>
+      <c t="s" r="E179" s="7">
+        <v>264</v>
+      </c>
+      <c r="F179" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G179" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H179" s="8">
+        <v>53</v>
+      </c>
+      <c t="s" r="I179" s="7">
+        <v>22</v>
+      </c>
+      <c t="s" r="J179" s="7">
+        <v>72</v>
+      </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c r="M179" s="7"/>
@@ -6978,63 +7000,45 @@
         <v>13</v>
       </c>
       <c r="B180" s="7">
-        <v>421</v>
+        <v>1217</v>
       </c>
       <c t="s" r="C180" s="7">
         <v>14</v>
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>255</v>
+        <v>29</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c r="M180" s="7"/>
     </row>
     <row r="181" ht="14.25" customHeight="1">
-      <c t="s" r="A181" s="6">
-        <v>13</v>
-      </c>
-      <c r="B181" s="7">
-        <v>422</v>
-      </c>
-      <c t="s" r="C181" s="7">
-        <v>14</v>
-      </c>
+      <c r="A181" s="6"/>
+      <c r="B181" s="7"/>
+      <c r="C181" s="7"/>
       <c r="D181" s="7"/>
-      <c t="s" r="E181" s="7">
-        <v>266</v>
-      </c>
-      <c r="F181" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G181" s="8">
-        <v>255</v>
-      </c>
-      <c t="s" r="H181" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I181" s="7">
-        <v>170</v>
-      </c>
-      <c t="s" r="J181" s="7">
-        <v>76</v>
-      </c>
+      <c r="E181" s="7"/>
+      <c r="F181" s="7"/>
+      <c r="G181" s="8"/>
+      <c r="H181" s="8"/>
+      <c r="I181" s="7"/>
+      <c r="J181" s="7"/>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c r="M181" s="7"/>
@@ -7044,14 +7048,14 @@
         <v>13</v>
       </c>
       <c r="B182" s="7">
-        <v>133</v>
+        <v>421</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7060,13 +7064,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>29</v>
+        <v>257</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7077,29 +7081,29 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>140</v>
+        <v>422</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>29</v>
+        <v>257</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>268</v>
+        <v>170</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7110,14 +7114,14 @@
         <v>13</v>
       </c>
       <c r="B184" s="7">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c t="s" r="C184" s="7">
         <v>14</v>
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7132,7 +7136,7 @@
         <v>269</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7143,14 +7147,14 @@
         <v>13</v>
       </c>
       <c r="B185" s="7">
-        <v>648</v>
+        <v>140</v>
       </c>
       <c t="s" r="C185" s="7">
         <v>14</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7159,13 +7163,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c t="s" r="I185" s="7">
         <v>270</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7176,20 +7180,20 @@
         <v>13</v>
       </c>
       <c r="B186" s="7">
-        <v>647</v>
+        <v>151</v>
       </c>
       <c t="s" r="C186" s="7">
         <v>14</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>29</v>
@@ -7198,23 +7202,41 @@
         <v>271</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>244</v>
+        <v>139</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c r="M186" s="7"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
-      <c r="A187" s="6"/>
-      <c r="B187" s="7"/>
-      <c r="C187" s="7"/>
+      <c t="s" r="A187" s="6">
+        <v>13</v>
+      </c>
+      <c r="B187" s="7">
+        <v>648</v>
+      </c>
+      <c t="s" r="C187" s="7">
+        <v>14</v>
+      </c>
       <c r="D187" s="7"/>
-      <c r="E187" s="7"/>
-      <c r="F187" s="7"/>
-      <c r="G187" s="8"/>
-      <c r="H187" s="8"/>
-      <c r="I187" s="7"/>
-      <c r="J187" s="7"/>
+      <c t="s" r="E187" s="7">
+        <v>268</v>
+      </c>
+      <c r="F187" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G187" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H187" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="I187" s="7">
+        <v>272</v>
+      </c>
+      <c t="s" r="J187" s="7">
+        <v>129</v>
+      </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c r="M187" s="7"/>
@@ -7224,63 +7246,45 @@
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>905</v>
+        <v>647</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c t="s" r="I188" s="7">
         <v>273</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>112</v>
+        <v>246</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c r="M188" s="7"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c t="s" r="A189" s="6">
-        <v>13</v>
-      </c>
-      <c r="B189" s="7">
-        <v>906</v>
-      </c>
-      <c t="s" r="C189" s="7">
-        <v>14</v>
-      </c>
+      <c r="A189" s="6"/>
+      <c r="B189" s="7"/>
+      <c r="C189" s="7"/>
       <c r="D189" s="7"/>
-      <c t="s" r="E189" s="7">
-        <v>272</v>
-      </c>
-      <c r="F189" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G189" s="8">
-        <v>97</v>
-      </c>
-      <c t="s" r="H189" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I189" s="7">
-        <v>228</v>
-      </c>
-      <c t="s" r="J189" s="7">
-        <v>123</v>
-      </c>
+      <c r="E189" s="7"/>
+      <c r="F189" s="7"/>
+      <c r="G189" s="8"/>
+      <c r="H189" s="8"/>
+      <c r="I189" s="7"/>
+      <c r="J189" s="7"/>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c r="M189" s="7"/>
@@ -7290,14 +7294,14 @@
         <v>13</v>
       </c>
       <c r="B190" s="7">
-        <v>567</v>
+        <v>905</v>
       </c>
       <c t="s" r="C190" s="7">
         <v>14</v>
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7306,13 +7310,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>274</v>
+        <v>112</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7323,29 +7327,29 @@
         <v>13</v>
       </c>
       <c r="B191" s="7">
-        <v>568</v>
+        <v>906</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7356,14 +7360,14 @@
         <v>13</v>
       </c>
       <c r="B192" s="7">
-        <v>519</v>
+        <v>567</v>
       </c>
       <c t="s" r="C192" s="7">
         <v>14</v>
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7372,13 +7376,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>199</v>
+        <v>276</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7389,45 +7393,63 @@
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>522</v>
+        <v>568</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>187</v>
+        <v>69</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c r="M193" s="7"/>
     </row>
     <row r="194" ht="14.25" customHeight="1">
-      <c r="A194" s="6"/>
-      <c r="B194" s="7"/>
-      <c r="C194" s="7"/>
+      <c t="s" r="A194" s="6">
+        <v>13</v>
+      </c>
+      <c r="B194" s="7">
+        <v>519</v>
+      </c>
+      <c t="s" r="C194" s="7">
+        <v>14</v>
+      </c>
       <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
-      <c r="G194" s="8"/>
-      <c r="H194" s="8"/>
-      <c r="I194" s="7"/>
-      <c r="J194" s="7"/>
+      <c t="s" r="E194" s="7">
+        <v>274</v>
+      </c>
+      <c r="F194" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G194" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H194" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="I194" s="7">
+        <v>35</v>
+      </c>
+      <c t="s" r="J194" s="7">
+        <v>176</v>
+      </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c r="M194" s="7"/>
@@ -7437,63 +7459,45 @@
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>1362</v>
+        <v>522</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>104</v>
+        <v>278</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c r="M195" s="7"/>
     </row>
     <row r="196" ht="14.25" customHeight="1">
-      <c t="s" r="A196" s="6">
-        <v>13</v>
-      </c>
-      <c r="B196" s="7">
-        <v>1363</v>
-      </c>
-      <c t="s" r="C196" s="7">
-        <v>14</v>
-      </c>
+      <c r="A196" s="6"/>
+      <c r="B196" s="7"/>
+      <c r="C196" s="7"/>
       <c r="D196" s="7"/>
-      <c t="s" r="E196" s="7">
-        <v>277</v>
-      </c>
-      <c r="F196" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G196" s="8">
-        <v>122</v>
-      </c>
-      <c t="s" r="H196" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I196" s="7">
-        <v>108</v>
-      </c>
-      <c t="s" r="J196" s="7">
-        <v>110</v>
-      </c>
+      <c r="E196" s="7"/>
+      <c r="F196" s="7"/>
+      <c r="G196" s="8"/>
+      <c r="H196" s="8"/>
+      <c r="I196" s="7"/>
+      <c r="J196" s="7"/>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c r="M196" s="7"/>
@@ -7503,14 +7507,14 @@
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>337</v>
+        <v>1362</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7519,13 +7523,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7536,29 +7540,29 @@
         <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>324</v>
+        <v>1363</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7569,14 +7573,14 @@
         <v>13</v>
       </c>
       <c r="B199" s="7">
-        <v>807</v>
+        <v>337</v>
       </c>
       <c t="s" r="C199" s="7">
         <v>14</v>
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7585,13 +7589,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>278</v>
+        <v>70</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>240</v>
+        <v>64</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>279</v>
+        <v>156</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7602,29 +7606,29 @@
         <v>13</v>
       </c>
       <c r="B200" s="7">
-        <v>800</v>
+        <v>324</v>
       </c>
       <c t="s" r="C200" s="7">
         <v>14</v>
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>278</v>
+        <v>70</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>280</v>
+        <v>121</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7635,14 +7639,14 @@
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>154</v>
+        <v>807</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7651,29 +7655,47 @@
         <v>29</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>40</v>
+        <v>280</v>
       </c>
       <c t="s" r="I201" s="7">
+        <v>242</v>
+      </c>
+      <c t="s" r="J201" s="7">
         <v>281</v>
-      </c>
-      <c t="s" r="J201" s="7">
-        <v>140</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c r="M201" s="7"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c r="A202" s="6"/>
-      <c r="B202" s="7"/>
-      <c r="C202" s="7"/>
+      <c t="s" r="A202" s="6">
+        <v>13</v>
+      </c>
+      <c r="B202" s="7">
+        <v>800</v>
+      </c>
+      <c t="s" r="C202" s="7">
+        <v>14</v>
+      </c>
       <c r="D202" s="7"/>
-      <c r="E202" s="7"/>
-      <c r="F202" s="7"/>
-      <c r="G202" s="8"/>
-      <c r="H202" s="8"/>
-      <c r="I202" s="7"/>
-      <c r="J202" s="7"/>
+      <c t="s" r="E202" s="7">
+        <v>279</v>
+      </c>
+      <c r="F202" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G202" s="8">
+        <v>280</v>
+      </c>
+      <c t="s" r="H202" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I202" s="7">
+        <v>282</v>
+      </c>
+      <c t="s" r="J202" s="7">
+        <v>149</v>
+      </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c r="M202" s="7"/>
@@ -7683,63 +7705,45 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H203" s="8">
         <v>40</v>
       </c>
-      <c t="s" r="H203" s="8">
-        <v>29</v>
-      </c>
       <c t="s" r="I203" s="7">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>283</v>
+        <v>140</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c r="M203" s="7"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
-      <c t="s" r="A204" s="6">
-        <v>13</v>
-      </c>
-      <c r="B204" s="7">
-        <v>130</v>
-      </c>
-      <c t="s" r="C204" s="7">
-        <v>14</v>
-      </c>
+      <c r="A204" s="6"/>
+      <c r="B204" s="7"/>
+      <c r="C204" s="7"/>
       <c r="D204" s="7"/>
-      <c t="s" r="E204" s="7">
-        <v>282</v>
-      </c>
-      <c r="F204" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G204" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H204" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I204" s="7">
-        <v>209</v>
-      </c>
-      <c t="s" r="J204" s="7">
-        <v>76</v>
-      </c>
+      <c r="E204" s="7"/>
+      <c r="F204" s="7"/>
+      <c r="G204" s="8"/>
+      <c r="H204" s="8"/>
+      <c r="I204" s="7"/>
+      <c r="J204" s="7"/>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c r="M204" s="7"/>
@@ -7749,14 +7753,14 @@
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>1491</v>
+        <v>123</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7765,13 +7769,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>52</v>
+        <v>285</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7782,29 +7786,29 @@
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>1492</v>
+        <v>130</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>284</v>
+        <v>76</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7815,14 +7819,14 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>405</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7831,13 +7835,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>94</v>
+        <v>269</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7848,29 +7852,29 @@
         <v>13</v>
       </c>
       <c r="B208" s="7">
-        <v>406</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>226</v>
+        <v>286</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7881,14 +7885,14 @@
         <v>13</v>
       </c>
       <c r="B209" s="7">
-        <v>169</v>
+        <v>405</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7897,29 +7901,47 @@
         <v>40</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>285</v>
+        <v>94</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>286</v>
+        <v>45</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c r="M209" s="7"/>
     </row>
     <row r="210" ht="15" customHeight="1">
-      <c r="A210" s="6"/>
-      <c r="B210" s="7"/>
-      <c r="C210" s="7"/>
+      <c t="s" r="A210" s="6">
+        <v>13</v>
+      </c>
+      <c r="B210" s="7">
+        <v>406</v>
+      </c>
+      <c t="s" r="C210" s="7">
+        <v>14</v>
+      </c>
       <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
-      <c r="G210" s="8"/>
-      <c r="H210" s="8"/>
-      <c r="I210" s="7"/>
-      <c r="J210" s="7"/>
+      <c t="s" r="E210" s="7">
+        <v>284</v>
+      </c>
+      <c r="F210" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G210" s="8">
+        <v>122</v>
+      </c>
+      <c t="s" r="H210" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I210" s="7">
+        <v>127</v>
+      </c>
+      <c t="s" r="J210" s="7">
+        <v>229</v>
+      </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c r="M210" s="7"/>
@@ -7929,26 +7951,26 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>849</v>
+        <v>169</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
+        <v>284</v>
+      </c>
+      <c r="F211" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G211" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H211" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I211" s="7">
         <v>287</v>
-      </c>
-      <c r="F211" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G211" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H211" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I211" s="7">
-        <v>162</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>288</v>
@@ -7958,34 +7980,16 @@
       <c r="M211" s="7"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
-      <c t="s" r="A212" s="6">
-        <v>13</v>
-      </c>
-      <c r="B212" s="7">
-        <v>848</v>
-      </c>
-      <c t="s" r="C212" s="7">
-        <v>14</v>
-      </c>
+      <c r="A212" s="6"/>
+      <c r="B212" s="7"/>
+      <c r="C212" s="7"/>
       <c r="D212" s="7"/>
-      <c t="s" r="E212" s="7">
-        <v>287</v>
-      </c>
-      <c r="F212" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G212" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H212" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I212" s="7">
-        <v>54</v>
-      </c>
-      <c t="s" r="J212" s="7">
-        <v>269</v>
-      </c>
+      <c r="E212" s="7"/>
+      <c r="F212" s="7"/>
+      <c r="G212" s="8"/>
+      <c r="H212" s="8"/>
+      <c r="I212" s="7"/>
+      <c r="J212" s="7"/>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c r="M212" s="7"/>
@@ -7995,14 +7999,14 @@
         <v>13</v>
       </c>
       <c r="B213" s="7">
-        <v>3900</v>
+        <v>849</v>
       </c>
       <c t="s" r="C213" s="7">
         <v>14</v>
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8011,13 +8015,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>289</v>
+        <v>30</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>270</v>
+        <v>162</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>102</v>
+        <v>290</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8025,77 +8029,95 @@
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c t="s" r="A214" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>3901</v>
+        <v>848</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>289</v>
+        <v>30</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>234</v>
+        <v>54</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c r="M214" s="7"/>
     </row>
     <row r="215" ht="15" customHeight="1">
-      <c r="A215" s="6"/>
-      <c r="B215" s="7"/>
-      <c r="C215" s="7"/>
+      <c t="s" r="A215" s="6">
+        <v>13</v>
+      </c>
+      <c r="B215" s="7">
+        <v>3900</v>
+      </c>
+      <c t="s" r="C215" s="7">
+        <v>14</v>
+      </c>
       <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
-      <c r="F215" s="7"/>
-      <c r="G215" s="8"/>
-      <c r="H215" s="8"/>
-      <c r="I215" s="7"/>
-      <c r="J215" s="7"/>
+      <c t="s" r="E215" s="7">
+        <v>289</v>
+      </c>
+      <c r="F215" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G215" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H215" s="8">
+        <v>291</v>
+      </c>
+      <c t="s" r="I215" s="7">
+        <v>272</v>
+      </c>
+      <c t="s" r="J215" s="7">
+        <v>102</v>
+      </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c r="M215" s="7"/>
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c t="s" r="A216" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B216" s="7">
-        <v>449</v>
+        <v>3901</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
+        <v>289</v>
+      </c>
+      <c r="F216" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G216" s="8">
         <v>291</v>
       </c>
-      <c r="F216" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G216" s="8">
-        <v>40</v>
-      </c>
       <c t="s" r="H216" s="8">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>62</v>
+        <v>236</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>292</v>
@@ -8105,34 +8127,16 @@
       <c r="M216" s="7"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
-      <c t="s" r="A217" s="6">
-        <v>13</v>
-      </c>
-      <c r="B217" s="7">
-        <v>450</v>
-      </c>
-      <c t="s" r="C217" s="7">
-        <v>14</v>
-      </c>
+      <c r="A217" s="6"/>
+      <c r="B217" s="7"/>
+      <c r="C217" s="7"/>
       <c r="D217" s="7"/>
-      <c t="s" r="E217" s="7">
-        <v>291</v>
-      </c>
-      <c r="F217" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G217" s="8">
-        <v>70</v>
-      </c>
-      <c t="s" r="H217" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I217" s="7">
-        <v>293</v>
-      </c>
-      <c t="s" r="J217" s="7">
-        <v>203</v>
-      </c>
+      <c r="E217" s="7"/>
+      <c r="F217" s="7"/>
+      <c r="G217" s="8"/>
+      <c r="H217" s="8"/>
+      <c r="I217" s="7"/>
+      <c r="J217" s="7"/>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c r="M217" s="7"/>
@@ -8142,14 +8146,14 @@
         <v>13</v>
       </c>
       <c r="B218" s="7">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c t="s" r="C218" s="7">
         <v>14</v>
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8161,10 +8165,10 @@
         <v>70</v>
       </c>
       <c t="s" r="I218" s="7">
+        <v>62</v>
+      </c>
+      <c t="s" r="J218" s="7">
         <v>294</v>
-      </c>
-      <c t="s" r="J218" s="7">
-        <v>295</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8175,14 +8179,14 @@
         <v>13</v>
       </c>
       <c r="B219" s="7">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c t="s" r="C219" s="7">
         <v>14</v>
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8194,10 +8198,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>32</v>
+        <v>295</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>68</v>
+        <v>206</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8208,14 +8212,14 @@
         <v>13</v>
       </c>
       <c r="B220" s="7">
-        <v>517</v>
+        <v>451</v>
       </c>
       <c t="s" r="C220" s="7">
         <v>14</v>
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8224,13 +8228,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>150</v>
+        <v>296</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8241,45 +8245,63 @@
         <v>13</v>
       </c>
       <c r="B221" s="7">
-        <v>520</v>
+        <v>454</v>
       </c>
       <c t="s" r="C221" s="7">
         <v>14</v>
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c r="M221" s="7"/>
     </row>
     <row r="222" ht="14.25" customHeight="1">
-      <c r="A222" s="6"/>
-      <c r="B222" s="7"/>
-      <c r="C222" s="7"/>
+      <c t="s" r="A222" s="6">
+        <v>13</v>
+      </c>
+      <c r="B222" s="7">
+        <v>517</v>
+      </c>
+      <c t="s" r="C222" s="7">
+        <v>14</v>
+      </c>
       <c r="D222" s="7"/>
-      <c r="E222" s="7"/>
-      <c r="F222" s="7"/>
-      <c r="G222" s="8"/>
-      <c r="H222" s="8"/>
-      <c r="I222" s="7"/>
-      <c r="J222" s="7"/>
+      <c t="s" r="E222" s="7">
+        <v>293</v>
+      </c>
+      <c r="F222" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G222" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H222" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="I222" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="J222" s="7">
+        <v>244</v>
+      </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c r="M222" s="7"/>
@@ -8289,63 +8311,45 @@
         <v>13</v>
       </c>
       <c r="B223" s="7">
-        <v>350</v>
+        <v>520</v>
       </c>
       <c t="s" r="C223" s="7">
         <v>14</v>
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>168</v>
+        <v>40</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c r="M223" s="7"/>
     </row>
     <row r="224" ht="14.25" customHeight="1">
-      <c t="s" r="A224" s="6">
-        <v>13</v>
-      </c>
-      <c r="B224" s="7">
-        <v>351</v>
-      </c>
-      <c t="s" r="C224" s="7">
-        <v>14</v>
-      </c>
+      <c r="A224" s="6"/>
+      <c r="B224" s="7"/>
+      <c r="C224" s="7"/>
       <c r="D224" s="7"/>
-      <c t="s" r="E224" s="7">
-        <v>296</v>
-      </c>
-      <c r="F224" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G224" s="8">
-        <v>168</v>
-      </c>
-      <c t="s" r="H224" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I224" s="7">
-        <v>48</v>
-      </c>
-      <c t="s" r="J224" s="7">
-        <v>120</v>
-      </c>
+      <c r="E224" s="7"/>
+      <c r="F224" s="7"/>
+      <c r="G224" s="8"/>
+      <c r="H224" s="8"/>
+      <c r="I224" s="7"/>
+      <c r="J224" s="7"/>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c r="M224" s="7"/>
@@ -8355,14 +8359,14 @@
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>274</v>
+        <v>124</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8371,13 +8375,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>298</v>
+        <v>237</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8388,29 +8392,29 @@
         <v>13</v>
       </c>
       <c r="B226" s="7">
-        <v>275</v>
+        <v>129</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>228</v>
+        <v>31</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8421,14 +8425,14 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>254</v>
+        <v>210</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8437,13 +8441,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8454,29 +8458,29 @@
         <v>13</v>
       </c>
       <c r="B228" s="7">
-        <v>255</v>
+        <v>211</v>
       </c>
       <c t="s" r="C228" s="7">
         <v>14</v>
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>191</v>
+        <v>300</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>243</v>
+        <v>124</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8487,14 +8491,14 @@
         <v>13</v>
       </c>
       <c r="B229" s="7">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c t="s" r="C229" s="7">
         <v>14</v>
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8506,10 +8510,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>299</v>
+        <v>229</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8542,7 +8546,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8557,7 +8561,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8575,7 +8579,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8587,10 +8591,10 @@
         <v>119</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8608,7 +8612,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8620,10 +8624,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8641,7 +8645,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8689,7 +8693,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8701,10 +8705,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8730,14 +8734,14 @@
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8749,10 +8753,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>307</v>
+        <v>167</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>235</v>
+        <v>120</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8763,14 +8767,14 @@
         <v>13</v>
       </c>
       <c r="B239" s="7">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c t="s" r="C239" s="7">
         <v>14</v>
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8782,10 +8786,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8796,14 +8800,14 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8812,13 +8816,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8829,29 +8833,29 @@
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>308</v>
+        <v>192</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>124</v>
+        <v>245</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8862,14 +8866,14 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8881,10 +8885,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>226</v>
+        <v>308</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9058,7 +9062,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="I248" s="7">
         <v>311</v>
@@ -9088,7 +9092,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>40</v>
@@ -9136,7 +9140,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>40</v>
@@ -9211,7 +9215,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9244,7 +9248,7 @@
         <v>315</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9307,10 +9311,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9391,7 +9395,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9457,7 +9461,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9487,10 +9491,10 @@
         <v>70</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9520,7 +9524,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>22</v>
@@ -9553,7 +9557,7 @@
         <v>320</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>312</v>
@@ -9628,13 +9632,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>95</v>
@@ -9667,7 +9671,7 @@
         <v>119</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>324</v>
@@ -9733,7 +9737,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>162</v>
@@ -9814,10 +9818,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9847,7 +9851,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>21</v>
@@ -9883,7 +9887,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9958,7 +9962,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>74</v>
@@ -9988,7 +9992,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>29</v>
@@ -10090,13 +10094,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="I282" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10120,7 +10124,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>29</v>
@@ -10240,7 +10244,7 @@
         <v>331</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>157</v>
@@ -10273,7 +10277,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>125</v>
@@ -10339,10 +10343,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10390,7 +10394,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10423,7 +10427,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10519,7 +10523,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>73</v>
@@ -10570,7 +10574,7 @@
         <v>180</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10600,7 +10604,7 @@
         <v>119</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>21</v>
@@ -10636,7 +10640,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10666,10 +10670,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10813,7 +10817,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>148</v>
@@ -10849,7 +10853,7 @@
         <v>315</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10882,7 +10886,7 @@
         <v>337</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10930,7 +10934,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11000,7 +11004,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>298</v>
+        <v>198</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11030,7 +11034,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>185</v>
@@ -11063,7 +11067,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>149</v>
@@ -11096,7 +11100,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>71</v>
@@ -11144,7 +11148,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>65</v>
@@ -11243,7 +11247,7 @@
         <v>106</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>342</v>
@@ -11291,7 +11295,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>89</v>
@@ -11324,10 +11328,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11393,7 +11397,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11435,10 +11439,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>345</v>
@@ -11465,7 +11469,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>29</v>
@@ -11504,7 +11508,7 @@
         <v>155</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>101</v>
@@ -11654,7 +11658,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11684,7 +11688,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>65</v>
@@ -11753,7 +11757,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11801,7 +11805,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11942,13 +11946,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11972,7 +11976,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>29</v>
@@ -12011,7 +12015,7 @@
         <v>168</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>69</v>
@@ -12191,7 +12195,7 @@
         <v>155</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>98</v>
@@ -12227,7 +12231,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12260,7 +12264,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12308,7 +12312,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12404,7 +12408,7 @@
         <v>354</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>37</v>
@@ -12437,7 +12441,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>166</v>
@@ -12584,7 +12588,7 @@
         <v>155</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>71</v>
@@ -12617,7 +12621,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>356</v>
@@ -12668,11 +12672,15 @@
         <v>154</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>190</v>
-      </c>
-      <c r="K368" s="7"/>
+        <v>191</v>
+      </c>
+      <c t="s" r="K368" s="7">
+        <v>120</v>
+      </c>
       <c r="L368" s="7"/>
-      <c r="M368" s="7"/>
+      <c t="s" r="M368" s="7">
+        <v>198</v>
+      </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
       <c t="s" r="A369" s="6">
@@ -12734,7 +12742,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12878,7 +12886,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>19</v>
@@ -13025,10 +13033,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13154,7 +13162,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>341</v>
@@ -13184,16 +13192,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13220,10 +13228,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>365</v>
@@ -13250,7 +13258,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>40</v>
@@ -13340,7 +13348,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13370,7 +13378,7 @@
         <v>119</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>116</v>
@@ -13406,7 +13414,7 @@
         <v>370</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13451,7 +13459,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>41</v>
@@ -13484,7 +13492,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>88</v>
@@ -13586,7 +13594,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13667,7 +13675,7 @@
         <v>363</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13730,10 +13738,10 @@
         <v>373</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13766,7 +13774,7 @@
         <v>334</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13841,7 +13849,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>172</v>
@@ -13871,7 +13879,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>40</v>
@@ -14057,10 +14065,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>297</v>
+        <v>197</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>298</v>
+        <v>198</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14189,10 +14197,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14303,10 +14311,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>298</v>
+        <v>198</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14339,7 +14347,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14369,7 +14377,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>151</v>
@@ -14483,10 +14491,10 @@
         <v>383</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14516,7 +14524,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>160</v>
@@ -14630,7 +14638,7 @@
         <v>155</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>172</v>
@@ -14765,7 +14773,7 @@
         <v>324</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14840,7 +14848,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="I440" s="7">
         <v>38</v>
@@ -14870,13 +14878,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>89</v>
@@ -14975,10 +14983,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15056,7 +15064,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="J447" s="7">
         <v>110</v>
@@ -15125,7 +15133,7 @@
         <v>364</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15155,7 +15163,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J450" s="7">
         <v>55</v>
@@ -15221,7 +15229,7 @@
         <v>331</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>151</v>
@@ -15254,7 +15262,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c t="s" r="J453" s="7">
         <v>23</v>
@@ -15305,7 +15313,7 @@
         <v>391</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15420,7 +15428,7 @@
         <v>395</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c t="s" r="J459" s="7">
         <v>396</v>
@@ -15485,7 +15493,7 @@
         <v>5805</v>
       </c>
       <c t="s" r="C462" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
@@ -15518,7 +15526,7 @@
         <v>5806</v>
       </c>
       <c t="s" r="C463" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
@@ -15534,13 +15542,13 @@
         <v>17</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="J463" s="7">
         <v>169</v>
       </c>
       <c t="s" r="K463" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
@@ -15651,7 +15659,7 @@
         <v>1628</v>
       </c>
       <c t="s" r="C468" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
@@ -15670,14 +15678,14 @@
         <v>167</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="K468" s="7">
         <v>169</v>
       </c>
       <c r="L468" s="7"/>
       <c t="s" r="M468" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="469" ht="14.25" customHeight="1">
@@ -15714,7 +15722,7 @@
       </c>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -15796,7 +15804,7 @@
         <v>172</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="K472" s="7">
         <v>91</v>
@@ -15833,7 +15841,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>

--- a/Data/FlightPlan/FPL_25SEP26.xlsx
+++ b/Data/FlightPlan/FPL_25SEP26.xlsx
@@ -269,7 +269,7 @@
     <t>13:30</t>
   </si>
   <si>
-    <t>14:01</t>
+    <t>14:10</t>
   </si>
   <si>
     <t>14:30</t>
@@ -278,6 +278,9 @@
     <t>16:40</t>
   </si>
   <si>
+    <t>14:55</t>
+  </si>
+  <si>
     <t>VN-A522</t>
   </si>
   <si>
@@ -341,6 +344,9 @@
     <t>14:20</t>
   </si>
   <si>
+    <t>14:38</t>
+  </si>
+  <si>
     <t>HND</t>
   </si>
   <si>
@@ -377,7 +383,7 @@
     <t>11:30</t>
   </si>
   <si>
-    <t>15:09</t>
+    <t>14:40</t>
   </si>
   <si>
     <t>15:30</t>
@@ -410,6 +416,9 @@
     <t>11:34</t>
   </si>
   <si>
+    <t>14:12</t>
+  </si>
+  <si>
     <t>15:15</t>
   </si>
   <si>
@@ -443,6 +452,9 @@
     <t>13:20</t>
   </si>
   <si>
+    <t>13:40</t>
+  </si>
+  <si>
     <t>TPE</t>
   </si>
   <si>
@@ -578,9 +590,6 @@
     <t>13:08</t>
   </si>
   <si>
-    <t>14:40</t>
-  </si>
-  <si>
     <t>15:35</t>
   </si>
   <si>
@@ -590,639 +599,630 @@
     <t>17:00</t>
   </si>
   <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>08:42</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>10:38</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>15:23</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>14:16</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>07:44</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>12:26</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>13:13</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>00:40</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
     <t>19:55</t>
   </si>
   <si>
     <t>21:20</t>
   </si>
   <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>08:42</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>10:38</t>
-  </si>
-  <si>
-    <t>12:49</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>13:10</t>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>12:17</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>10:43</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>11:03</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>13:48</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>14:54</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>07:24</t>
+  </si>
+  <si>
+    <t>08:43</t>
+  </si>
+  <si>
+    <t>12:36</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:32</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>13:26</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>11:29</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>07:58</t>
+  </si>
+  <si>
+    <t>11:01</t>
+  </si>
+  <si>
+    <t>13:46</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>12:19</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>11:53</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>14:32</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>16:03</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>13:18</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>07:57</t>
+  </si>
+  <si>
+    <t>13:37</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>10:59</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>12:37</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>12:28</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:59</t>
+  </si>
+  <si>
+    <t>771A *</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>12:33</t>
   </si>
   <si>
     <t>15:05</t>
   </si>
   <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>15:23</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>14:16</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>07:44</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>12:26</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>13:13</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>00:40</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>09:07</t>
-  </si>
-  <si>
-    <t>11:06</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>12:17</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>10:43</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>11:03</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>13:48</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>14:54</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>07:24</t>
-  </si>
-  <si>
-    <t>08:43</t>
-  </si>
-  <si>
-    <t>12:36</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:32</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>13:26</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>11:29</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>07:58</t>
-  </si>
-  <si>
-    <t>11:01</t>
-  </si>
-  <si>
-    <t>13:32</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>12:19</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>08:58</t>
-  </si>
-  <si>
-    <t>11:53</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>16:03</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>11:22</t>
-  </si>
-  <si>
-    <t>13:18</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>07:57</t>
-  </si>
-  <si>
-    <t>13:37</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>10:59</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>12:37</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>10:03</t>
-  </si>
-  <si>
-    <t>12:28</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:59</t>
-  </si>
-  <si>
-    <t>771A *</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>12:33</t>
-  </si>
-  <si>
     <t>04:00</t>
   </si>
   <si>
@@ -1280,9 +1280,6 @@
     <t>10:49</t>
   </si>
   <si>
-    <t>13:14</t>
-  </si>
-  <si>
     <t>13:25</t>
   </si>
   <si>
@@ -1358,9 +1355,6 @@
     <t>07:01</t>
   </si>
   <si>
-    <t>14:38</t>
-  </si>
-  <si>
     <t>VN-A684</t>
   </si>
   <si>
@@ -1412,6 +1406,9 @@
     <t>13:50</t>
   </si>
   <si>
+    <t>13:52</t>
+  </si>
+  <si>
     <t>HKG</t>
   </si>
   <si>
@@ -1424,6 +1421,9 @@
     <t>11:39</t>
   </si>
   <si>
+    <t>14:04</t>
+  </si>
+  <si>
     <t>VN-A698</t>
   </si>
   <si>
@@ -1460,6 +1460,9 @@
     <t>11:12</t>
   </si>
   <si>
+    <t>13:19</t>
+  </si>
+  <si>
     <t>68 *</t>
   </si>
   <si>
@@ -1526,7 +1529,7 @@
     <t>Total Record(s): 392</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 25, 2026 12:03</t>
+    <t xml:space="preserve">Generated on  Sep 25, 2026 12:46</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2987,9 +2990,13 @@
       <c t="s" r="J36" s="7">
         <v>88</v>
       </c>
-      <c r="K36" s="7"/>
+      <c t="s" r="K36" s="7">
+        <v>89</v>
+      </c>
       <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
+      <c t="s" r="M36" s="7">
+        <v>61</v>
+      </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="6"/>
@@ -3018,7 +3025,7 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -3027,18 +3034,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H38" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c t="s" r="M38" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
@@ -3053,27 +3060,27 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G39" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H39" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
       <c t="s" r="M39" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -3088,7 +3095,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -3097,18 +3104,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="I40" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c t="s" r="M40" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -3123,27 +3130,27 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="H41" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c t="s" r="M41" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -3158,7 +3165,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -3173,14 +3180,14 @@
         <v>82</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="K42" s="7">
         <v>56</v>
       </c>
       <c r="L42" s="7"/>
       <c t="s" r="M42" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
@@ -3210,7 +3217,7 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -3219,18 +3226,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="I44" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c t="s" r="M44" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -3245,13 +3252,13 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="H45" s="8">
         <v>30</v>
@@ -3260,11 +3267,13 @@
         <v>19</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
+      <c t="s" r="M45" s="7">
+        <v>111</v>
+      </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c t="s" r="A46" s="6">
@@ -3278,7 +3287,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3287,13 +3296,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I46" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -3311,22 +3320,22 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3359,27 +3368,27 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>76</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
       <c t="s" r="M49" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
@@ -3394,7 +3403,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3406,7 +3415,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c t="s" r="J50" s="7">
         <v>55</v>
@@ -3414,7 +3423,7 @@
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c t="s" r="M50" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
@@ -3429,7 +3438,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3438,10 +3447,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H51" s="8">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c t="s" r="J51" s="7">
         <v>87</v>
@@ -3449,7 +3458,7 @@
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3464,22 +3473,22 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G52" s="8">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="H52" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3497,7 +3506,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3512,7 +3521,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3530,7 +3539,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3542,10 +3551,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3578,7 +3587,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3587,18 +3596,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c t="s" r="M56" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -3613,26 +3622,28 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H57" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c t="s" r="J57" s="7">
         <v>85</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
-      <c r="M57" s="7"/>
+      <c t="s" r="M57" s="7">
+        <v>135</v>
+      </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c t="s" r="A58" s="6">
@@ -3646,7 +3657,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3655,13 +3666,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3679,22 +3690,22 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3712,7 +3723,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3724,10 +3735,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3760,7 +3771,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3769,13 +3780,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3795,27 +3806,27 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c t="s" r="M63" s="7">
-        <v>33</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -3830,7 +3841,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3839,13 +3850,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3863,22 +3874,22 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3896,7 +3907,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3908,10 +3919,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3929,7 +3940,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3938,13 +3949,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3977,7 +3988,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3989,15 +4000,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -4012,7 +4023,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4024,7 +4035,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J70" s="7">
         <v>70</v>
@@ -4032,7 +4043,7 @@
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -4047,7 +4058,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4056,13 +4067,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -4080,22 +4091,22 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="H72" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -4128,7 +4139,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4140,15 +4151,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4163,7 +4174,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4175,15 +4186,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4198,7 +4209,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4207,13 +4218,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -4231,22 +4242,22 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4264,7 +4275,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4297,7 +4308,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4309,10 +4320,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4345,7 +4356,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4357,15 +4368,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4380,7 +4391,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4413,7 +4424,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4422,10 +4433,10 @@
         <v>42</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c t="s" r="J83" s="7">
         <v>52</v>
@@ -4461,7 +4472,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4470,18 +4481,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4496,19 +4507,19 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>32</v>
@@ -4516,7 +4527,7 @@
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4531,27 +4542,27 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4566,19 +4577,19 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c t="s" r="J88" s="7">
         <v>56</v>
@@ -4586,7 +4597,7 @@
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4601,7 +4612,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4610,13 +4621,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>189</v>
+        <v>124</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4634,22 +4645,22 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4660,14 +4671,14 @@
         <v>13</v>
       </c>
       <c r="B91" s="7">
-        <v>312</v>
+        <v>262</v>
       </c>
       <c t="s" r="C91" s="7">
         <v>14</v>
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4676,13 +4687,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>97</v>
+        <v>196</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>64</v>
+        <v>198</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4693,29 +4704,29 @@
         <v>13</v>
       </c>
       <c r="B92" s="7">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c t="s" r="C92" s="7">
         <v>14</v>
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>97</v>
+        <v>196</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4748,7 +4759,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4760,15 +4771,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -4783,7 +4794,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4795,15 +4806,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4818,7 +4829,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4830,15 +4841,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4853,7 +4864,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4865,17 +4876,17 @@
         <v>42</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="K97" s="7">
-        <v>203</v>
+        <v>19</v>
       </c>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4890,7 +4901,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4908,11 +4919,11 @@
         <v>22</v>
       </c>
       <c t="s" r="K98" s="7">
-        <v>204</v>
+        <v>125</v>
       </c>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>47</v>
+        <v>209</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -4942,27 +4953,27 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>207</v>
+        <v>89</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -4977,7 +4988,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4986,13 +4997,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -5010,22 +5021,22 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -5058,19 +5069,19 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="H104" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>19</v>
@@ -5078,7 +5089,7 @@
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5093,7 +5104,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5108,7 +5119,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5126,7 +5137,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5138,10 +5149,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -5159,7 +5170,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5168,13 +5179,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -5207,7 +5218,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5216,18 +5227,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c t="s" r="I109" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5242,13 +5253,13 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>30</v>
@@ -5257,7 +5268,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5277,7 +5288,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5286,18 +5297,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5312,19 +5323,19 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>87</v>
@@ -5345,7 +5356,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5360,7 +5371,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5378,7 +5389,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5390,10 +5401,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5411,7 +5422,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5423,10 +5434,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5459,22 +5470,22 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5494,7 +5505,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5509,14 +5520,14 @@
         <v>55</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="K118" s="7">
         <v>82</v>
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5531,7 +5542,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5540,20 +5551,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="K119" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5568,29 +5579,29 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c t="s" r="K120" s="7">
         <v>75</v>
       </c>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5601,11 +5612,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C121" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5617,7 +5628,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>51</v>
@@ -5634,11 +5645,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C122" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5647,10 +5658,10 @@
         <v>42</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>28</v>
@@ -5686,7 +5697,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5695,10 +5706,10 @@
         <v>42</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>56</v>
@@ -5706,7 +5717,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5721,22 +5732,22 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5754,7 +5765,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5763,13 +5774,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I126" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5787,22 +5798,22 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5835,27 +5846,27 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -5870,7 +5881,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5885,7 +5896,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5903,7 +5914,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5915,7 +5926,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>35</v>
@@ -5936,7 +5947,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5948,10 +5959,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5969,7 +5980,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5981,7 +5992,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J133" s="7">
         <v>65</v>
@@ -6013,17 +6024,17 @@
         <v>7615</v>
       </c>
       <c t="s" r="C135" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>42</v>
@@ -6032,7 +6043,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -6048,11 +6059,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C136" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6064,10 +6075,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>256</v>
+        <v>147</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -6085,7 +6096,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6097,28 +6108,32 @@
         <v>30</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>258</v>
-      </c>
-      <c r="K137" s="7"/>
+        <v>259</v>
+      </c>
+      <c t="s" r="K137" s="7">
+        <v>259</v>
+      </c>
       <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
+      <c t="s" r="M137" s="7">
+        <v>260</v>
+      </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c t="s" r="A138" s="6">
         <v>13</v>
       </c>
       <c r="B138" s="7">
-        <v>262</v>
+        <v>312</v>
       </c>
       <c t="s" r="C138" s="7">
         <v>14</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6127,50 +6142,58 @@
         <v>30</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>259</v>
+        <v>98</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>210</v>
-      </c>
-      <c r="K138" s="7"/>
+        <v>64</v>
+      </c>
+      <c t="s" r="K138" s="7">
+        <v>75</v>
+      </c>
       <c r="L138" s="7"/>
-      <c r="M138" s="7"/>
+      <c t="s" r="M138" s="7">
+        <v>23</v>
+      </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
       <c t="s" r="A139" s="6">
         <v>13</v>
       </c>
       <c r="B139" s="7">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c t="s" r="C139" s="7">
         <v>14</v>
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>259</v>
+        <v>98</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>217</v>
-      </c>
-      <c r="K139" s="7"/>
+        <v>262</v>
+      </c>
+      <c t="s" r="K139" s="7">
+        <v>152</v>
+      </c>
       <c r="L139" s="7"/>
-      <c r="M139" s="7"/>
+      <c t="s" r="M139" s="7">
+        <v>129</v>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="6"/>
@@ -6195,11 +6218,11 @@
         <v>2925</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6211,15 +6234,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6234,7 +6257,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6246,15 +6269,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6269,7 +6292,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6284,11 +6307,15 @@
         <v>34</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>190</v>
-      </c>
-      <c r="K143" s="7"/>
+        <v>193</v>
+      </c>
+      <c t="s" r="K143" s="7">
+        <v>193</v>
+      </c>
       <c r="L143" s="7"/>
-      <c r="M143" s="7"/>
+      <c t="s" r="M143" s="7">
+        <v>126</v>
+      </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
       <c t="s" r="A144" s="6">
@@ -6298,11 +6325,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C144" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6317,14 +6344,14 @@
         <v>34</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="K144" s="7">
-        <v>124</v>
+        <v>265</v>
       </c>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>263</v>
+        <v>198</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6335,11 +6362,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C145" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6348,20 +6375,20 @@
         <v>42</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="K145" s="7">
-        <v>147</v>
+        <v>261</v>
       </c>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>240</v>
+        <v>114</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6372,33 +6399,33 @@
         <v>5069</v>
       </c>
       <c t="s" r="C146" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="K146" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>269</v>
+        <v>132</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6428,7 +6455,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6443,12 +6470,12 @@
         <v>55</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>271</v>
+        <v>207</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6463,7 +6490,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6478,7 +6505,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>260</v>
+        <v>197</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6496,7 +6523,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6508,7 +6535,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>273</v>
@@ -6556,7 +6583,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>45</v>
@@ -6594,7 +6621,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6626,15 +6653,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>271</v>
+        <v>207</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6694,10 +6721,10 @@
         <v>277</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6730,7 +6757,7 @@
         <v>278</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6757,7 +6784,7 @@
         <v>42</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="I158" s="7">
         <v>279</v>
@@ -6808,10 +6835,10 @@
         <v>272</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c t="s" r="K160" s="7">
         <v>282</v>
@@ -6845,14 +6872,16 @@
         <v>30</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>284</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
-      <c r="M161" s="7"/>
+      <c t="s" r="M161" s="7">
+        <v>193</v>
+      </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
       <c t="s" r="A162" s="6">
@@ -6959,10 +6988,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6992,10 +7021,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -7025,10 +7054,10 @@
         <v>290</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7109,7 +7138,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>260</v>
+        <v>197</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -7139,7 +7168,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>294</v>
@@ -7256,7 +7285,7 @@
         <v>282</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7285,13 +7314,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7315,16 +7344,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7351,7 +7380,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>23</v>
@@ -7381,7 +7410,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>30</v>
@@ -7435,7 +7464,7 @@
         <v>293</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>32</v>
@@ -7443,7 +7472,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7470,7 +7499,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>82</v>
@@ -7511,7 +7540,7 @@
         <v>85</v>
       </c>
       <c t="s" r="K183" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
@@ -7542,10 +7571,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>307</v>
+        <v>86</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="K184" s="7">
         <v>87</v>
@@ -7579,13 +7608,13 @@
         <v>30</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>308</v>
+        <v>209</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c t="s" r="K185" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
@@ -7616,10 +7645,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7649,7 +7678,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>279</v>
@@ -7685,7 +7714,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7694,18 +7723,18 @@
         <v>42</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7720,27 +7749,27 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>189</v>
+        <v>124</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7755,7 +7784,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7764,13 +7793,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="I191" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7788,19 +7817,19 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>75</v>
@@ -7821,7 +7850,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7836,7 +7865,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7854,7 +7883,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7866,10 +7895,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7902,7 +7931,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7911,18 +7940,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -7937,27 +7966,27 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -7972,7 +8001,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7987,7 +8016,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -8007,7 +8036,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8019,15 +8048,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8042,7 +8071,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8057,7 +8086,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -8075,7 +8104,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8090,7 +8119,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -8108,7 +8137,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8141,7 +8170,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8153,10 +8182,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -8189,7 +8218,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8204,12 +8233,12 @@
         <v>280</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8224,7 +8253,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8236,7 +8265,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>82</v>
@@ -8259,7 +8288,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8268,7 +8297,7 @@
         <v>42</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>305</v>
@@ -8277,11 +8306,11 @@
         <v>56</v>
       </c>
       <c t="s" r="K207" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>234</v>
+        <v>57</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8296,13 +8325,13 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>42</v>
@@ -8314,11 +8343,11 @@
         <v>59</v>
       </c>
       <c t="s" r="K208" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8333,7 +8362,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8342,16 +8371,16 @@
         <v>42</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>49</v>
       </c>
       <c t="s" r="K209" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
@@ -8370,29 +8399,29 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c t="s" r="K210" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8407,7 +8436,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8419,10 +8448,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8455,7 +8484,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8467,15 +8496,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8490,7 +8519,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8502,10 +8531,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>308</v>
+        <v>209</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8523,22 +8552,22 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
+        <v>327</v>
+      </c>
+      <c r="F215" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G215" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H215" s="8">
         <v>329</v>
       </c>
-      <c r="F215" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G215" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H215" s="8">
-        <v>331</v>
-      </c>
       <c t="s" r="I215" s="7">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8556,22 +8585,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
+        <v>327</v>
+      </c>
+      <c r="F216" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G216" s="8">
         <v>329</v>
       </c>
-      <c r="F216" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G216" s="8">
+      <c t="s" r="H216" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I216" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="J216" s="7">
         <v>331</v>
-      </c>
-      <c t="s" r="H216" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I216" s="7">
-        <v>268</v>
-      </c>
-      <c t="s" r="J216" s="7">
-        <v>332</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8604,7 +8633,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8619,12 +8648,12 @@
         <v>40</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8639,7 +8668,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8651,15 +8680,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8674,7 +8703,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8686,17 +8715,17 @@
         <v>76</v>
       </c>
       <c t="s" r="I220" s="7">
+        <v>336</v>
+      </c>
+      <c t="s" r="J220" s="7">
         <v>337</v>
       </c>
-      <c t="s" r="J220" s="7">
+      <c t="s" r="K220" s="7">
         <v>338</v>
-      </c>
-      <c t="s" r="K220" s="7">
-        <v>339</v>
       </c>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8711,7 +8740,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8729,11 +8758,11 @@
         <v>74</v>
       </c>
       <c t="s" r="K221" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8748,7 +8777,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8760,14 +8789,18 @@
         <v>58</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>278</v>
       </c>
-      <c r="K222" s="7"/>
+      <c t="s" r="K222" s="7">
+        <v>246</v>
+      </c>
       <c r="L222" s="7"/>
-      <c r="M222" s="7"/>
+      <c t="s" r="M222" s="7">
+        <v>127</v>
+      </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
       <c t="s" r="A223" s="6">
@@ -8781,7 +8814,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8793,14 +8826,18 @@
         <v>42</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>148</v>
-      </c>
-      <c r="K223" s="7"/>
+        <v>152</v>
+      </c>
+      <c t="s" r="K223" s="7">
+        <v>128</v>
+      </c>
       <c r="L223" s="7"/>
-      <c r="M223" s="7"/>
+      <c t="s" r="M223" s="7">
+        <v>24</v>
+      </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c r="A224" s="6"/>
@@ -8829,7 +8866,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8841,10 +8878,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I225" s="7">
+        <v>341</v>
+      </c>
+      <c t="s" r="J225" s="7">
         <v>342</v>
-      </c>
-      <c t="s" r="J225" s="7">
-        <v>269</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8864,7 +8901,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8899,7 +8936,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8908,7 +8945,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="I227" s="7">
         <v>84</v>
@@ -8934,22 +8971,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8967,7 +9004,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8979,10 +9016,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -9021,13 +9058,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>347</v>
@@ -9059,7 +9096,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="I232" s="7">
         <v>348</v>
@@ -9091,13 +9128,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>351</v>
@@ -9127,13 +9164,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="I234" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -9226,10 +9263,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -9261,7 +9298,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>70</v>
@@ -9332,7 +9369,7 @@
         <v>357</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -9365,7 +9402,7 @@
         <v>358</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9410,10 +9447,10 @@
         <v>360</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9448,7 +9485,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9477,13 +9514,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9507,16 +9544,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9549,7 +9586,7 @@
         <v>363</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9621,13 +9658,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>84</v>
@@ -9662,14 +9699,16 @@
         <v>58</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>85</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
-      <c r="M252" s="7"/>
+      <c t="s" r="M252" s="7">
+        <v>147</v>
+      </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c t="s" r="A253" s="6">
@@ -9698,7 +9737,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9728,10 +9767,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>260</v>
+        <v>197</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9794,10 +9833,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9842,7 +9881,7 @@
         <v>370</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>45</v>
@@ -9885,7 +9924,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -9912,14 +9951,16 @@
         <v>42</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
-      <c r="M260" s="7"/>
+      <c t="s" r="M260" s="7">
+        <v>372</v>
+      </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
       <c t="s" r="A261" s="6">
@@ -9945,10 +9986,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>189</v>
+        <v>124</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>308</v>
+        <v>209</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9978,10 +10019,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>260</v>
+        <v>197</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10011,7 +10052,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>23</v>
@@ -10041,7 +10082,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>353</v>
@@ -10071,13 +10112,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>373</v>
+        <v>270</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>374</v>
@@ -10157,10 +10198,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>377</v>
@@ -10187,13 +10228,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>78</v>
@@ -10226,10 +10267,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10274,10 +10315,10 @@
         <v>360</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10309,7 +10350,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>71</v>
@@ -10344,7 +10385,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>307</v>
+        <v>86</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>22</v>
@@ -10380,7 +10421,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10407,13 +10448,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="I276" s="7">
         <v>381</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10493,7 +10534,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>55</v>
@@ -10525,7 +10566,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="I280" s="7">
         <v>46</v>
@@ -10557,7 +10598,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>30</v>
@@ -10566,7 +10607,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10671,16 +10712,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>76</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10747,10 +10788,10 @@
         <v>389</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10783,7 +10824,7 @@
         <v>351</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10810,13 +10851,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10840,16 +10881,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10894,10 +10935,10 @@
         <v>360</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10959,13 +11000,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10989,13 +11030,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>64</v>
@@ -11076,10 +11117,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -11108,13 +11149,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -11138,7 +11179,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>30</v>
@@ -11147,7 +11188,7 @@
         <v>292</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>393</v>
+        <v>265</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -11177,10 +11218,10 @@
         <v>370</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11210,10 +11251,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11246,7 +11287,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11255,7 +11296,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="I304" s="7">
         <v>52</v>
@@ -11266,7 +11307,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11281,27 +11322,27 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11316,7 +11357,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11328,10 +11369,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>271</v>
+        <v>207</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11349,7 +11390,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11361,10 +11402,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11382,7 +11423,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11394,7 +11435,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>302</v>
@@ -11430,7 +11471,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11442,15 +11483,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11458,14 +11499,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B311" s="7">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c t="s" r="C311" s="7">
         <v>14</v>
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11480,14 +11521,14 @@
         <v>383</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c t="s" r="K311" s="7">
         <v>383</v>
       </c>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11502,7 +11543,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11514,15 +11555,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11537,7 +11578,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11549,10 +11590,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>207</v>
+        <v>89</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11570,7 +11611,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11582,10 +11623,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11603,7 +11644,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11615,7 +11656,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>77</v>
@@ -11651,7 +11692,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11671,7 +11712,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11686,7 +11727,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11695,13 +11736,13 @@
         <v>76</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>56</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>204</v>
+        <v>403</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11719,22 +11760,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>76</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11752,7 +11793,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11761,7 +11802,7 @@
         <v>76</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>273</v>
@@ -11809,13 +11850,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11841,16 +11882,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11879,13 +11920,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I324" s="7">
         <v>87</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11909,13 +11950,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>273</v>
@@ -11963,7 +12004,7 @@
         <v>356</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>409</v>
@@ -11971,7 +12012,7 @@
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -11998,7 +12039,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>56</v>
@@ -12030,10 +12071,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>22</v>
@@ -12060,7 +12101,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>30</v>
@@ -12117,12 +12158,12 @@
         <v>412</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12149,7 +12190,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>45</v>
@@ -12181,7 +12222,7 @@
         <v>42</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="I334" s="7">
         <v>69</v>
@@ -12213,13 +12254,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>70</v>
@@ -12251,13 +12292,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I336" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12281,16 +12322,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -12332,10 +12373,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>347</v>
@@ -12364,7 +12405,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>30</v>
@@ -12373,7 +12414,7 @@
         <v>409</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12405,10 +12446,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12435,13 +12476,13 @@
         <v>76</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12483,13 +12524,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="I344" s="7">
         <v>347</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12515,7 +12556,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>30</v>
@@ -12551,10 +12592,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>75</v>
@@ -12581,7 +12622,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>30</v>
@@ -12635,13 +12676,13 @@
         <v>30</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="K349" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
@@ -12672,13 +12713,13 @@
         <v>58</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>45</v>
       </c>
       <c t="s" r="K350" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
@@ -12706,7 +12747,7 @@
         <v>58</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="I351" s="7">
         <v>55</v>
@@ -12715,11 +12756,11 @@
         <v>82</v>
       </c>
       <c t="s" r="K351" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>423</v>
+        <v>146</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12740,7 +12781,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>58</v>
@@ -12749,10 +12790,10 @@
         <v>305</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="K352" s="7">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
@@ -12783,17 +12824,17 @@
         <v>360</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>284</v>
       </c>
       <c t="s" r="K353" s="7">
-        <v>133</v>
+        <v>324</v>
       </c>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>308</v>
+        <v>137</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12820,17 +12861,17 @@
         <v>58</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>308</v>
+        <v>209</v>
       </c>
       <c t="s" r="K354" s="7">
-        <v>258</v>
+        <v>138</v>
       </c>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>75</v>
+        <v>198</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12860,7 +12901,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12872,15 +12913,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -12895,7 +12936,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12907,15 +12948,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -12930,7 +12971,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12948,11 +12989,11 @@
         <v>87</v>
       </c>
       <c t="s" r="K358" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>204</v>
+        <v>403</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -12967,7 +13008,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12976,10 +13017,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>66</v>
@@ -13000,22 +13041,22 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -13048,7 +13089,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13060,15 +13101,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13083,7 +13124,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13098,7 +13139,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>204</v>
+        <v>403</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -13116,7 +13157,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13128,10 +13169,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -13149,7 +13190,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13182,7 +13223,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -13194,10 +13235,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -13230,7 +13271,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13242,13 +13283,13 @@
         <v>30</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="K368" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
@@ -13267,7 +13308,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13276,13 +13317,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c t="s" r="I369" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13300,22 +13341,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13333,7 +13374,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13345,10 +13386,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13381,7 +13422,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -13390,10 +13431,10 @@
         <v>42</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>45</v>
@@ -13401,7 +13442,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13416,13 +13457,13 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>42</v>
@@ -13431,12 +13472,12 @@
         <v>69</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -13451,7 +13492,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13463,7 +13504,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>19</v>
@@ -13488,7 +13529,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13506,11 +13547,11 @@
         <v>22</v>
       </c>
       <c t="s" r="K376" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13525,7 +13566,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13534,13 +13575,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13558,22 +13599,22 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I378" s="7">
+        <v>434</v>
+      </c>
+      <c t="s" r="J378" s="7">
         <v>435</v>
-      </c>
-      <c t="s" r="J378" s="7">
-        <v>436</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13606,7 +13647,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13615,18 +13656,18 @@
         <v>42</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -13641,19 +13682,19 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>28</v>
@@ -13661,7 +13702,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13676,7 +13717,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13685,18 +13726,18 @@
         <v>42</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -13711,22 +13752,22 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13744,7 +13785,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13756,14 +13797,18 @@
         <v>293</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>204</v>
+        <v>403</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>88</v>
       </c>
-      <c r="K384" s="7"/>
+      <c t="s" r="K384" s="7">
+        <v>125</v>
+      </c>
       <c r="L384" s="7"/>
-      <c r="M384" s="7"/>
+      <c t="s" r="M384" s="7">
+        <v>61</v>
+      </c>
     </row>
     <row r="385" ht="15" customHeight="1">
       <c t="s" r="A385" s="6">
@@ -13777,7 +13822,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13789,14 +13834,18 @@
         <v>42</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>358</v>
       </c>
-      <c r="K385" s="7"/>
+      <c t="s" r="K385" s="7">
+        <v>313</v>
+      </c>
       <c r="L385" s="7"/>
-      <c r="M385" s="7"/>
+      <c t="s" r="M385" s="7">
+        <v>198</v>
+      </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
       <c t="s" r="A386" s="6">
@@ -13810,7 +13859,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13819,13 +13868,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13843,22 +13892,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I387" s="7">
+        <v>440</v>
+      </c>
+      <c t="s" r="J387" s="7">
         <v>441</v>
-      </c>
-      <c t="s" r="J387" s="7">
-        <v>442</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13891,27 +13940,27 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
+        <v>442</v>
+      </c>
+      <c r="F389" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G389" s="8">
+        <v>117</v>
+      </c>
+      <c t="s" r="H389" s="8">
+        <v>131</v>
+      </c>
+      <c t="s" r="I389" s="7">
+        <v>95</v>
+      </c>
+      <c t="s" r="J389" s="7">
         <v>443</v>
-      </c>
-      <c r="F389" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G389" s="8">
-        <v>115</v>
-      </c>
-      <c t="s" r="H389" s="8">
-        <v>129</v>
-      </c>
-      <c t="s" r="I389" s="7">
-        <v>94</v>
-      </c>
-      <c t="s" r="J389" s="7">
-        <v>444</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -13926,22 +13975,22 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="I390" s="7">
         <v>292</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13959,22 +14008,22 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>285</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13992,22 +14041,22 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -14040,7 +14089,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14049,7 +14098,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="I394" s="7">
         <v>280</v>
@@ -14060,7 +14109,7 @@
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14075,19 +14124,19 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>45</v>
@@ -14095,7 +14144,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14110,7 +14159,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14119,10 +14168,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>87</v>
@@ -14130,7 +14179,7 @@
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>449</v>
+        <v>111</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14145,22 +14194,22 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -14178,7 +14227,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14190,10 +14239,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14226,27 +14275,27 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14261,7 +14310,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14270,17 +14319,19 @@
         <v>58</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>284</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
-      <c r="M401" s="7"/>
+      <c t="s" r="M401" s="7">
+        <v>89</v>
+      </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
       <c t="s" r="A402" s="6">
@@ -14294,22 +14345,22 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
+        <v>448</v>
+      </c>
+      <c r="F402" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G402" s="8">
         <v>450</v>
-      </c>
-      <c r="F402" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G402" s="8">
-        <v>452</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -14327,7 +14378,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14336,13 +14387,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14360,19 +14411,19 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
+        <v>448</v>
+      </c>
+      <c r="F404" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G404" s="8">
         <v>450</v>
-      </c>
-      <c r="F404" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G404" s="8">
-        <v>452</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>302</v>
@@ -14408,27 +14459,27 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14443,7 +14494,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14455,7 +14506,7 @@
         <v>356</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>56</v>
@@ -14463,7 +14514,7 @@
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14478,7 +14529,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14490,10 +14541,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14511,7 +14562,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14520,13 +14571,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c t="s" r="I409" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14544,22 +14595,22 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14577,7 +14628,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14586,13 +14637,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14625,7 +14676,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14634,10 +14685,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>55</v>
@@ -14645,7 +14696,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -14660,27 +14711,27 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -14695,7 +14746,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14707,10 +14758,10 @@
         <v>370</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>256</v>
+        <v>147</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14728,7 +14779,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14743,7 +14794,7 @@
         <v>292</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14761,7 +14812,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14773,10 +14824,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14794,7 +14845,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14806,10 +14857,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14842,7 +14893,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
@@ -14857,12 +14908,12 @@
         <v>45</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -14877,7 +14928,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -14889,15 +14940,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -14912,7 +14963,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -14924,17 +14975,17 @@
         <v>42</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>307</v>
+        <v>86</v>
       </c>
       <c t="s" r="K422" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>207</v>
+        <v>89</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -14949,7 +15000,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14961,10 +15012,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14982,7 +15033,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -14997,7 +15048,7 @@
         <v>285</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -15030,7 +15081,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15039,7 +15090,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c t="s" r="I426" s="7">
         <v>45</v>
@@ -15050,7 +15101,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15065,27 +15116,27 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G427" s="8">
+        <v>461</v>
+      </c>
+      <c t="s" r="H427" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I427" s="7">
         <v>463</v>
       </c>
-      <c t="s" r="H427" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I427" s="7">
-        <v>465</v>
-      </c>
       <c t="s" r="J427" s="7">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>234</v>
+        <v>465</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -15100,7 +15151,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -15109,13 +15160,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c t="s" r="I428" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -15133,22 +15184,22 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -15166,7 +15217,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -15214,7 +15265,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -15234,7 +15285,7 @@
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15249,7 +15300,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -15261,15 +15312,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15284,7 +15335,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -15296,14 +15347,16 @@
         <v>76</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
-      <c r="M434" s="7"/>
+      <c t="s" r="M434" s="7">
+        <v>470</v>
+      </c>
     </row>
     <row r="435" ht="15" customHeight="1">
       <c t="s" r="A435" s="6">
@@ -15317,7 +15370,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -15329,13 +15382,13 @@
         <v>42</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="K435" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
@@ -15354,7 +15407,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -15366,7 +15419,7 @@
         <v>360</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>37</v>
@@ -15387,7 +15440,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -15402,7 +15455,7 @@
         <v>377</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -15420,7 +15473,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -15432,7 +15485,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>383</v>
@@ -15512,13 +15565,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>259</v>
+        <v>196</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15544,16 +15597,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>259</v>
+        <v>196</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="K442" s="7">
         <v>84</v>
@@ -15587,10 +15640,10 @@
         <v>370</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -15620,10 +15673,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15736,10 +15789,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15768,13 +15821,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="I449" s="7">
         <v>82</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15800,20 +15853,22 @@
         <v>320</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>307</v>
+        <v>86</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
-      <c r="M450" s="7"/>
+      <c t="s" r="M450" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
       <c t="s" r="A451" s="6">
@@ -15842,7 +15897,7 @@
         <v>284</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15908,7 +15963,7 @@
         <v>285</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15938,7 +15993,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>24</v>
@@ -16024,11 +16079,13 @@
         <v>70</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
-      <c r="M457" s="7"/>
+      <c t="s" r="M457" s="7">
+        <v>483</v>
+      </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
       <c r="A458" s="6"/>
@@ -16050,20 +16107,20 @@
         <v>13</v>
       </c>
       <c t="s" r="B459" s="7">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c t="s" r="C459" s="7">
         <v>14</v>
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c t="s" r="H459" s="8">
         <v>17</v>
@@ -16072,14 +16129,14 @@
         <v>40</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="K459" s="7">
         <v>40</v>
       </c>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -16094,7 +16151,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -16103,13 +16160,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -16127,22 +16184,22 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -16171,11 +16228,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C463" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
@@ -16184,13 +16241,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -16206,33 +16263,33 @@
         <v>5806</v>
       </c>
       <c t="s" r="C464" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>260</v>
+        <v>197</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c t="s" r="K464" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L464" s="7"/>
       <c t="s" r="M464" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="465" ht="15" customHeight="1">
@@ -16262,27 +16319,27 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G466" s="8">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c t="s" r="H466" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
       <c t="s" r="M466" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="467" ht="14.25" customHeight="1">
@@ -16297,7 +16354,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
@@ -16309,7 +16366,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c t="s" r="J467" s="7">
         <v>23</v>
@@ -16345,7 +16402,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
@@ -16357,17 +16414,17 @@
         <v>58</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>269</v>
+        <v>342</v>
       </c>
       <c t="s" r="K469" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -16382,7 +16439,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
@@ -16391,7 +16448,7 @@
         <v>58</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c t="s" r="I470" s="7">
         <v>69</v>
@@ -16400,11 +16457,11 @@
         <v>22</v>
       </c>
       <c t="s" r="K470" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -16434,7 +16491,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F472" s="7">
         <v>330</v>
@@ -16446,13 +16503,13 @@
         <v>30</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="K472" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L472" s="7"/>
       <c t="s" r="M472" s="7">
@@ -16471,7 +16528,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F473" s="7">
         <v>330</v>
@@ -16480,20 +16537,20 @@
         <v>30</v>
       </c>
       <c t="s" r="H473" s="8">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="K473" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L473" s="7"/>
       <c t="s" r="M473" s="7">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="474" ht="14.25" customHeight="1">
@@ -16508,13 +16565,13 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F474" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G474" s="8">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c t="s" r="H474" s="8">
         <v>30</v>
@@ -16523,11 +16580,15 @@
         <v>51</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>342</v>
-      </c>
-      <c r="K474" s="7"/>
+        <v>341</v>
+      </c>
+      <c t="s" r="K474" s="7">
+        <v>439</v>
+      </c>
       <c r="L474" s="7"/>
-      <c r="M474" s="7"/>
+      <c t="s" r="M474" s="7">
+        <v>183</v>
+      </c>
     </row>
     <row r="475" ht="15" customHeight="1">
       <c r="A475" s="6"/>
@@ -16556,7 +16617,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F476" s="7">
         <v>330</v>
@@ -16565,18 +16626,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H476" s="8">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J476" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
       <c t="s" r="M476" s="7">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="477" ht="14.25" customHeight="1">
@@ -16591,22 +16652,22 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F477" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G477" s="8">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c t="s" r="H477" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I477" s="7">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c t="s" r="J477" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K477" s="7"/>
       <c r="L477" s="7"/>
@@ -16614,7 +16675,7 @@
     </row>
     <row r="478" ht="15.75" customHeight="1">
       <c t="s" r="A478" s="9">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B478" s="9"/>
       <c r="C478" s="9"/>
@@ -16634,7 +16695,7 @@
     <row r="479" ht="65.25" customHeight="1"/>
     <row r="480" ht="17.25" customHeight="1">
       <c t="s" r="A480" s="10">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B480" s="10"/>
       <c r="C480" s="10"/>
@@ -16647,7 +16708,7 @@
       <c r="J480" s="10"/>
       <c r="K480" s="10"/>
       <c t="s" r="L480" s="11">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M480" s="11"/>
       <c r="N480" s="11"/>
